--- a/reports/Group/Project-planing.xlsx
+++ b/reports/Group/Project-planing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxnii\OneDrive\Documentos\DP2\Workspace-26\Projects\Acme-Starters-B\reports\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958EC0B6-6338-4950-A012-B204AA66EE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197D0FBF-C470-425F-8518-8E3B566E135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="Internal" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_DV_Assignees">Internal!$B$9:$B$14</definedName>
+    <definedName name="_DV_Roles">Internal!$B$26:$B$32</definedName>
+    <definedName name="_DV_Types">Internal!$B$35:$B$39</definedName>
     <definedName name="Analyst">Internal!$D$28:$H$28</definedName>
     <definedName name="Developer">Internal!$D$29:$I$29</definedName>
     <definedName name="Manager">Internal!$D$27:$I$27</definedName>
@@ -47,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="264">
   <si>
     <t>Deliverable D01</t>
   </si>
@@ -537,18 +540,6 @@
     <t>Analyst</t>
   </si>
   <si>
-    <t>T0005/D</t>
-  </si>
-  <si>
-    <t>T0009/D</t>
-  </si>
-  <si>
-    <t>T0010/D</t>
-  </si>
-  <si>
-    <t>T0011/D</t>
-  </si>
-  <si>
     <t>Deliverable D03</t>
   </si>
   <si>
@@ -624,84 +615,39 @@
     <t>O</t>
   </si>
   <si>
-    <t>T0001/M</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>EUR 150,00</t>
-  </si>
-  <si>
     <t>Instantiate and share a planning document from the planning template provided, and plan on the tasks required to fulfil the Level B deliverable.</t>
   </si>
   <si>
-    <t>T0002/M</t>
-  </si>
-  <si>
-    <t>EUR 50,00</t>
-  </si>
-  <si>
     <t>Set up the shared workgroup workspace for Level B and ensure all members have access.</t>
   </si>
   <si>
-    <t>T0003/M</t>
-  </si>
-  <si>
-    <t>EUR 100,00</t>
-  </si>
-  <si>
     <t>Prepare a chartering report for Level B. Review and update the charter and risk analysis for Level B scope.</t>
   </si>
   <si>
-    <t>T0004/M</t>
-  </si>
-  <si>
     <t>Initialise the Level B project branch in the workgroup repository at GitHub.</t>
   </si>
   <si>
     <t>Prepare the foundations of the analysis report for Level B, including interpretation notes, open issues, and questions that require lecturer confirmation.</t>
   </si>
   <si>
-    <t>T0006/M</t>
-  </si>
-  <si>
     <t>Ensure that every member understands the scope and goals of Level B and agrees to the common working methodology.</t>
   </si>
   <si>
-    <t>T0007/D</t>
-  </si>
-  <si>
     <t>Adapt the starter project from Level C to Level B. Apply required infrastructure changes and update the project name to "Acme-Starters-B".</t>
   </si>
   <si>
-    <t>T0008/D</t>
-  </si>
-  <si>
-    <t>EUR 25,00</t>
-  </si>
-  <si>
     <t>Create the sample data required to populate administrator accounts with credentials "administrator1/administrator1" and "administrator2/administrator2" for Level B.</t>
   </si>
   <si>
-    <t>EUR 75,00</t>
-  </si>
-  <si>
     <t>Implement the model-level constraints for Level B as sketched in file "Model-BG.uxf".</t>
   </si>
   <si>
-    <t>EUR 250,00</t>
-  </si>
-  <si>
     <t>Implement the Level B data model as sketched in file "Model-B01.uxf". Covers the manager role entity and profile attributes: position, skills, and executive flag (IR-B01, IR-B02).</t>
   </si>
   <si>
     <t>Implement the Level B data model as sketched in file "Model-B02.uxf". Covers the project entity with attributes: title, keywords, description, kick-off moment, and close-out moment (IR-B03).</t>
   </si>
   <si>
-    <t>T0012/D</t>
-  </si>
-  <si>
     <t>Implement the Level B data model as sketched in file "Model-B03.uxf". Covers project components: inventions, campaigns, and strategies linked to projects (IR-B04).</t>
   </si>
   <si>
@@ -711,9 +657,6 @@
     <t>Implement the Level B data model as sketched in file "Model-B05.uxf". Covers project publication state, effort computation (IR-B07), and ad banner entity with slogan, target URL, and picture (IR-B08).</t>
   </si>
   <si>
-    <t>EUR 200,00</t>
-  </si>
-  <si>
     <t>Any authenticated principal must be able to acquire role manager (FR-B01) and update the corresponding manager profile, which includes: position, skills, and executive flag (IR-B02).</t>
   </si>
   <si>
@@ -729,117 +672,54 @@
     <t>Any project member must be able to display project data, including unpublished project data, for projects in which they are involved (FR-B05).</t>
   </si>
   <si>
-    <t>T0020/QA/T0015/D</t>
-  </si>
-  <si>
-    <t>4/14/2025 0:00</t>
-  </si>
-  <si>
-    <t>4/15/2025 0:00</t>
-  </si>
-  <si>
     <t>Test acquire manager role and update manager profile feature.</t>
   </si>
   <si>
-    <t>T0021/QA/T0016/D</t>
-  </si>
-  <si>
     <t>Test manager projects CRUD feature.</t>
   </si>
   <si>
-    <t>T0022/QA/T0017/D</t>
-  </si>
-  <si>
     <t>Test project members management feature.</t>
   </si>
   <si>
-    <t>T0023/QA/T0018/D</t>
-  </si>
-  <si>
     <t>Test project components (add to project) feature.</t>
   </si>
   <si>
-    <t>T0024/QA/T0019/D</t>
-  </si>
-  <si>
     <t>Test project member display feature.</t>
   </si>
   <si>
-    <t>T0025/D</t>
-  </si>
-  <si>
-    <t>4/18/2025 0:00</t>
-  </si>
-  <si>
     <t>A manager must be able to publish his or her projects only when they include at least one invention (FR-B06, IR-B06). Publishing a project must automatically publish all its components (FR-B07).</t>
   </si>
   <si>
-    <t>T0026/D</t>
-  </si>
-  <si>
     <t>Managers must have dashboards displaying: total projects managed, deviation vs. other managers, and min/max/average/standard deviation of project effort (FR-B08, IR-B07).</t>
   </si>
   <si>
-    <t>T0027/D</t>
-  </si>
-  <si>
     <t>Any sponsor may sponsor any published project by attaching any of his or her published sponsorships (FR-B09). Access control must prevent unauthorised access to unpublished project data by non-members (NFR-B02).</t>
   </si>
   <si>
-    <t>T0028/D</t>
-  </si>
-  <si>
     <t>Any auditor may audit any published project by attaching any of his or her published audit reports (FR-B10). Access control must prevent unauthorised access to unpublished project data by non-members (NFR-B02).</t>
   </si>
   <si>
-    <t>T0029/D</t>
-  </si>
-  <si>
     <t>The administrator must be able to manage ad banners (FR-B11). Ad banners must be shown as little intrusively as possible (NFR-B01). Each banner stores: slogan, target URL, and picture (IR-B08).</t>
   </si>
   <si>
-    <t>T0030/QA/T0025/D</t>
-  </si>
-  <si>
-    <t>4/21/2025 0:00</t>
-  </si>
-  <si>
-    <t>4/22/2025 0:00</t>
-  </si>
-  <si>
     <t>Test project publication and cascade publish feature.</t>
   </si>
   <si>
-    <t>T0031/QA/T0026/D</t>
-  </si>
-  <si>
     <t>Test manager dashboard and effort computation feature.</t>
   </si>
   <si>
-    <t>T0032/QA/T0027/D</t>
-  </si>
-  <si>
     <t>Test sponsor attach to published project feature.</t>
   </si>
   <si>
-    <t>T0033/QA/T0028/D</t>
-  </si>
-  <si>
     <t>Test auditor attach audit report to published project feature.</t>
   </si>
   <si>
-    <t>T0034/QA/T0029/D</t>
-  </si>
-  <si>
     <t>Test ad banners management and rendering feature.</t>
   </si>
   <si>
     <t>T0035/D</t>
   </si>
   <si>
-    <t>4/24/2025 0:00</t>
-  </si>
-  <si>
     <t>Implement access control to prevent unauthorised access to unpublished project information by non-members (NFR-B02). Validate transactional consistency of project and component publication (NFR-B04).</t>
   </si>
   <si>
@@ -849,93 +729,42 @@
     <t>Ensure effort computation and dashboard indicators are numerically consistent and reproducible (NFR-B03). Verify formula: sum(active months of components) / number of involved people (IR-B07).</t>
   </si>
   <si>
-    <t>T0037/D</t>
-  </si>
-  <si>
     <t>Implement non-intrusive rendering of ad banners (NFR-B01). Validate that only published sponsorships and audit reports can be attached to published projects (TR-B06).</t>
   </si>
   <si>
-    <t>T0038/QA/T0035/D</t>
-  </si>
-  <si>
-    <t>4/25/2025 0:00</t>
-  </si>
-  <si>
     <t>Test access control and publication transactional consistency.</t>
   </si>
   <si>
-    <t>T0039/QA/T0036/D</t>
-  </si>
-  <si>
     <t>Test effort computation numerical consistency.</t>
   </si>
   <si>
-    <t>T0040/QA/T0037/D</t>
-  </si>
-  <si>
     <t>Test ad banner rendering and sponsorship/audit attachment constraints.</t>
   </si>
   <si>
-    <t>T0041/QA/T0015/D</t>
-  </si>
-  <si>
-    <t>4/28/2025 0:00</t>
-  </si>
-  <si>
-    <t>EUR 120,00</t>
-  </si>
-  <si>
     <t>Produce sample data to test manager role features (TR-B01). Create at least three manager accounts with credentials "manageri/manageri" where "i" ranges from one to three. The last account must have profile data only.</t>
   </si>
   <si>
-    <t>T0042/QA/T0016/D</t>
-  </si>
-  <si>
     <t>Produce sample data with at least three managers and heterogeneous project portfolios (TR-B01, TR-B02). Include projects with mixed publication states and multiple members/components to validate visibility and publication rules.</t>
   </si>
   <si>
-    <t>T0043/QA/T0025/D</t>
-  </si>
-  <si>
     <t>Validate precondition: projects cannot be published unless they contain at least one invention (TR-B03). Validate automatic publication cascade from projects to all components (TR-B04).</t>
   </si>
   <si>
-    <t>T0044/QA/T0026/D</t>
-  </si>
-  <si>
     <t>Validate effort computation and dashboard statistics with deterministic datasets (TR-B05). Verify min, max, average, and standard deviation indicators are numerically correct.</t>
   </si>
   <si>
-    <t>T0045/QA/T0029/D</t>
-  </si>
-  <si>
     <t>Validate that only published sponsorships and audit reports can be attached to published projects (TR-B06). Validate administrator operations and rendering behaviour for ad banners (TR-B07).</t>
   </si>
   <si>
-    <t>EUR 60,00</t>
-  </si>
-  <si>
     <t>Create deployment configuration for Level B application.</t>
   </si>
   <si>
-    <t>4/29/2025 0:00</t>
-  </si>
-  <si>
-    <t>EUR 30,00</t>
-  </si>
-  <si>
     <t>Deploy the Level B application to the target platform.</t>
   </si>
   <si>
-    <t>T0048/M</t>
-  </si>
-  <si>
     <t>Monitor and keep the deployed Level B application healthy and running.</t>
   </si>
   <si>
-    <t>T0049/D</t>
-  </si>
-  <si>
     <t>Package the Level B application and all required deliverables for submission.</t>
   </si>
   <si>
@@ -951,139 +780,94 @@
     <t>Verify that the Level B deliverables have been correctly uploaded to the delivery centre.</t>
   </si>
   <si>
-    <t>3/31/2025 15:30</t>
-  </si>
-  <si>
-    <t>3/31/2025 17:30</t>
-  </si>
-  <si>
-    <t>EUR 0,00</t>
-  </si>
-  <si>
-    <t>T0057/O</t>
-  </si>
-  <si>
-    <t>T0058/O</t>
-  </si>
-  <si>
-    <t>4/14/2025 15:30</t>
-  </si>
-  <si>
-    <t>4/14/2025 17:30</t>
-  </si>
-  <si>
-    <t>T0059/O</t>
-  </si>
-  <si>
-    <t>4/17/2025 17:30</t>
-  </si>
-  <si>
-    <t>4/17/2025 19:30</t>
-  </si>
-  <si>
-    <t>T0060/O</t>
-  </si>
-  <si>
-    <t>4/21/2025 15:30</t>
-  </si>
-  <si>
-    <t>4/21/2025 17:30</t>
-  </si>
-  <si>
-    <t>T0061/O</t>
-  </si>
-  <si>
-    <t>4/24/2025 17:30</t>
-  </si>
-  <si>
-    <t>4/24/2025 19:30</t>
-  </si>
-  <si>
-    <t>T0062/O</t>
-  </si>
-  <si>
-    <t>4/28/2025 15:30</t>
-  </si>
-  <si>
-    <t>4/28/2025 17:30</t>
-  </si>
-  <si>
-    <t>T0063/O</t>
-  </si>
-  <si>
-    <t>3/25/2025 0:00</t>
-  </si>
-  <si>
     <t>Study, read and understand the Level B lecture theory and course materials.</t>
   </si>
   <si>
-    <t>T0064/O</t>
-  </si>
-  <si>
-    <t>3/31/2025 15:00</t>
-  </si>
-  <si>
-    <t>T0065/O</t>
-  </si>
-  <si>
-    <t>T0066/O</t>
-  </si>
-  <si>
-    <t>4/14/2025 15:00</t>
-  </si>
-  <si>
-    <t>T0067/O</t>
-  </si>
-  <si>
-    <t>4/21/2025 15:00</t>
-  </si>
-  <si>
-    <t>T0068/O</t>
-  </si>
-  <si>
-    <t>4/28/2025 15:00</t>
-  </si>
-  <si>
-    <t>T0046/M</t>
-  </si>
-  <si>
     <t>Write the planning report required by the customer's auditor, documenting the project planning, task breakdown, schedule, and resource allocation for Level B.</t>
   </si>
   <si>
-    <t>T0047/M</t>
-  </si>
-  <si>
     <t>Write the Lint report required by the customer's auditor, documenting the results of static code analysis (linting) performed on the Level B codebase.</t>
   </si>
   <si>
     <t>Write the testing report required by the customer's auditor, documenting the formal testing activities, test cases, results, and coverage for Level B.</t>
   </si>
   <si>
-    <t>T0050/D</t>
-  </si>
-  <si>
-    <t>T0051/M</t>
-  </si>
-  <si>
-    <t>T0053/R/T0052/D</t>
-  </si>
-  <si>
-    <t>T0054/R/T0052/D</t>
-  </si>
-  <si>
-    <t>T0055/M</t>
-  </si>
-  <si>
-    <t>T0056/R/T0055/M</t>
-  </si>
-  <si>
-    <t>T0069/O</t>
-  </si>
-  <si>
-    <t>T0070/O</t>
-  </si>
-  <si>
-    <t>T0071/O</t>
+    <t>T0023/D</t>
+  </si>
+  <si>
+    <t>T0034/D</t>
+  </si>
+  <si>
+    <t>T0059/D</t>
+  </si>
+  <si>
+    <t>T0066/R/T0064/D</t>
+  </si>
+  <si>
+    <t>T0067/M</t>
+  </si>
+  <si>
+    <t>Prepare the Level B analysis report and UML data model required by the auditor (MR-B01), including traceability between the structured requirements and the implemented solution.</t>
+  </si>
+  <si>
+    <t>Validate the analysis decisions and requirement ambiguities with a lecturer and document the confirmed resolutions in the analysis report (AR-B01).</t>
+  </si>
+  <si>
+    <t>Update the Level B planning records with progress tracking, budget estimates, and execution notes as required by the planning report (MR-B02, MR-B03).</t>
+  </si>
+  <si>
+    <t>Create and execute formal hacking tests for unpublished project access, including guessed URLs, wrong realm, wrong user, wrong action, and tampered navigation attributes, ensuring intrusion alerts or equivalent protection responses.</t>
+  </si>
+  <si>
+    <t>T0058/QA/T0023/D</t>
+  </si>
+  <si>
+    <t>Record and organise the Level B legal and hacking trace files, converting them into repeatable .legal and .hacking test cases for the formal test suite.</t>
+  </si>
+  <si>
+    <t>T0076/QA/T0058/QA/T0023/D</t>
+  </si>
+  <si>
+    <t>Replay the Level B formal test suite and review instruction coverage and the test case analyser results, identifying missing legal or hacking test cases where feasible.</t>
+  </si>
+  <si>
+    <t>T0077/QA/T0076/QA/T0058/QA/T0023/D</t>
+  </si>
+  <si>
+    <t>Review path coverage, loop cases, and mutation-oriented checks for the Level B test suite, documenting uncovered paths and justified exclusions where applicable.</t>
+  </si>
+  <si>
+    <t>Check testing variability conditions for Level B, including English/Spanish rendering, simulated clock usage for temporal data, and simulated random seed control for repeatable execution.</t>
+  </si>
+  <si>
+    <t>Replay the Level B test suite, import tester.trace into Excel, filter resource requests, compute per-feature execution times, and prepare the summary chart required for the performance analysis workflow.</t>
+  </si>
+  <si>
+    <t>T0080/QA/T0077/QA/T0076/QA/T0058/QA/T0023/D</t>
+  </si>
+  <si>
+    <t>Compute descriptive statistics and a 95% confidence interval for the Level B execution times using the performance data gathered from the formal test suite.</t>
+  </si>
+  <si>
+    <t>Profile the Most Inefficient Request of Level B using the recommended profiling tools and analyse whether the bottleneck is due to software or hardware behaviour.</t>
+  </si>
+  <si>
+    <t>T0082/D</t>
+  </si>
+  <si>
+    <t>Review the Level B queries and refactor them with indices where justified by the performance analysis, documenting the rationale and the affected entities or repositories.</t>
+  </si>
+  <si>
+    <t>T0083/D</t>
+  </si>
+  <si>
+    <t>Collect new performance data after the refactoring, perform the hypothesis contrast or Z-test, and document whether the changes produced a statistically significant improvement.</t>
+  </si>
+  <si>
+    <t>Run lint and check-i18n on the Level B codebase, review the findings, and prepare the evidence to support the Lint report.</t>
+  </si>
+  <si>
+    <t>Write the Level B analysis report required by the auditor, including the requirement analysis, UML data model, documented ambiguities, confirmed lecturer decisions, and traceability notes.</t>
   </si>
 </sst>
 </file>
@@ -1092,9 +876,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$EUR]\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1121,14 +905,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1401,7 +1177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1562,16 +1338,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1583,49 +1353,40 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1635,9 +1396,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1670,6 +1428,34 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2081,7 +1867,9 @@
   <we:alternateReferences>
     <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
   </we:alternateReferences>
-  <we:properties/>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;8710cdab-7c66-4d33-914f-50a168ce45d2&quot;"/>
+  </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </we:webextension>
@@ -2097,118 +1885,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="94" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="103"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="103"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="103"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="103"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="103"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="103"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="103"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="103"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="103"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="97"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="103"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2225,17 +2013,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="95" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
@@ -2249,39 +2037,39 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="94" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -2309,29 +2097,29 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="98" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="99"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="93"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="49"/>
-      <c r="C10" s="104" t="s">
+      <c r="C10" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="99"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="50"/>
@@ -2348,16 +2136,16 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="98" t="s">
         <v>151</v>
       </c>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="99"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2384,40 +2172,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="106" t="s">
+      <c r="C2" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="105"/>
-      <c r="P4" s="105"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -2436,7 +2224,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="102" t="s">
+      <c r="C6" s="96" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -2459,7 +2247,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="105"/>
+      <c r="C7" s="99"/>
       <c r="D7" s="10" t="s">
         <v>4</v>
       </c>
@@ -2477,19 +2265,19 @@
       <c r="F9" s="57"/>
       <c r="G9" s="57"/>
       <c r="H9" s="57"/>
-      <c r="I9" s="102" t="s">
+      <c r="I9" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="105"/>
+      <c r="J9" s="99"/>
       <c r="K9" s="57"/>
-      <c r="L9" s="102" t="s">
+      <c r="L9" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="105"/>
-      <c r="N9" s="102" t="s">
+      <c r="M9" s="99"/>
+      <c r="N9" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="105"/>
+      <c r="O9" s="99"/>
       <c r="P9" s="57"/>
     </row>
     <row r="10" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7547,45 +7335,47 @@
   <dimension ref="B2:P113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
+    <col min="3" max="8" width="18.88671875" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" style="107" customWidth="1"/>
+    <col min="10" max="15" width="18.88671875" customWidth="1"/>
     <col min="16" max="16" width="64.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="95" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
+      <c r="P2" s="93"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93"/>
+      <c r="P4" s="93"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -7594,7 +7384,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="106"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -7604,7 +7394,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="102" t="s">
+      <c r="C6" s="96" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -7612,12 +7402,12 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N113)</f>
-        <v>0</v>
+        <v>7485</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="106"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -7627,13 +7417,13 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="99"/>
+      <c r="C7" s="93"/>
       <c r="D7" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O113)</f>
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -7645,19 +7435,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="98" t="s">
+      <c r="I9" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="99"/>
+      <c r="J9" s="93"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="98" t="s">
+      <c r="L9" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="99"/>
-      <c r="N9" s="98" t="s">
+      <c r="M9" s="93"/>
+      <c r="N9" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="99"/>
+      <c r="O9" s="93"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7711,137 +7501,150 @@
       <c r="B11" s="68">
         <v>1</v>
       </c>
-      <c r="C11" s="69" t="s">
-        <v>183</v>
+      <c r="C11" s="69" t="str">
+        <f>IF(ISBLANK(D11), "", _xlfn.CONCAT("T", TEXT(B11, "0000"), "/", VLOOKUP(D11, Internal!$B$35:C$39, 2, FALSE), IF(OR(D11="QA", D11="Revision"), _xlfn.CONCAT("/", H11), "")))</f>
+        <v>T0001/O</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E11" s="53" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H11" s="53"/>
-      <c r="I11" s="73">
-        <v>45661</v>
-      </c>
-      <c r="J11" s="70">
-        <v>45751</v>
-      </c>
-      <c r="K11" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L11" s="72">
-        <v>3</v>
-      </c>
-      <c r="M11" s="72">
-        <v>4</v>
-      </c>
-      <c r="N11" s="71" t="s">
-        <v>185</v>
-      </c>
-      <c r="O11" s="71"/>
+      <c r="I11" s="108">
+        <v>45741</v>
+      </c>
+      <c r="J11" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K11" s="70" t="str">
+        <f ca="1">IF(OR(I11="",J11=""),"",IF(AND(J11&lt;&gt;"",I11&gt;=NOW()),"Planned",IF(AND(J11&lt;&gt;"",J11&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L11" s="71">
+        <v>20</v>
+      </c>
+      <c r="M11" s="71"/>
+      <c r="N11" s="70">
+        <f>IF(ISBLANK(L11), "", L11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="70" t="str">
+        <f>IF(ISBLANK(M11), "", M11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P11" s="53" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="68">
         <v>2</v>
       </c>
-      <c r="C12" s="69" t="s">
-        <v>187</v>
+      <c r="C12" s="69" t="str">
+        <f>IF(ISBLANK(D12), "", _xlfn.CONCAT("T", TEXT(B12, "0000"), "/", VLOOKUP(D12, Internal!$B$35:C$39, 2, FALSE), IF(OR(D12="QA", D12="Revision"), _xlfn.CONCAT("/", H12), "")))</f>
+        <v>T0002/O</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H12" s="53"/>
-      <c r="I12" s="73">
-        <v>45661</v>
-      </c>
-      <c r="J12" s="70">
-        <v>45751</v>
-      </c>
-      <c r="K12" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L12" s="72">
-        <v>1</v>
-      </c>
-      <c r="M12" s="72">
-        <v>2</v>
-      </c>
-      <c r="N12" s="71" t="s">
-        <v>188</v>
-      </c>
-      <c r="O12" s="71"/>
+      <c r="I12" s="108">
+        <v>45747.625</v>
+      </c>
+      <c r="J12" s="101">
+        <v>45747.645833333299</v>
+      </c>
+      <c r="K12" s="70" t="str">
+        <f ca="1">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L12" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="71"/>
+      <c r="N12" s="70">
+        <f>IF(ISBLANK(L12), "", L12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="70" t="str">
+        <f>IF(ISBLANK(M12), "", M12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P12" s="53" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="68">
         <v>3</v>
       </c>
-      <c r="C13" s="69" t="s">
-        <v>190</v>
+      <c r="C13" s="69" t="str">
+        <f>IF(ISBLANK(D13), "", _xlfn.CONCAT("T", TEXT(B13, "0000"), "/", VLOOKUP(D13, Internal!$B$35:C$39, 2, FALSE), IF(OR(D13="QA", D13="Revision"), _xlfn.CONCAT("/", H13), "")))</f>
+        <v>T0003/O</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E13" s="53" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G13" s="53" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H13" s="53"/>
-      <c r="I13" s="73">
-        <v>45661</v>
-      </c>
-      <c r="J13" s="70">
-        <v>45751</v>
-      </c>
-      <c r="K13" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L13" s="72">
-        <v>2</v>
-      </c>
-      <c r="M13" s="72">
-        <v>3</v>
-      </c>
-      <c r="N13" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="O13" s="71"/>
+      <c r="I13" s="108">
+        <v>45747.645833333299</v>
+      </c>
+      <c r="J13" s="101">
+        <v>45747.729166666701</v>
+      </c>
+      <c r="K13" s="70" t="str">
+        <f ca="1">IF(OR(I13="",J13=""),"",IF(AND(J13&lt;&gt;"",I13&gt;=NOW()),"Planned",IF(AND(J13&lt;&gt;"",J13&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L13" s="71">
+        <v>1.8</v>
+      </c>
+      <c r="M13" s="71"/>
+      <c r="N13" s="70">
+        <f>IF(ISBLANK(L13), "", L13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="70" t="str">
+        <f>IF(ISBLANK(M13), "", M13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P13" s="53" t="s">
-        <v>192</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="68">
         <v>4</v>
       </c>
-      <c r="C14" s="69" t="s">
-        <v>193</v>
+      <c r="C14" s="69" t="str">
+        <f>IF(ISBLANK(D14), "", _xlfn.CONCAT("T", TEXT(B14, "0000"), "/", VLOOKUP(D14, Internal!$B$35:C$39, 2, FALSE), IF(OR(D14="QA", D14="Revision"), _xlfn.CONCAT("/", H14), "")))</f>
+        <v>T0004/M</v>
       </c>
       <c r="D14" s="53" t="s">
         <v>21</v>
@@ -7853,167 +7656,191 @@
         <v>23</v>
       </c>
       <c r="G14" s="53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H14" s="53"/>
-      <c r="I14" s="73">
-        <v>45661</v>
-      </c>
-      <c r="J14" s="70">
+      <c r="I14" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J14" s="101">
         <v>45751</v>
       </c>
-      <c r="K14" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L14" s="72">
-        <v>1</v>
-      </c>
-      <c r="M14" s="72">
-        <v>1</v>
-      </c>
-      <c r="N14" s="71" t="s">
-        <v>188</v>
-      </c>
-      <c r="O14" s="71"/>
+      <c r="K14" s="70" t="str">
+        <f ca="1">IF(OR(I14="",J14=""),"",IF(AND(J14&lt;&gt;"",I14&gt;=NOW()),"Planned",IF(AND(J14&lt;&gt;"",J14&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L14" s="71">
+        <v>3</v>
+      </c>
+      <c r="M14" s="71">
+        <v>4</v>
+      </c>
+      <c r="N14" s="70">
+        <f>IF(ISBLANK(L14), "", L14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>150</v>
+      </c>
+      <c r="O14" s="70">
+        <f>IF(ISBLANK(M14), "", M14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
       <c r="P14" s="53" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="68">
         <v>5</v>
       </c>
-      <c r="C15" s="69" t="s">
-        <v>154</v>
+      <c r="C15" s="69" t="str">
+        <f>IF(ISBLANK(D15), "", _xlfn.CONCAT("T", TEXT(B15, "0000"), "/", VLOOKUP(D15, Internal!$B$35:C$39, 2, FALSE), IF(OR(D15="QA", D15="Revision"), _xlfn.CONCAT("/", H15), "")))</f>
+        <v>T0005/M</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E15" s="53" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G15" s="53" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="53"/>
-      <c r="I15" s="73">
-        <v>45661</v>
-      </c>
-      <c r="J15" s="70">
+      <c r="I15" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J15" s="101">
         <v>45751</v>
       </c>
-      <c r="K15" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L15" s="72">
+      <c r="K15" s="70" t="str">
+        <f ca="1">IF(OR(I15="",J15=""),"",IF(AND(J15&lt;&gt;"",I15&gt;=NOW()),"Planned",IF(AND(J15&lt;&gt;"",J15&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L15" s="71">
+        <v>1</v>
+      </c>
+      <c r="M15" s="71">
         <v>2</v>
       </c>
-      <c r="M15" s="72">
-        <v>3</v>
-      </c>
-      <c r="N15" s="71" t="s">
-        <v>188</v>
-      </c>
-      <c r="O15" s="71"/>
+      <c r="N15" s="70">
+        <f>IF(ISBLANK(L15), "", L15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>50</v>
+      </c>
+      <c r="O15" s="70">
+        <f>IF(ISBLANK(M15), "", M15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
       <c r="P15" s="53" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="68">
         <v>6</v>
       </c>
-      <c r="C16" s="69" t="s">
-        <v>196</v>
+      <c r="C16" s="69" t="str">
+        <f>IF(ISBLANK(D16), "", _xlfn.CONCAT("T", TEXT(B16, "0000"), "/", VLOOKUP(D16, Internal!$B$35:C$39, 2, FALSE), IF(OR(D16="QA", D16="Revision"), _xlfn.CONCAT("/", H16), "")))</f>
+        <v>T0006/M</v>
       </c>
       <c r="D16" s="53" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F16" s="53" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="53" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H16" s="53"/>
-      <c r="I16" s="73">
-        <v>45661</v>
-      </c>
-      <c r="J16" s="70">
+      <c r="I16" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J16" s="101">
         <v>45751</v>
       </c>
-      <c r="K16" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L16" s="72">
-        <v>1</v>
-      </c>
-      <c r="M16" s="72">
-        <v>1</v>
-      </c>
-      <c r="N16" s="71" t="s">
-        <v>188</v>
-      </c>
-      <c r="O16" s="71"/>
+      <c r="K16" s="70" t="str">
+        <f ca="1">IF(OR(I16="",J16=""),"",IF(AND(J16&lt;&gt;"",I16&gt;=NOW()),"Planned",IF(AND(J16&lt;&gt;"",J16&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L16" s="71">
+        <v>2</v>
+      </c>
+      <c r="M16" s="71">
+        <v>3</v>
+      </c>
+      <c r="N16" s="70">
+        <f>IF(ISBLANK(L16), "", L16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O16" s="70">
+        <f>IF(ISBLANK(M16), "", M16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>150</v>
+      </c>
       <c r="P16" s="53" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="68">
         <v>7</v>
       </c>
-      <c r="C17" s="69" t="s">
-        <v>198</v>
+      <c r="C17" s="69" t="str">
+        <f>IF(ISBLANK(D17), "", _xlfn.CONCAT("T", TEXT(B17, "0000"), "/", VLOOKUP(D17, Internal!$B$35:C$39, 2, FALSE), IF(OR(D17="QA", D17="Revision"), _xlfn.CONCAT("/", H17), "")))</f>
+        <v>T0007/M</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G17" s="53" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="73">
-        <v>45661</v>
-      </c>
-      <c r="J17" s="70">
+      <c r="I17" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J17" s="101">
         <v>45751</v>
       </c>
-      <c r="K17" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L17" s="72">
-        <v>2</v>
-      </c>
-      <c r="M17" s="72">
+      <c r="K17" s="70" t="str">
+        <f ca="1">IF(OR(I17="",J17=""),"",IF(AND(J17&lt;&gt;"",I17&gt;=NOW()),"Planned",IF(AND(J17&lt;&gt;"",J17&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L17" s="71">
         <v>1</v>
       </c>
-      <c r="N17" s="71" t="s">
-        <v>188</v>
-      </c>
-      <c r="O17" s="71"/>
+      <c r="M17" s="71">
+        <v>1</v>
+      </c>
+      <c r="N17" s="70">
+        <f>IF(ISBLANK(L17), "", L17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>50</v>
+      </c>
+      <c r="O17" s="70">
+        <f>IF(ISBLANK(M17), "", M17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>50</v>
+      </c>
       <c r="P17" s="53" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="68">
         <v>8</v>
       </c>
-      <c r="C18" s="69" t="s">
-        <v>200</v>
+      <c r="C18" s="69" t="str">
+        <f>IF(ISBLANK(D18), "", _xlfn.CONCAT("T", TEXT(B18, "0000"), "/", VLOOKUP(D18, Internal!$B$35:C$39, 2, FALSE), IF(OR(D18="QA", D18="Revision"), _xlfn.CONCAT("/", H18), "")))</f>
+        <v>T0008/D</v>
       </c>
       <c r="D18" s="53" t="s">
         <v>30</v>
@@ -8025,79 +7852,93 @@
         <v>32</v>
       </c>
       <c r="G18" s="53" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="H18" s="53"/>
-      <c r="I18" s="70">
-        <v>45661</v>
-      </c>
-      <c r="J18" s="70">
+      <c r="I18" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J18" s="101">
         <v>45751</v>
       </c>
-      <c r="K18" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L18" s="72">
-        <v>1</v>
-      </c>
-      <c r="M18" s="72">
-        <v>1</v>
-      </c>
-      <c r="N18" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O18" s="71"/>
+      <c r="K18" s="70" t="str">
+        <f ca="1">IF(OR(I18="",J18=""),"",IF(AND(J18&lt;&gt;"",I18&gt;=NOW()),"Planned",IF(AND(J18&lt;&gt;"",J18&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L18" s="71">
+        <v>2</v>
+      </c>
+      <c r="M18" s="71">
+        <v>3</v>
+      </c>
+      <c r="N18" s="70">
+        <f>IF(ISBLANK(L18), "", L18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>50</v>
+      </c>
+      <c r="O18" s="70">
+        <f>IF(ISBLANK(M18), "", M18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>75</v>
+      </c>
       <c r="P18" s="53" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="68">
         <v>9</v>
       </c>
-      <c r="C19" s="69" t="s">
-        <v>155</v>
+      <c r="C19" s="69" t="str">
+        <f>IF(ISBLANK(D19), "", _xlfn.CONCAT("T", TEXT(B19, "0000"), "/", VLOOKUP(D19, Internal!$B$35:C$39, 2, FALSE), IF(OR(D19="QA", D19="Revision"), _xlfn.CONCAT("/", H19), "")))</f>
+        <v>T0009/M</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G19" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="53"/>
+      <c r="I19" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J19" s="101">
+        <v>45751</v>
+      </c>
+      <c r="K19" s="70" t="str">
+        <f ca="1">IF(OR(I19="",J19=""),"",IF(AND(J19&lt;&gt;"",I19&gt;=NOW()),"Planned",IF(AND(J19&lt;&gt;"",J19&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L19" s="71">
+        <v>1</v>
+      </c>
+      <c r="M19" s="71">
+        <v>1</v>
+      </c>
+      <c r="N19" s="70">
+        <f>IF(ISBLANK(L19), "", L19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>50</v>
       </c>
-      <c r="H19" s="53"/>
-      <c r="I19" s="70">
-        <v>45661</v>
-      </c>
-      <c r="J19" s="70">
-        <v>45751</v>
-      </c>
-      <c r="K19" s="71" t="s">
+      <c r="O19" s="70">
+        <f>IF(ISBLANK(M19), "", M19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>50</v>
+      </c>
+      <c r="P19" s="53" t="s">
         <v>184</v>
-      </c>
-      <c r="L19" s="72">
-        <v>3</v>
-      </c>
-      <c r="M19" s="72"/>
-      <c r="N19" s="71" t="s">
-        <v>203</v>
-      </c>
-      <c r="O19" s="71"/>
-      <c r="P19" s="53" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="68">
         <v>10</v>
       </c>
-      <c r="C20" s="69" t="s">
-        <v>156</v>
+      <c r="C20" s="69" t="str">
+        <f>IF(ISBLANK(D20), "", _xlfn.CONCAT("T", TEXT(B20, "0000"), "/", VLOOKUP(D20, Internal!$B$35:C$39, 2, FALSE), IF(OR(D20="QA", D20="Revision"), _xlfn.CONCAT("/", H20), "")))</f>
+        <v>T0010/D</v>
       </c>
       <c r="D20" s="53" t="s">
         <v>30</v>
@@ -8109,77 +7950,93 @@
         <v>32</v>
       </c>
       <c r="G20" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="53"/>
+      <c r="I20" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J20" s="101">
+        <v>45751</v>
+      </c>
+      <c r="K20" s="70" t="str">
+        <f ca="1">IF(OR(I20="",J20=""),"",IF(AND(J20&lt;&gt;"",I20&gt;=NOW()),"Planned",IF(AND(J20&lt;&gt;"",J20&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L20" s="71">
+        <v>2</v>
+      </c>
+      <c r="M20" s="71">
+        <v>1</v>
+      </c>
+      <c r="N20" s="70">
+        <f>IF(ISBLANK(L20), "", L20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>50</v>
       </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J20" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K20" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L20" s="72">
-        <v>10</v>
-      </c>
-      <c r="M20" s="72"/>
-      <c r="N20" s="71" t="s">
-        <v>205</v>
-      </c>
-      <c r="O20" s="71"/>
+      <c r="O20" s="70">
+        <f>IF(ISBLANK(M20), "", M20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
       <c r="P20" s="53" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="68">
         <v>11</v>
       </c>
-      <c r="C21" s="69" t="s">
-        <v>157</v>
+      <c r="C21" s="69" t="str">
+        <f>IF(ISBLANK(D21), "", _xlfn.CONCAT("T", TEXT(B21, "0000"), "/", VLOOKUP(D21, Internal!$B$35:C$39, 2, FALSE), IF(OR(D21="QA", D21="Revision"), _xlfn.CONCAT("/", H21), "")))</f>
+        <v>T0011/D</v>
       </c>
       <c r="D21" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F21" s="53" t="s">
         <v>32</v>
       </c>
       <c r="G21" s="53" t="s">
-        <v>50</v>
+        <v>171</v>
       </c>
       <c r="H21" s="53"/>
-      <c r="I21" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J21" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K21" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L21" s="72">
-        <v>10</v>
-      </c>
-      <c r="M21" s="72"/>
-      <c r="N21" s="71" t="s">
-        <v>205</v>
-      </c>
-      <c r="O21" s="71"/>
+      <c r="I21" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J21" s="101">
+        <v>45751</v>
+      </c>
+      <c r="K21" s="70" t="str">
+        <f ca="1">IF(OR(I21="",J21=""),"",IF(AND(J21&lt;&gt;"",I21&gt;=NOW()),"Planned",IF(AND(J21&lt;&gt;"",J21&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L21" s="71">
+        <v>1</v>
+      </c>
+      <c r="M21" s="71">
+        <v>1</v>
+      </c>
+      <c r="N21" s="70">
+        <f>IF(ISBLANK(L21), "", L21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O21" s="70">
+        <f>IF(ISBLANK(M21), "", M21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
       <c r="P21" s="53" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="68">
         <v>12</v>
       </c>
-      <c r="C22" s="69" t="s">
-        <v>208</v>
+      <c r="C22" s="69" t="str">
+        <f>IF(ISBLANK(D22), "", _xlfn.CONCAT("T", TEXT(B22, "0000"), "/", VLOOKUP(D22, Internal!$B$35:C$39, 2, FALSE), IF(OR(D22="QA", D22="Revision"), _xlfn.CONCAT("/", H22), "")))</f>
+        <v>T0012/D</v>
       </c>
       <c r="D22" s="53" t="s">
         <v>30</v>
@@ -8194,80 +8051,92 @@
         <v>50</v>
       </c>
       <c r="H22" s="53"/>
-      <c r="I22" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J22" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K22" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L22" s="72">
-        <v>10</v>
-      </c>
-      <c r="M22" s="72"/>
-      <c r="N22" s="71" t="s">
-        <v>205</v>
-      </c>
-      <c r="O22" s="71"/>
+      <c r="I22" s="108">
+        <v>45748</v>
+      </c>
+      <c r="J22" s="101">
+        <v>45751</v>
+      </c>
+      <c r="K22" s="70" t="str">
+        <f ca="1">IF(OR(I22="",J22=""),"",IF(AND(J22&lt;&gt;"",I22&gt;=NOW()),"Planned",IF(AND(J22&lt;&gt;"",J22&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L22" s="71">
+        <v>3</v>
+      </c>
+      <c r="M22" s="71"/>
+      <c r="N22" s="70">
+        <f>IF(ISBLANK(L22), "", L22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>75</v>
+      </c>
+      <c r="O22" s="70" t="str">
+        <f>IF(ISBLANK(M22), "", M22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P22" s="53" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="68">
         <v>13</v>
       </c>
-      <c r="C23" s="69" t="s">
-        <v>62</v>
+      <c r="C23" s="69" t="str">
+        <f>IF(ISBLANK(D23), "", _xlfn.CONCAT("T", TEXT(B23, "0000"), "/", VLOOKUP(D23, Internal!$B$35:C$39, 2, FALSE), IF(OR(D23="QA", D23="Revision"), _xlfn.CONCAT("/", H23), "")))</f>
+        <v>T0013/O</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G23" s="53" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H23" s="53"/>
-      <c r="I23" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J23" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K23" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L23" s="72">
-        <v>10</v>
-      </c>
-      <c r="M23" s="72"/>
-      <c r="N23" s="71" t="s">
-        <v>205</v>
-      </c>
-      <c r="O23" s="71"/>
+      <c r="I23" s="108">
+        <v>45750.729166666701</v>
+      </c>
+      <c r="J23" s="101">
+        <v>45750.8125</v>
+      </c>
+      <c r="K23" s="70" t="str">
+        <f ca="1">IF(OR(I23="",J23=""),"",IF(AND(J23&lt;&gt;"",I23&gt;=NOW()),"Planned",IF(AND(J23&lt;&gt;"",J23&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L23" s="71">
+        <v>1.8</v>
+      </c>
+      <c r="M23" s="71"/>
+      <c r="N23" s="70">
+        <f>IF(ISBLANK(L23), "", L23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="70" t="str">
+        <f>IF(ISBLANK(M23), "", M23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P23" s="53" t="s">
-        <v>210</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="68">
         <v>14</v>
       </c>
-      <c r="C24" s="69" t="s">
-        <v>64</v>
+      <c r="C24" s="69" t="str">
+        <f>IF(ISBLANK(D24), "", _xlfn.CONCAT("T", TEXT(B24, "0000"), "/", VLOOKUP(D24, Internal!$B$35:C$39, 2, FALSE), IF(OR(D24="QA", D24="Revision"), _xlfn.CONCAT("/", H24), "")))</f>
+        <v>T0014/D</v>
       </c>
       <c r="D24" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F24" s="53" t="s">
         <v>32</v>
@@ -8276,39 +8145,45 @@
         <v>50</v>
       </c>
       <c r="H24" s="53"/>
-      <c r="I24" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J24" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K24" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L24" s="72">
+      <c r="I24" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J24" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K24" s="70" t="str">
+        <f ca="1">IF(OR(I24="",J24=""),"",IF(AND(J24&lt;&gt;"",I24&gt;=NOW()),"Planned",IF(AND(J24&lt;&gt;"",J24&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L24" s="71">
         <v>10</v>
       </c>
-      <c r="M24" s="72"/>
-      <c r="N24" s="71" t="s">
-        <v>205</v>
-      </c>
-      <c r="O24" s="71"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="70">
+        <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>250</v>
+      </c>
+      <c r="O24" s="70" t="str">
+        <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P24" s="53" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="68">
         <v>15</v>
       </c>
-      <c r="C25" s="69" t="s">
-        <v>66</v>
+      <c r="C25" s="69" t="str">
+        <f>IF(ISBLANK(D25), "", _xlfn.CONCAT("T", TEXT(B25, "0000"), "/", VLOOKUP(D25, Internal!$B$35:C$39, 2, FALSE), IF(OR(D25="QA", D25="Revision"), _xlfn.CONCAT("/", H25), "")))</f>
+        <v>T0015/D</v>
       </c>
       <c r="D25" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="53" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F25" s="53" t="s">
         <v>32</v>
@@ -8317,39 +8192,45 @@
         <v>50</v>
       </c>
       <c r="H25" s="53"/>
-      <c r="I25" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J25" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K25" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L25" s="72">
-        <v>8</v>
-      </c>
-      <c r="M25" s="72"/>
-      <c r="N25" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O25" s="71"/>
+      <c r="I25" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J25" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K25" s="70" t="str">
+        <f ca="1">IF(OR(I25="",J25=""),"",IF(AND(J25&lt;&gt;"",I25&gt;=NOW()),"Planned",IF(AND(J25&lt;&gt;"",J25&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L25" s="71">
+        <v>10</v>
+      </c>
+      <c r="M25" s="71"/>
+      <c r="N25" s="70">
+        <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>250</v>
+      </c>
+      <c r="O25" s="70" t="str">
+        <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P25" s="53" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="68">
         <v>16</v>
       </c>
-      <c r="C26" s="69" t="s">
-        <v>68</v>
+      <c r="C26" s="69" t="str">
+        <f>IF(ISBLANK(D26), "", _xlfn.CONCAT("T", TEXT(B26, "0000"), "/", VLOOKUP(D26, Internal!$B$35:C$39, 2, FALSE), IF(OR(D26="QA", D26="Revision"), _xlfn.CONCAT("/", H26), "")))</f>
+        <v>T0016/D</v>
       </c>
       <c r="D26" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F26" s="53" t="s">
         <v>32</v>
@@ -8358,39 +8239,45 @@
         <v>50</v>
       </c>
       <c r="H26" s="53"/>
-      <c r="I26" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J26" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K26" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L26" s="72">
-        <v>8</v>
-      </c>
-      <c r="M26" s="72"/>
-      <c r="N26" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O26" s="71"/>
+      <c r="I26" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J26" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K26" s="70" t="str">
+        <f ca="1">IF(OR(I26="",J26=""),"",IF(AND(J26&lt;&gt;"",I26&gt;=NOW()),"Planned",IF(AND(J26&lt;&gt;"",J26&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L26" s="71">
+        <v>10</v>
+      </c>
+      <c r="M26" s="71"/>
+      <c r="N26" s="70">
+        <f>IF(ISBLANK(L26), "", L26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>250</v>
+      </c>
+      <c r="O26" s="70" t="str">
+        <f>IF(ISBLANK(M26), "", M26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P26" s="53" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="68">
         <v>17</v>
       </c>
-      <c r="C27" s="69" t="s">
-        <v>70</v>
+      <c r="C27" s="69" t="str">
+        <f>IF(ISBLANK(D27), "", _xlfn.CONCAT("T", TEXT(B27, "0000"), "/", VLOOKUP(D27, Internal!$B$35:C$39, 2, FALSE), IF(OR(D27="QA", D27="Revision"), _xlfn.CONCAT("/", H27), "")))</f>
+        <v>T0017/D</v>
       </c>
       <c r="D27" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="F27" s="53" t="s">
         <v>32</v>
@@ -8399,39 +8286,45 @@
         <v>50</v>
       </c>
       <c r="H27" s="53"/>
-      <c r="I27" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J27" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K27" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L27" s="72">
-        <v>8</v>
-      </c>
-      <c r="M27" s="72"/>
-      <c r="N27" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O27" s="71"/>
+      <c r="I27" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J27" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K27" s="70" t="str">
+        <f ca="1">IF(OR(I27="",J27=""),"",IF(AND(J27&lt;&gt;"",I27&gt;=NOW()),"Planned",IF(AND(J27&lt;&gt;"",J27&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L27" s="71">
+        <v>10</v>
+      </c>
+      <c r="M27" s="71"/>
+      <c r="N27" s="70">
+        <f>IF(ISBLANK(L27), "", L27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>250</v>
+      </c>
+      <c r="O27" s="70" t="str">
+        <f>IF(ISBLANK(M27), "", M27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P27" s="53" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="68">
         <v>18</v>
       </c>
-      <c r="C28" s="69" t="s">
-        <v>116</v>
+      <c r="C28" s="69" t="str">
+        <f>IF(ISBLANK(D28), "", _xlfn.CONCAT("T", TEXT(B28, "0000"), "/", VLOOKUP(D28, Internal!$B$35:C$39, 2, FALSE), IF(OR(D28="QA", D28="Revision"), _xlfn.CONCAT("/", H28), "")))</f>
+        <v>T0018/D</v>
       </c>
       <c r="D28" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F28" s="53" t="s">
         <v>32</v>
@@ -8440,39 +8333,45 @@
         <v>50</v>
       </c>
       <c r="H28" s="53"/>
-      <c r="I28" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J28" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K28" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L28" s="72">
-        <v>8</v>
-      </c>
-      <c r="M28" s="72"/>
-      <c r="N28" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O28" s="71"/>
+      <c r="I28" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J28" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K28" s="70" t="str">
+        <f ca="1">IF(OR(I28="",J28=""),"",IF(AND(J28&lt;&gt;"",I28&gt;=NOW()),"Planned",IF(AND(J28&lt;&gt;"",J28&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L28" s="71">
+        <v>10</v>
+      </c>
+      <c r="M28" s="71"/>
+      <c r="N28" s="70">
+        <f>IF(ISBLANK(L28), "", L28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>250</v>
+      </c>
+      <c r="O28" s="70" t="str">
+        <f>IF(ISBLANK(M28), "", M28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P28" s="53" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="68">
         <v>19</v>
       </c>
-      <c r="C29" s="69" t="s">
-        <v>118</v>
+      <c r="C29" s="69" t="str">
+        <f>IF(ISBLANK(D29), "", _xlfn.CONCAT("T", TEXT(B29, "0000"), "/", VLOOKUP(D29, Internal!$B$35:C$39, 2, FALSE), IF(OR(D29="QA", D29="Revision"), _xlfn.CONCAT("/", H29), "")))</f>
+        <v>T0019/D</v>
       </c>
       <c r="D29" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="53" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F29" s="53" t="s">
         <v>32</v>
@@ -8481,36 +8380,42 @@
         <v>50</v>
       </c>
       <c r="H29" s="53"/>
-      <c r="I29" s="70">
-        <v>45842</v>
-      </c>
-      <c r="J29" s="70">
-        <v>45965</v>
-      </c>
-      <c r="K29" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L29" s="72">
+      <c r="I29" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J29" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K29" s="70" t="str">
+        <f ca="1">IF(OR(I29="",J29=""),"",IF(AND(J29&lt;&gt;"",I29&gt;=NOW()),"Planned",IF(AND(J29&lt;&gt;"",J29&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L29" s="71">
         <v>8</v>
       </c>
-      <c r="M29" s="72"/>
-      <c r="N29" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="70">
+        <f>IF(ISBLANK(L29), "", L29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O29" s="70" t="str">
+        <f>IF(ISBLANK(M29), "", M29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P29" s="53" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="68">
         <v>20</v>
       </c>
-      <c r="C30" s="69" t="s">
-        <v>218</v>
+      <c r="C30" s="69" t="str">
+        <f>IF(ISBLANK(D30), "", _xlfn.CONCAT("T", TEXT(B30, "0000"), "/", VLOOKUP(D30, Internal!$B$35:C$39, 2, FALSE), IF(OR(D30="QA", D30="Revision"), _xlfn.CONCAT("/", H30), "")))</f>
+        <v>T0020/D</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E30" s="53" t="s">
         <v>47</v>
@@ -8519,41 +8424,45 @@
         <v>32</v>
       </c>
       <c r="G30" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="I30" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J30" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="K30" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L30" s="72">
-        <v>1</v>
-      </c>
-      <c r="M30" s="72"/>
-      <c r="N30" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O30" s="71"/>
+        <v>50</v>
+      </c>
+      <c r="H30" s="53"/>
+      <c r="I30" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J30" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K30" s="70" t="str">
+        <f ca="1">IF(OR(I30="",J30=""),"",IF(AND(J30&lt;&gt;"",I30&gt;=NOW()),"Planned",IF(AND(J30&lt;&gt;"",J30&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L30" s="71">
+        <v>8</v>
+      </c>
+      <c r="M30" s="71"/>
+      <c r="N30" s="70">
+        <f>IF(ISBLANK(L30), "", L30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O30" s="70" t="str">
+        <f>IF(ISBLANK(M30), "", M30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P30" s="53" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="68">
         <v>21</v>
       </c>
-      <c r="C31" s="69" t="s">
-        <v>222</v>
+      <c r="C31" s="69" t="str">
+        <f>IF(ISBLANK(D31), "", _xlfn.CONCAT("T", TEXT(B31, "0000"), "/", VLOOKUP(D31, Internal!$B$35:C$39, 2, FALSE), IF(OR(D31="QA", D31="Revision"), _xlfn.CONCAT("/", H31), "")))</f>
+        <v>T0021/D</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E31" s="53" t="s">
         <v>49</v>
@@ -8562,41 +8471,45 @@
         <v>32</v>
       </c>
       <c r="G31" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H31" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="I31" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J31" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="K31" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L31" s="72">
-        <v>1</v>
-      </c>
-      <c r="M31" s="72"/>
-      <c r="N31" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O31" s="71"/>
+        <v>50</v>
+      </c>
+      <c r="H31" s="53"/>
+      <c r="I31" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J31" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K31" s="70" t="str">
+        <f ca="1">IF(OR(I31="",J31=""),"",IF(AND(J31&lt;&gt;"",I31&gt;=NOW()),"Planned",IF(AND(J31&lt;&gt;"",J31&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L31" s="71">
+        <v>8</v>
+      </c>
+      <c r="M31" s="71"/>
+      <c r="N31" s="70">
+        <f>IF(ISBLANK(L31), "", L31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O31" s="70" t="str">
+        <f>IF(ISBLANK(M31), "", M31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P31" s="53" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="68">
         <v>22</v>
       </c>
-      <c r="C32" s="69" t="s">
-        <v>224</v>
+      <c r="C32" s="69" t="str">
+        <f>IF(ISBLANK(D32), "", _xlfn.CONCAT("T", TEXT(B32, "0000"), "/", VLOOKUP(D32, Internal!$B$35:C$39, 2, FALSE), IF(OR(D32="QA", D32="Revision"), _xlfn.CONCAT("/", H32), "")))</f>
+        <v>T0022/D</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E32" s="53" t="s">
         <v>22</v>
@@ -8605,41 +8518,45 @@
         <v>32</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H32" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="I32" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J32" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="K32" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L32" s="72">
-        <v>1</v>
-      </c>
-      <c r="M32" s="72"/>
-      <c r="N32" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O32" s="71"/>
+        <v>50</v>
+      </c>
+      <c r="H32" s="53"/>
+      <c r="I32" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J32" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K32" s="70" t="str">
+        <f ca="1">IF(OR(I32="",J32=""),"",IF(AND(J32&lt;&gt;"",I32&gt;=NOW()),"Planned",IF(AND(J32&lt;&gt;"",J32&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L32" s="71">
+        <v>8</v>
+      </c>
+      <c r="M32" s="71"/>
+      <c r="N32" s="70">
+        <f>IF(ISBLANK(L32), "", L32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O32" s="70" t="str">
+        <f>IF(ISBLANK(M32), "", M32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P32" s="53" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="68">
         <v>23</v>
       </c>
-      <c r="C33" s="69" t="s">
-        <v>226</v>
+      <c r="C33" s="69" t="str">
+        <f>IF(ISBLANK(D33), "", _xlfn.CONCAT("T", TEXT(B33, "0000"), "/", VLOOKUP(D33, Internal!$B$35:C$39, 2, FALSE), IF(OR(D33="QA", D33="Revision"), _xlfn.CONCAT("/", H33), "")))</f>
+        <v>T0023/D</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E33" s="53" t="s">
         <v>56</v>
@@ -8648,292 +8565,336 @@
         <v>32</v>
       </c>
       <c r="G33" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H33" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="I33" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J33" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="K33" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L33" s="72">
-        <v>1</v>
-      </c>
-      <c r="M33" s="72"/>
-      <c r="N33" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O33" s="71"/>
+        <v>50</v>
+      </c>
+      <c r="H33" s="53"/>
+      <c r="I33" s="108">
+        <v>45754</v>
+      </c>
+      <c r="J33" s="101">
+        <v>45758</v>
+      </c>
+      <c r="K33" s="70" t="str">
+        <f ca="1">IF(OR(I33="",J33=""),"",IF(AND(J33&lt;&gt;"",I33&gt;=NOW()),"Planned",IF(AND(J33&lt;&gt;"",J33&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L33" s="71">
+        <v>8</v>
+      </c>
+      <c r="M33" s="71"/>
+      <c r="N33" s="70">
+        <f>IF(ISBLANK(L33), "", L33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O33" s="70" t="str">
+        <f>IF(ISBLANK(M33), "", M33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P33" s="53" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="68">
         <v>24</v>
       </c>
-      <c r="C34" s="69" t="s">
-        <v>228</v>
+      <c r="C34" s="69" t="str">
+        <f>IF(ISBLANK(D34), "", _xlfn.CONCAT("T", TEXT(B34, "0000"), "/", VLOOKUP(D34, Internal!$B$35:C$39, 2, FALSE), IF(OR(D34="QA", D34="Revision"), _xlfn.CONCAT("/", H34), "")))</f>
+        <v>T0024/O</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F34" s="53" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H34" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="I34" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J34" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="K34" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L34" s="72">
-        <v>1</v>
-      </c>
-      <c r="M34" s="72"/>
-      <c r="N34" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O34" s="71"/>
+        <v>43</v>
+      </c>
+      <c r="H34" s="53"/>
+      <c r="I34" s="108">
+        <v>45754.625</v>
+      </c>
+      <c r="J34" s="101">
+        <v>45754.645833333299</v>
+      </c>
+      <c r="K34" s="70" t="str">
+        <f ca="1">IF(OR(I34="",J34=""),"",IF(AND(J34&lt;&gt;"",I34&gt;=NOW()),"Planned",IF(AND(J34&lt;&gt;"",J34&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L34" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="71"/>
+      <c r="N34" s="70">
+        <f>IF(ISBLANK(L34), "", L34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="70" t="str">
+        <f>IF(ISBLANK(M34), "", M34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P34" s="53" t="s">
-        <v>229</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="68">
         <v>25</v>
       </c>
-      <c r="C35" s="69" t="s">
-        <v>230</v>
+      <c r="C35" s="69" t="str">
+        <f>IF(ISBLANK(D35), "", _xlfn.CONCAT("T", TEXT(B35, "0000"), "/", VLOOKUP(D35, Internal!$B$35:C$39, 2, FALSE), IF(OR(D35="QA", D35="Revision"), _xlfn.CONCAT("/", H35), "")))</f>
+        <v>T0025/O</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E35" s="53" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F35" s="53" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G35" s="53" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H35" s="53"/>
-      <c r="I35" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J35" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="K35" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L35" s="72">
-        <v>8</v>
-      </c>
-      <c r="M35" s="72"/>
-      <c r="N35" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O35" s="71"/>
+      <c r="I35" s="108">
+        <v>45754.645833333299</v>
+      </c>
+      <c r="J35" s="101">
+        <v>45754.729166666701</v>
+      </c>
+      <c r="K35" s="70" t="str">
+        <f ca="1">IF(OR(I35="",J35=""),"",IF(AND(J35&lt;&gt;"",I35&gt;=NOW()),"Planned",IF(AND(J35&lt;&gt;"",J35&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L35" s="71">
+        <v>1.8</v>
+      </c>
+      <c r="M35" s="71"/>
+      <c r="N35" s="70">
+        <f>IF(ISBLANK(L35), "", L35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="70" t="str">
+        <f>IF(ISBLANK(M35), "", M35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P35" s="53" t="s">
-        <v>232</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="68">
         <v>26</v>
       </c>
-      <c r="C36" s="69" t="s">
-        <v>233</v>
+      <c r="C36" s="69" t="str">
+        <f>IF(ISBLANK(D36), "", _xlfn.CONCAT("T", TEXT(B36, "0000"), "/", VLOOKUP(D36, Internal!$B$35:C$39, 2, FALSE), IF(OR(D36="QA", D36="Revision"), _xlfn.CONCAT("/", H36), "")))</f>
+        <v>T0026/O</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F36" s="53" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G36" s="53" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H36" s="53"/>
-      <c r="I36" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J36" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="K36" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L36" s="72">
-        <v>8</v>
-      </c>
-      <c r="M36" s="72"/>
-      <c r="N36" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O36" s="71"/>
+      <c r="I36" s="108">
+        <v>45757.729166666701</v>
+      </c>
+      <c r="J36" s="101">
+        <v>45757.8125</v>
+      </c>
+      <c r="K36" s="70" t="str">
+        <f ca="1">IF(OR(I36="",J36=""),"",IF(AND(J36&lt;&gt;"",I36&gt;=NOW()),"Planned",IF(AND(J36&lt;&gt;"",J36&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L36" s="71">
+        <v>1.8</v>
+      </c>
+      <c r="M36" s="71"/>
+      <c r="N36" s="70">
+        <f>IF(ISBLANK(L36), "", L36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="70" t="str">
+        <f>IF(ISBLANK(M36), "", M36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P36" s="53" t="s">
-        <v>234</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="68">
         <v>27</v>
       </c>
-      <c r="C37" s="69" t="s">
-        <v>235</v>
+      <c r="C37" s="69" t="str">
+        <f>IF(ISBLANK(D37), "", _xlfn.CONCAT("T", TEXT(B37, "0000"), "/", VLOOKUP(D37, Internal!$B$35:C$39, 2, FALSE), IF(OR(D37="QA", D37="Revision"), _xlfn.CONCAT("/", H37), "")))</f>
+        <v>T0027/QA/T0019/D</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F37" s="53" t="s">
         <v>32</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H37" s="53"/>
-      <c r="I37" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J37" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="K37" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L37" s="72">
-        <v>8</v>
-      </c>
-      <c r="M37" s="72"/>
-      <c r="N37" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O37" s="71"/>
+        <v>77</v>
+      </c>
+      <c r="H37" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="I37" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J37" s="101">
+        <v>45762</v>
+      </c>
+      <c r="K37" s="70" t="str">
+        <f ca="1">IF(OR(I37="",J37=""),"",IF(AND(J37&lt;&gt;"",I37&gt;=NOW()),"Planned",IF(AND(J37&lt;&gt;"",J37&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L37" s="71">
+        <v>1</v>
+      </c>
+      <c r="M37" s="71"/>
+      <c r="N37" s="70">
+        <f>IF(ISBLANK(L37), "", L37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O37" s="70" t="str">
+        <f>IF(ISBLANK(M37), "", M37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P37" s="53" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="68">
         <v>28</v>
       </c>
-      <c r="C38" s="69" t="s">
-        <v>237</v>
+      <c r="C38" s="69" t="str">
+        <f>IF(ISBLANK(D38), "", _xlfn.CONCAT("T", TEXT(B38, "0000"), "/", VLOOKUP(D38, Internal!$B$35:C$39, 2, FALSE), IF(OR(D38="QA", D38="Revision"), _xlfn.CONCAT("/", H38), "")))</f>
+        <v>T0028/QA/T0020/D</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F38" s="53" t="s">
         <v>32</v>
       </c>
       <c r="G38" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" s="53"/>
-      <c r="I38" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J38" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="K38" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L38" s="72">
-        <v>8</v>
-      </c>
-      <c r="M38" s="72"/>
-      <c r="N38" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O38" s="71"/>
+        <v>77</v>
+      </c>
+      <c r="H38" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="I38" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J38" s="101">
+        <v>45762</v>
+      </c>
+      <c r="K38" s="70" t="str">
+        <f ca="1">IF(OR(I38="",J38=""),"",IF(AND(J38&lt;&gt;"",I38&gt;=NOW()),"Planned",IF(AND(J38&lt;&gt;"",J38&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L38" s="71">
+        <v>1</v>
+      </c>
+      <c r="M38" s="71"/>
+      <c r="N38" s="70">
+        <f>IF(ISBLANK(L38), "", L38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O38" s="70" t="str">
+        <f>IF(ISBLANK(M38), "", M38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P38" s="53" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="68">
         <v>29</v>
       </c>
-      <c r="C39" s="69" t="s">
-        <v>239</v>
+      <c r="C39" s="69" t="str">
+        <f>IF(ISBLANK(D39), "", _xlfn.CONCAT("T", TEXT(B39, "0000"), "/", VLOOKUP(D39, Internal!$B$35:C$39, 2, FALSE), IF(OR(D39="QA", D39="Revision"), _xlfn.CONCAT("/", H39), "")))</f>
+        <v>T0029/QA/T0021/D</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E39" s="53" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F39" s="53" t="s">
         <v>32</v>
       </c>
       <c r="G39" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H39" s="53"/>
-      <c r="I39" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="J39" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="K39" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L39" s="72">
-        <v>8</v>
-      </c>
-      <c r="M39" s="72"/>
-      <c r="N39" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O39" s="71"/>
+        <v>77</v>
+      </c>
+      <c r="H39" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="I39" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J39" s="101">
+        <v>45762</v>
+      </c>
+      <c r="K39" s="70" t="str">
+        <f ca="1">IF(OR(I39="",J39=""),"",IF(AND(J39&lt;&gt;"",I39&gt;=NOW()),"Planned",IF(AND(J39&lt;&gt;"",J39&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L39" s="71">
+        <v>1</v>
+      </c>
+      <c r="M39" s="71"/>
+      <c r="N39" s="70">
+        <f>IF(ISBLANK(L39), "", L39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O39" s="70" t="str">
+        <f>IF(ISBLANK(M39), "", M39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P39" s="53" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="68">
         <v>30</v>
       </c>
-      <c r="C40" s="69" t="s">
-        <v>241</v>
+      <c r="C40" s="69" t="str">
+        <f>IF(ISBLANK(D40), "", _xlfn.CONCAT("T", TEXT(B40, "0000"), "/", VLOOKUP(D40, Internal!$B$35:C$39, 2, FALSE), IF(OR(D40="QA", D40="Revision"), _xlfn.CONCAT("/", H40), "")))</f>
+        <v>T0030/QA/T0022/D</v>
       </c>
       <c r="D40" s="53" t="s">
         <v>59</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F40" s="53" t="s">
         <v>32</v>
@@ -8942,41 +8903,47 @@
         <v>77</v>
       </c>
       <c r="H40" s="53" t="s">
-        <v>230</v>
-      </c>
-      <c r="I40" s="70" t="s">
-        <v>242</v>
-      </c>
-      <c r="J40" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="K40" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L40" s="72">
+        <v>121</v>
+      </c>
+      <c r="I40" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J40" s="101">
+        <v>45762</v>
+      </c>
+      <c r="K40" s="70" t="str">
+        <f ca="1">IF(OR(I40="",J40=""),"",IF(AND(J40&lt;&gt;"",I40&gt;=NOW()),"Planned",IF(AND(J40&lt;&gt;"",J40&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L40" s="71">
         <v>1</v>
       </c>
-      <c r="M40" s="72"/>
-      <c r="N40" s="71" t="s">
+      <c r="M40" s="71"/>
+      <c r="N40" s="70">
+        <f>IF(ISBLANK(L40), "", L40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O40" s="70" t="str">
+        <f>IF(ISBLANK(M40), "", M40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P40" s="53" t="s">
         <v>201</v>
-      </c>
-      <c r="O40" s="71"/>
-      <c r="P40" s="53" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="41" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="68">
         <v>31</v>
       </c>
-      <c r="C41" s="69" t="s">
-        <v>245</v>
+      <c r="C41" s="69" t="str">
+        <f>IF(ISBLANK(D41), "", _xlfn.CONCAT("T", TEXT(B41, "0000"), "/", VLOOKUP(D41, Internal!$B$35:C$39, 2, FALSE), IF(OR(D41="QA", D41="Revision"), _xlfn.CONCAT("/", H41), "")))</f>
+        <v>T0031/QA/T0023/D</v>
       </c>
       <c r="D41" s="53" t="s">
         <v>59</v>
       </c>
       <c r="E41" s="53" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F41" s="53" t="s">
         <v>32</v>
@@ -8985,170 +8952,188 @@
         <v>77</v>
       </c>
       <c r="H41" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="I41" s="70" t="s">
-        <v>242</v>
-      </c>
-      <c r="J41" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="K41" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L41" s="72">
+        <v>238</v>
+      </c>
+      <c r="I41" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J41" s="101">
+        <v>45762</v>
+      </c>
+      <c r="K41" s="70" t="str">
+        <f ca="1">IF(OR(I41="",J41=""),"",IF(AND(J41&lt;&gt;"",I41&gt;=NOW()),"Planned",IF(AND(J41&lt;&gt;"",J41&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L41" s="71">
         <v>1</v>
       </c>
-      <c r="M41" s="72"/>
-      <c r="N41" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O41" s="71"/>
+      <c r="M41" s="71"/>
+      <c r="N41" s="70">
+        <f>IF(ISBLANK(L41), "", L41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O41" s="70" t="str">
+        <f>IF(ISBLANK(M41), "", M41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P41" s="53" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="68">
         <v>32</v>
       </c>
-      <c r="C42" s="69" t="s">
-        <v>247</v>
+      <c r="C42" s="69" t="str">
+        <f>IF(ISBLANK(D42), "", _xlfn.CONCAT("T", TEXT(B42, "0000"), "/", VLOOKUP(D42, Internal!$B$35:C$39, 2, FALSE), IF(OR(D42="QA", D42="Revision"), _xlfn.CONCAT("/", H42), "")))</f>
+        <v>T0032/D</v>
       </c>
       <c r="D42" s="53" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F42" s="53" t="s">
         <v>32</v>
       </c>
       <c r="G42" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H42" s="53" t="s">
-        <v>235</v>
-      </c>
-      <c r="I42" s="70" t="s">
-        <v>242</v>
-      </c>
-      <c r="J42" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="K42" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L42" s="72">
-        <v>1</v>
-      </c>
-      <c r="M42" s="72"/>
-      <c r="N42" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O42" s="71"/>
+        <v>50</v>
+      </c>
+      <c r="H42" s="53"/>
+      <c r="I42" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J42" s="101">
+        <v>45765</v>
+      </c>
+      <c r="K42" s="70" t="str">
+        <f ca="1">IF(OR(I42="",J42=""),"",IF(AND(J42&lt;&gt;"",I42&gt;=NOW()),"Planned",IF(AND(J42&lt;&gt;"",J42&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L42" s="71">
+        <v>8</v>
+      </c>
+      <c r="M42" s="71"/>
+      <c r="N42" s="70">
+        <f>IF(ISBLANK(L42), "", L42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O42" s="70" t="str">
+        <f>IF(ISBLANK(M42), "", M42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P42" s="53" t="s">
-        <v>248</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="68">
         <v>33</v>
       </c>
-      <c r="C43" s="69" t="s">
-        <v>249</v>
+      <c r="C43" s="69" t="str">
+        <f>IF(ISBLANK(D43), "", _xlfn.CONCAT("T", TEXT(B43, "0000"), "/", VLOOKUP(D43, Internal!$B$35:C$39, 2, FALSE), IF(OR(D43="QA", D43="Revision"), _xlfn.CONCAT("/", H43), "")))</f>
+        <v>T0033/D</v>
       </c>
       <c r="D43" s="53" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E43" s="53" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F43" s="53" t="s">
         <v>32</v>
       </c>
       <c r="G43" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H43" s="53" t="s">
-        <v>237</v>
-      </c>
-      <c r="I43" s="70" t="s">
-        <v>242</v>
-      </c>
-      <c r="J43" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="K43" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L43" s="72">
-        <v>1</v>
-      </c>
-      <c r="M43" s="72"/>
-      <c r="N43" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O43" s="71"/>
+        <v>50</v>
+      </c>
+      <c r="H43" s="53"/>
+      <c r="I43" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J43" s="101">
+        <v>45765</v>
+      </c>
+      <c r="K43" s="70" t="str">
+        <f ca="1">IF(OR(I43="",J43=""),"",IF(AND(J43&lt;&gt;"",I43&gt;=NOW()),"Planned",IF(AND(J43&lt;&gt;"",J43&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L43" s="71">
+        <v>8</v>
+      </c>
+      <c r="M43" s="71"/>
+      <c r="N43" s="70">
+        <f>IF(ISBLANK(L43), "", L43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O43" s="70" t="str">
+        <f>IF(ISBLANK(M43), "", M43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P43" s="53" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="68">
         <v>34</v>
       </c>
-      <c r="C44" s="69" t="s">
-        <v>251</v>
+      <c r="C44" s="69" t="str">
+        <f>IF(ISBLANK(D44), "", _xlfn.CONCAT("T", TEXT(B44, "0000"), "/", VLOOKUP(D44, Internal!$B$35:C$39, 2, FALSE), IF(OR(D44="QA", D44="Revision"), _xlfn.CONCAT("/", H44), "")))</f>
+        <v>T0034/D</v>
       </c>
       <c r="D44" s="53" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E44" s="53" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F44" s="53" t="s">
         <v>32</v>
       </c>
       <c r="G44" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H44" s="53" t="s">
-        <v>239</v>
-      </c>
-      <c r="I44" s="70" t="s">
-        <v>242</v>
-      </c>
-      <c r="J44" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="K44" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L44" s="72">
-        <v>1</v>
-      </c>
-      <c r="M44" s="72"/>
-      <c r="N44" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O44" s="71"/>
+        <v>50</v>
+      </c>
+      <c r="H44" s="53"/>
+      <c r="I44" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J44" s="101">
+        <v>45765</v>
+      </c>
+      <c r="K44" s="70" t="str">
+        <f ca="1">IF(OR(I44="",J44=""),"",IF(AND(J44&lt;&gt;"",I44&gt;=NOW()),"Planned",IF(AND(J44&lt;&gt;"",J44&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L44" s="71">
+        <v>8</v>
+      </c>
+      <c r="M44" s="71"/>
+      <c r="N44" s="70">
+        <f>IF(ISBLANK(L44), "", L44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O44" s="70" t="str">
+        <f>IF(ISBLANK(M44), "", M44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P44" s="53" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="68">
         <v>35</v>
       </c>
-      <c r="C45" s="69" t="s">
-        <v>253</v>
+      <c r="C45" s="69" t="str">
+        <f>IF(ISBLANK(D45), "", _xlfn.CONCAT("T", TEXT(B45, "0000"), "/", VLOOKUP(D45, Internal!$B$35:C$39, 2, FALSE), IF(OR(D45="QA", D45="Revision"), _xlfn.CONCAT("/", H45), "")))</f>
+        <v>T0035/D</v>
       </c>
       <c r="D45" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E45" s="53" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F45" s="53" t="s">
         <v>32</v>
@@ -9157,39 +9142,45 @@
         <v>50</v>
       </c>
       <c r="H45" s="53"/>
-      <c r="I45" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="J45" s="70" t="s">
-        <v>254</v>
-      </c>
-      <c r="K45" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L45" s="72">
-        <v>4</v>
-      </c>
-      <c r="M45" s="72"/>
-      <c r="N45" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="O45" s="71"/>
+      <c r="I45" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J45" s="101">
+        <v>45765</v>
+      </c>
+      <c r="K45" s="70" t="str">
+        <f ca="1">IF(OR(I45="",J45=""),"",IF(AND(J45&lt;&gt;"",I45&gt;=NOW()),"Planned",IF(AND(J45&lt;&gt;"",J45&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L45" s="71">
+        <v>8</v>
+      </c>
+      <c r="M45" s="71"/>
+      <c r="N45" s="70">
+        <f>IF(ISBLANK(L45), "", L45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O45" s="70" t="str">
+        <f>IF(ISBLANK(M45), "", M45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P45" s="53" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="68">
         <v>36</v>
       </c>
-      <c r="C46" s="69" t="s">
-        <v>256</v>
+      <c r="C46" s="69" t="str">
+        <f>IF(ISBLANK(D46), "", _xlfn.CONCAT("T", TEXT(B46, "0000"), "/", VLOOKUP(D46, Internal!$B$35:C$39, 2, FALSE), IF(OR(D46="QA", D46="Revision"), _xlfn.CONCAT("/", H46), "")))</f>
+        <v>T0036/D</v>
       </c>
       <c r="D46" s="53" t="s">
         <v>30</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F46" s="53" t="s">
         <v>32</v>
@@ -9198,166 +9189,186 @@
         <v>50</v>
       </c>
       <c r="H46" s="53"/>
-      <c r="I46" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="J46" s="70" t="s">
-        <v>254</v>
-      </c>
-      <c r="K46" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L46" s="72">
-        <v>4</v>
-      </c>
-      <c r="M46" s="72"/>
-      <c r="N46" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="O46" s="71"/>
+      <c r="I46" s="108">
+        <v>45761</v>
+      </c>
+      <c r="J46" s="101">
+        <v>45765</v>
+      </c>
+      <c r="K46" s="70" t="str">
+        <f ca="1">IF(OR(I46="",J46=""),"",IF(AND(J46&lt;&gt;"",I46&gt;=NOW()),"Planned",IF(AND(J46&lt;&gt;"",J46&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L46" s="71">
+        <v>8</v>
+      </c>
+      <c r="M46" s="71"/>
+      <c r="N46" s="70">
+        <f>IF(ISBLANK(L46), "", L46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O46" s="70" t="str">
+        <f>IF(ISBLANK(M46), "", M46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P46" s="53" t="s">
-        <v>257</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="68">
         <v>37</v>
       </c>
-      <c r="C47" s="69" t="s">
-        <v>258</v>
+      <c r="C47" s="69" t="str">
+        <f>IF(ISBLANK(D47), "", _xlfn.CONCAT("T", TEXT(B47, "0000"), "/", VLOOKUP(D47, Internal!$B$35:C$39, 2, FALSE), IF(OR(D47="QA", D47="Revision"), _xlfn.CONCAT("/", H47), "")))</f>
+        <v>T0037/O</v>
       </c>
       <c r="D47" s="53" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E47" s="53" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F47" s="53" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G47" s="53" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H47" s="53"/>
-      <c r="I47" s="70" t="s">
-        <v>243</v>
-      </c>
-      <c r="J47" s="70" t="s">
-        <v>254</v>
-      </c>
-      <c r="K47" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L47" s="72">
-        <v>4</v>
-      </c>
-      <c r="M47" s="72"/>
-      <c r="N47" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="O47" s="71"/>
+      <c r="I47" s="108">
+        <v>45761.625</v>
+      </c>
+      <c r="J47" s="101">
+        <v>45761.645833333299</v>
+      </c>
+      <c r="K47" s="70" t="str">
+        <f ca="1">IF(OR(I47="",J47=""),"",IF(AND(J47&lt;&gt;"",I47&gt;=NOW()),"Planned",IF(AND(J47&lt;&gt;"",J47&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L47" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="M47" s="71"/>
+      <c r="N47" s="70">
+        <f>IF(ISBLANK(L47), "", L47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O47" s="70" t="str">
+        <f>IF(ISBLANK(M47), "", M47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P47" s="53" t="s">
-        <v>259</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="68">
         <v>38</v>
       </c>
-      <c r="C48" s="69" t="s">
-        <v>260</v>
+      <c r="C48" s="69" t="str">
+        <f>IF(ISBLANK(D48), "", _xlfn.CONCAT("T", TEXT(B48, "0000"), "/", VLOOKUP(D48, Internal!$B$35:C$39, 2, FALSE), IF(OR(D48="QA", D48="Revision"), _xlfn.CONCAT("/", H48), "")))</f>
+        <v>T0038/O</v>
       </c>
       <c r="D48" s="53" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F48" s="53" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G48" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H48" s="53" t="s">
-        <v>253</v>
-      </c>
-      <c r="I48" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="J48" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="K48" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L48" s="72">
-        <v>1</v>
-      </c>
-      <c r="M48" s="72"/>
-      <c r="N48" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O48" s="71"/>
+        <v>45</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="108">
+        <v>45761.645833333299</v>
+      </c>
+      <c r="J48" s="101">
+        <v>45761.729166666701</v>
+      </c>
+      <c r="K48" s="70" t="str">
+        <f ca="1">IF(OR(I48="",J48=""),"",IF(AND(J48&lt;&gt;"",I48&gt;=NOW()),"Planned",IF(AND(J48&lt;&gt;"",J48&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L48" s="71">
+        <v>1.8</v>
+      </c>
+      <c r="M48" s="71"/>
+      <c r="N48" s="70">
+        <f>IF(ISBLANK(L48), "", L48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O48" s="70" t="str">
+        <f>IF(ISBLANK(M48), "", M48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P48" s="53" t="s">
-        <v>262</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="68">
         <v>39</v>
       </c>
-      <c r="C49" s="69" t="s">
-        <v>263</v>
+      <c r="C49" s="69" t="str">
+        <f>IF(ISBLANK(D49), "", _xlfn.CONCAT("T", TEXT(B49, "0000"), "/", VLOOKUP(D49, Internal!$B$35:C$39, 2, FALSE), IF(OR(D49="QA", D49="Revision"), _xlfn.CONCAT("/", H49), "")))</f>
+        <v>T0039/O</v>
       </c>
       <c r="D49" s="53" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E49" s="53" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F49" s="53" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G49" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H49" s="53" t="s">
-        <v>256</v>
-      </c>
-      <c r="I49" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="J49" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="K49" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L49" s="72">
-        <v>1</v>
-      </c>
-      <c r="M49" s="72"/>
-      <c r="N49" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O49" s="71"/>
+        <v>45</v>
+      </c>
+      <c r="H49" s="53"/>
+      <c r="I49" s="108">
+        <v>45764.729166666701</v>
+      </c>
+      <c r="J49" s="101">
+        <v>45764.8125</v>
+      </c>
+      <c r="K49" s="70" t="str">
+        <f ca="1">IF(OR(I49="",J49=""),"",IF(AND(J49&lt;&gt;"",I49&gt;=NOW()),"Planned",IF(AND(J49&lt;&gt;"",J49&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L49" s="71">
+        <v>1.8</v>
+      </c>
+      <c r="M49" s="71"/>
+      <c r="N49" s="70">
+        <f>IF(ISBLANK(L49), "", L49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O49" s="70" t="str">
+        <f>IF(ISBLANK(M49), "", M49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P49" s="53" t="s">
-        <v>264</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="68">
         <v>40</v>
       </c>
-      <c r="C50" s="69" t="s">
-        <v>265</v>
+      <c r="C50" s="69" t="str">
+        <f>IF(ISBLANK(D50), "", _xlfn.CONCAT("T", TEXT(B50, "0000"), "/", VLOOKUP(D50, Internal!$B$35:C$39, 2, FALSE), IF(OR(D50="QA", D50="Revision"), _xlfn.CONCAT("/", H50), "")))</f>
+        <v>T0040/QA/T0019/D</v>
       </c>
       <c r="D50" s="53" t="s">
         <v>59</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F50" s="53" t="s">
         <v>32</v>
@@ -9366,836 +9377,958 @@
         <v>77</v>
       </c>
       <c r="H50" s="53" t="s">
-        <v>258</v>
-      </c>
-      <c r="I50" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="J50" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="K50" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L50" s="72">
+        <v>118</v>
+      </c>
+      <c r="I50" s="108">
+        <v>45768</v>
+      </c>
+      <c r="J50" s="101">
+        <v>45769</v>
+      </c>
+      <c r="K50" s="70" t="str">
+        <f ca="1">IF(OR(I50="",J50=""),"",IF(AND(J50&lt;&gt;"",I50&gt;=NOW()),"Planned",IF(AND(J50&lt;&gt;"",J50&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L50" s="71">
         <v>1</v>
       </c>
-      <c r="M50" s="72"/>
-      <c r="N50" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="O50" s="71"/>
+      <c r="M50" s="71"/>
+      <c r="N50" s="70">
+        <f>IF(ISBLANK(L50), "", L50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O50" s="70" t="str">
+        <f>IF(ISBLANK(M50), "", M50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P50" s="53" t="s">
-        <v>266</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="68">
         <v>41</v>
       </c>
-      <c r="C51" s="69" t="s">
-        <v>267</v>
+      <c r="C51" s="69" t="str">
+        <f>IF(ISBLANK(D51), "", _xlfn.CONCAT("T", TEXT(B51, "0000"), "/", VLOOKUP(D51, Internal!$B$35:C$39, 2, FALSE), IF(OR(D51="QA", D51="Revision"), _xlfn.CONCAT("/", H51), "")))</f>
+        <v>T0041/QA/T0020/D</v>
       </c>
       <c r="D51" s="53" t="s">
         <v>59</v>
       </c>
       <c r="E51" s="53" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F51" s="53" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G51" s="53" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="H51" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="I51" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="J51" s="70" t="s">
-        <v>268</v>
-      </c>
-      <c r="K51" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L51" s="72">
-        <v>4</v>
-      </c>
-      <c r="M51" s="72"/>
-      <c r="N51" s="71" t="s">
-        <v>269</v>
-      </c>
-      <c r="O51" s="71"/>
+        <v>119</v>
+      </c>
+      <c r="I51" s="108">
+        <v>45768</v>
+      </c>
+      <c r="J51" s="101">
+        <v>45769</v>
+      </c>
+      <c r="K51" s="70" t="str">
+        <f ca="1">IF(OR(I51="",J51=""),"",IF(AND(J51&lt;&gt;"",I51&gt;=NOW()),"Planned",IF(AND(J51&lt;&gt;"",J51&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L51" s="71">
+        <v>1</v>
+      </c>
+      <c r="M51" s="71"/>
+      <c r="N51" s="70">
+        <f>IF(ISBLANK(L51), "", L51*VLOOKUP($F51,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O51" s="70" t="str">
+        <f>IF(ISBLANK(M51), "", M51*VLOOKUP($F51,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P51" s="53" t="s">
-        <v>270</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="68">
         <v>42</v>
       </c>
-      <c r="C52" s="69" t="s">
-        <v>271</v>
+      <c r="C52" s="69" t="str">
+        <f>IF(ISBLANK(D52), "", _xlfn.CONCAT("T", TEXT(B52, "0000"), "/", VLOOKUP(D52, Internal!$B$35:C$39, 2, FALSE), IF(OR(D52="QA", D52="Revision"), _xlfn.CONCAT("/", H52), "")))</f>
+        <v>T0042/QA/T0021/D</v>
       </c>
       <c r="D52" s="53" t="s">
         <v>59</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F52" s="53" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G52" s="53" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="H52" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="I52" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="J52" s="70" t="s">
-        <v>268</v>
-      </c>
-      <c r="K52" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L52" s="72">
-        <v>4</v>
-      </c>
-      <c r="M52" s="72"/>
-      <c r="N52" s="71" t="s">
-        <v>269</v>
-      </c>
-      <c r="O52" s="71"/>
+        <v>120</v>
+      </c>
+      <c r="I52" s="108">
+        <v>45768</v>
+      </c>
+      <c r="J52" s="101">
+        <v>45769</v>
+      </c>
+      <c r="K52" s="70" t="str">
+        <f ca="1">IF(OR(I52="",J52=""),"",IF(AND(J52&lt;&gt;"",I52&gt;=NOW()),"Planned",IF(AND(J52&lt;&gt;"",J52&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L52" s="71">
+        <v>1</v>
+      </c>
+      <c r="M52" s="71"/>
+      <c r="N52" s="70">
+        <f>IF(ISBLANK(L52), "", L52*VLOOKUP($F52,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O52" s="70" t="str">
+        <f>IF(ISBLANK(M52), "", M52*VLOOKUP($F52,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P52" s="53" t="s">
-        <v>272</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="68">
         <v>43</v>
       </c>
-      <c r="C53" s="69" t="s">
-        <v>273</v>
+      <c r="C53" s="69" t="str">
+        <f>IF(ISBLANK(D53), "", _xlfn.CONCAT("T", TEXT(B53, "0000"), "/", VLOOKUP(D53, Internal!$B$35:C$39, 2, FALSE), IF(OR(D53="QA", D53="Revision"), _xlfn.CONCAT("/", H53), "")))</f>
+        <v>T0043/QA/T0022/D</v>
       </c>
       <c r="D53" s="53" t="s">
         <v>59</v>
       </c>
       <c r="E53" s="53" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F53" s="53" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G53" s="53" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="H53" s="53" t="s">
-        <v>230</v>
-      </c>
-      <c r="I53" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="J53" s="70" t="s">
-        <v>268</v>
-      </c>
-      <c r="K53" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L53" s="72">
-        <v>4</v>
-      </c>
-      <c r="M53" s="72"/>
-      <c r="N53" s="71" t="s">
-        <v>269</v>
-      </c>
-      <c r="O53" s="71"/>
+        <v>121</v>
+      </c>
+      <c r="I53" s="108">
+        <v>45768</v>
+      </c>
+      <c r="J53" s="101">
+        <v>45769</v>
+      </c>
+      <c r="K53" s="70" t="str">
+        <f ca="1">IF(OR(I53="",J53=""),"",IF(AND(J53&lt;&gt;"",I53&gt;=NOW()),"Planned",IF(AND(J53&lt;&gt;"",J53&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L53" s="71">
+        <v>1</v>
+      </c>
+      <c r="M53" s="71"/>
+      <c r="N53" s="70">
+        <f>IF(ISBLANK(L53), "", L53*VLOOKUP($F53,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O53" s="70" t="str">
+        <f>IF(ISBLANK(M53), "", M53*VLOOKUP($F53,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P53" s="53" t="s">
-        <v>274</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="68">
         <v>44</v>
       </c>
-      <c r="C54" s="69" t="s">
-        <v>275</v>
+      <c r="C54" s="69" t="str">
+        <f>IF(ISBLANK(D54), "", _xlfn.CONCAT("T", TEXT(B54, "0000"), "/", VLOOKUP(D54, Internal!$B$35:C$39, 2, FALSE), IF(OR(D54="QA", D54="Revision"), _xlfn.CONCAT("/", H54), "")))</f>
+        <v>T0044/QA/T0023/D</v>
       </c>
       <c r="D54" s="53" t="s">
         <v>59</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F54" s="53" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G54" s="53" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="H54" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="I54" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="J54" s="70" t="s">
-        <v>268</v>
-      </c>
-      <c r="K54" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L54" s="72">
+        <v>238</v>
+      </c>
+      <c r="I54" s="108">
+        <v>45768</v>
+      </c>
+      <c r="J54" s="101">
+        <v>45769</v>
+      </c>
+      <c r="K54" s="70" t="str">
+        <f ca="1">IF(OR(I54="",J54=""),"",IF(AND(J54&lt;&gt;"",I54&gt;=NOW()),"Planned",IF(AND(J54&lt;&gt;"",J54&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L54" s="71">
+        <v>1</v>
+      </c>
+      <c r="M54" s="71"/>
+      <c r="N54" s="70">
+        <f>IF(ISBLANK(L54), "", L54*VLOOKUP($F54,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O54" s="70" t="str">
+        <f>IF(ISBLANK(M54), "", M54*VLOOKUP($F54,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P54" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="72">
+        <v>45</v>
+      </c>
+      <c r="C55" s="73" t="str">
+        <f>IF(ISBLANK(D55), "", _xlfn.CONCAT("T", TEXT(B55, "0000"), "/", VLOOKUP(D55, Internal!$B$35:C$39, 2, FALSE), IF(OR(D55="QA", D55="Revision"), _xlfn.CONCAT("/", H55), "")))</f>
+        <v>T0045/O</v>
+      </c>
+      <c r="D55" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="G55" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="H55" s="74"/>
+      <c r="I55" s="109">
+        <v>45768.625</v>
+      </c>
+      <c r="J55" s="102">
+        <v>45768.645833333299</v>
+      </c>
+      <c r="K55" s="75" t="str">
+        <f ca="1">IF(OR(I55="",J55=""),"",IF(AND(J55&lt;&gt;"",I55&gt;=NOW()),"Planned",IF(AND(J55&lt;&gt;"",J55&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L55" s="76">
+        <v>0.5</v>
+      </c>
+      <c r="M55" s="76"/>
+      <c r="N55" s="75">
+        <f>IF(ISBLANK(L55), "", L55*VLOOKUP($F55,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O55" s="75" t="str">
+        <f>IF(ISBLANK(M55), "", M55*VLOOKUP($F55,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P55" s="74" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="82">
+        <v>46</v>
+      </c>
+      <c r="C56" s="83" t="str">
+        <f>IF(ISBLANK(D56), "", _xlfn.CONCAT("T", TEXT(B56, "0000"), "/", VLOOKUP(D56, Internal!$B$35:C$39, 2, FALSE), IF(OR(D56="QA", D56="Revision"), _xlfn.CONCAT("/", H56), "")))</f>
+        <v>T0046/O</v>
+      </c>
+      <c r="D56" s="84" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="F56" s="84" t="s">
+        <v>40</v>
+      </c>
+      <c r="G56" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="H56" s="84"/>
+      <c r="I56" s="103">
+        <v>45768.645833333299</v>
+      </c>
+      <c r="J56" s="103">
+        <v>45768.729166666701</v>
+      </c>
+      <c r="K56" s="85" t="str">
+        <f ca="1">IF(OR(I56="",J56=""),"",IF(AND(J56&lt;&gt;"",I56&gt;=NOW()),"Planned",IF(AND(J56&lt;&gt;"",J56&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L56" s="86">
+        <v>1.8</v>
+      </c>
+      <c r="M56" s="86"/>
+      <c r="N56" s="85">
+        <f>IF(ISBLANK(L56), "", L56*VLOOKUP($F56,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O56" s="85" t="str">
+        <f>IF(ISBLANK(M56), "", M56*VLOOKUP($F56,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P56" s="84" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="82">
+        <v>47</v>
+      </c>
+      <c r="C57" s="83" t="str">
+        <f>IF(ISBLANK(D57), "", _xlfn.CONCAT("T", TEXT(B57, "0000"), "/", VLOOKUP(D57, Internal!$B$35:C$39, 2, FALSE), IF(OR(D57="QA", D57="Revision"), _xlfn.CONCAT("/", H57), "")))</f>
+        <v>T0047/D</v>
+      </c>
+      <c r="D57" s="84" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="84" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="G57" s="84" t="s">
+        <v>50</v>
+      </c>
+      <c r="H57" s="84"/>
+      <c r="I57" s="103">
+        <v>45769</v>
+      </c>
+      <c r="J57" s="103">
+        <v>45771</v>
+      </c>
+      <c r="K57" s="85" t="str">
+        <f ca="1">IF(OR(I57="",J57=""),"",IF(AND(J57&lt;&gt;"",I57&gt;=NOW()),"Planned",IF(AND(J57&lt;&gt;"",J57&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L57" s="86">
         <v>4</v>
       </c>
-      <c r="M54" s="72"/>
-      <c r="N54" s="71" t="s">
-        <v>269</v>
-      </c>
-      <c r="O54" s="71"/>
-      <c r="P54" s="53" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="55" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="74">
-        <v>45</v>
-      </c>
-      <c r="C55" s="75" t="s">
-        <v>277</v>
-      </c>
-      <c r="D55" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="E55" s="76" t="s">
-        <v>56</v>
-      </c>
-      <c r="F55" s="76" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="H55" s="76" t="s">
-        <v>239</v>
-      </c>
-      <c r="I55" s="77" t="s">
-        <v>261</v>
-      </c>
-      <c r="J55" s="77" t="s">
-        <v>268</v>
-      </c>
-      <c r="K55" s="78" t="s">
-        <v>184</v>
-      </c>
-      <c r="L55" s="79">
+      <c r="M57" s="86"/>
+      <c r="N57" s="85">
+        <f>IF(ISBLANK(L57), "", L57*VLOOKUP($F57,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O57" s="85" t="str">
+        <f>IF(ISBLANK(M57), "", M57*VLOOKUP($F57,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P57" s="84" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="77">
+        <v>48</v>
+      </c>
+      <c r="C58" s="78" t="str">
+        <f>IF(ISBLANK(D58), "", _xlfn.CONCAT("T", TEXT(B58, "0000"), "/", VLOOKUP(D58, Internal!$B$35:C$39, 2, FALSE), IF(OR(D58="QA", D58="Revision"), _xlfn.CONCAT("/", H58), "")))</f>
+        <v>T0048/D</v>
+      </c>
+      <c r="D58" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="G58" s="79" t="s">
+        <v>50</v>
+      </c>
+      <c r="H58" s="79"/>
+      <c r="I58" s="104">
+        <v>45769</v>
+      </c>
+      <c r="J58" s="104">
+        <v>45771</v>
+      </c>
+      <c r="K58" s="80" t="str">
+        <f ca="1">IF(OR(I58="",J58=""),"",IF(AND(J58&lt;&gt;"",I58&gt;=NOW()),"Planned",IF(AND(J58&lt;&gt;"",J58&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L58" s="81">
         <v>4</v>
       </c>
-      <c r="M55" s="79"/>
-      <c r="N55" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="O55" s="78"/>
-      <c r="P55" s="76" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="56" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="86">
-        <v>46</v>
-      </c>
-      <c r="C56" s="87" t="s">
-        <v>323</v>
-      </c>
-      <c r="D56" s="88" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="88" t="s">
-        <v>22</v>
-      </c>
-      <c r="F56" s="88" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="88"/>
-      <c r="I56" s="89">
-        <v>45776</v>
-      </c>
-      <c r="J56" s="89">
-        <v>45776</v>
-      </c>
-      <c r="K56" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L56" s="91">
-        <v>2</v>
-      </c>
-      <c r="M56" s="91"/>
-      <c r="N56" s="90" t="s">
-        <v>191</v>
-      </c>
-      <c r="O56" s="90"/>
-      <c r="P56" s="88" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="57" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="86">
-        <v>47</v>
-      </c>
-      <c r="C57" s="87" t="s">
-        <v>325</v>
-      </c>
-      <c r="D57" s="88" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="88" t="s">
-        <v>22</v>
-      </c>
-      <c r="F57" s="88" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="88"/>
-      <c r="I57" s="89">
-        <v>45776</v>
-      </c>
-      <c r="J57" s="89">
-        <v>45776</v>
-      </c>
-      <c r="K57" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L57" s="91">
-        <v>2</v>
-      </c>
-      <c r="M57" s="91"/>
-      <c r="N57" s="90" t="s">
-        <v>191</v>
-      </c>
-      <c r="O57" s="90"/>
-      <c r="P57" s="88" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="58" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="80">
-        <v>48</v>
-      </c>
-      <c r="C58" s="81" t="s">
-        <v>284</v>
-      </c>
-      <c r="D58" s="82" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="82" t="s">
-        <v>22</v>
-      </c>
-      <c r="F58" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="G58" s="82" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="82"/>
-      <c r="I58" s="83">
-        <v>45776</v>
-      </c>
-      <c r="J58" s="83">
-        <v>45776</v>
-      </c>
-      <c r="K58" s="84" t="s">
-        <v>184</v>
-      </c>
-      <c r="L58" s="85">
-        <v>2</v>
-      </c>
-      <c r="M58" s="85"/>
-      <c r="N58" s="84" t="s">
-        <v>191</v>
-      </c>
-      <c r="O58" s="84"/>
-      <c r="P58" s="82" t="s">
-        <v>327</v>
+      <c r="M58" s="81"/>
+      <c r="N58" s="80">
+        <f>IF(ISBLANK(L58), "", L58*VLOOKUP($F58,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O58" s="80" t="str">
+        <f>IF(ISBLANK(M58), "", M58*VLOOKUP($F58,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P58" s="79" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="92">
+      <c r="B59" s="87">
         <v>49</v>
       </c>
-      <c r="C59" s="93" t="s">
-        <v>286</v>
-      </c>
-      <c r="D59" s="94" t="s">
+      <c r="C59" s="88" t="str">
+        <f>IF(ISBLANK(D59), "", _xlfn.CONCAT("T", TEXT(B59, "0000"), "/", VLOOKUP(D59, Internal!$B$35:C$39, 2, FALSE), IF(OR(D59="QA", D59="Revision"), _xlfn.CONCAT("/", H59), "")))</f>
+        <v>T0049/D</v>
+      </c>
+      <c r="D59" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="94" t="s">
-        <v>47</v>
-      </c>
-      <c r="F59" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="G59" s="94" t="s">
-        <v>123</v>
-      </c>
-      <c r="H59" s="94"/>
-      <c r="I59" s="95" t="s">
-        <v>268</v>
-      </c>
-      <c r="J59" s="95" t="s">
-        <v>268</v>
-      </c>
-      <c r="K59" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="L59" s="97">
-        <v>2</v>
-      </c>
-      <c r="M59" s="97"/>
-      <c r="N59" s="96" t="s">
-        <v>279</v>
-      </c>
-      <c r="O59" s="96"/>
-      <c r="P59" s="94" t="s">
-        <v>280</v>
+      <c r="E59" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="F59" s="89" t="s">
+        <v>32</v>
+      </c>
+      <c r="G59" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="H59" s="89"/>
+      <c r="I59" s="110">
+        <v>45769</v>
+      </c>
+      <c r="J59" s="105">
+        <v>45771</v>
+      </c>
+      <c r="K59" s="90" t="str">
+        <f ca="1">IF(OR(I59="",J59=""),"",IF(AND(J59&lt;&gt;"",I59&gt;=NOW()),"Planned",IF(AND(J59&lt;&gt;"",J59&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L59" s="91">
+        <v>4</v>
+      </c>
+      <c r="M59" s="91"/>
+      <c r="N59" s="90">
+        <f>IF(ISBLANK(L59), "", L59*VLOOKUP($F59,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O59" s="90" t="str">
+        <f>IF(ISBLANK(M59), "", M59*VLOOKUP($F59,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P59" s="89" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B60" s="68">
         <v>50</v>
       </c>
-      <c r="C60" s="69" t="s">
-        <v>328</v>
+      <c r="C60" s="69" t="str">
+        <f>IF(ISBLANK(D60), "", _xlfn.CONCAT("T", TEXT(B60, "0000"), "/", VLOOKUP(D60, Internal!$B$35:C$39, 2, FALSE), IF(OR(D60="QA", D60="Revision"), _xlfn.CONCAT("/", H60), "")))</f>
+        <v>T0050/O</v>
       </c>
       <c r="D60" s="53" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E60" s="53" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F60" s="53" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="G60" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="H60" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="I60" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="J60" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="K60" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L60" s="72">
-        <v>1</v>
-      </c>
-      <c r="M60" s="72"/>
-      <c r="N60" s="71" t="s">
-        <v>282</v>
-      </c>
-      <c r="O60" s="71"/>
+        <v>45</v>
+      </c>
+      <c r="H60" s="53"/>
+      <c r="I60" s="108">
+        <v>45771.729166666701</v>
+      </c>
+      <c r="J60" s="101">
+        <v>45771.8125</v>
+      </c>
+      <c r="K60" s="70" t="str">
+        <f ca="1">IF(OR(I60="",J60=""),"",IF(AND(J60&lt;&gt;"",I60&gt;=NOW()),"Planned",IF(AND(J60&lt;&gt;"",J60&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L60" s="71">
+        <v>1.8</v>
+      </c>
+      <c r="M60" s="71"/>
+      <c r="N60" s="70">
+        <f>IF(ISBLANK(L60), "", L60*VLOOKUP($F60,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O60" s="70" t="str">
+        <f>IF(ISBLANK(M60), "", M60*VLOOKUP($F60,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P60" s="53" t="s">
-        <v>283</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="68">
         <v>51</v>
       </c>
-      <c r="C61" s="69" t="s">
-        <v>329</v>
+      <c r="C61" s="69" t="str">
+        <f>IF(ISBLANK(D61), "", _xlfn.CONCAT("T", TEXT(B61, "0000"), "/", VLOOKUP(D61, Internal!$B$35:C$39, 2, FALSE), IF(OR(D61="QA", D61="Revision"), _xlfn.CONCAT("/", H61), "")))</f>
+        <v>T0051/QA/T0034/D</v>
       </c>
       <c r="D61" s="53" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E61" s="53" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F61" s="53" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="G61" s="53" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="H61" s="53" t="s">
-        <v>328</v>
-      </c>
-      <c r="I61" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="J61" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="K61" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L61" s="72">
-        <v>4</v>
-      </c>
-      <c r="M61" s="72"/>
-      <c r="N61" s="71" t="s">
-        <v>269</v>
-      </c>
-      <c r="O61" s="71"/>
+        <v>239</v>
+      </c>
+      <c r="I61" s="108">
+        <v>45772</v>
+      </c>
+      <c r="J61" s="101">
+        <v>45772</v>
+      </c>
+      <c r="K61" s="70" t="str">
+        <f ca="1">IF(OR(I61="",J61=""),"",IF(AND(J61&lt;&gt;"",I61&gt;=NOW()),"Planned",IF(AND(J61&lt;&gt;"",J61&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L61" s="71">
+        <v>1</v>
+      </c>
+      <c r="M61" s="71"/>
+      <c r="N61" s="70">
+        <f>IF(ISBLANK(L61), "", L61*VLOOKUP($F61,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O61" s="70" t="str">
+        <f>IF(ISBLANK(M61), "", M61*VLOOKUP($F61,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P61" s="53" t="s">
-        <v>285</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="68">
         <v>52</v>
       </c>
-      <c r="C62" s="69" t="s">
-        <v>88</v>
+      <c r="C62" s="69" t="str">
+        <f>IF(ISBLANK(D62), "", _xlfn.CONCAT("T", TEXT(B62, "0000"), "/", VLOOKUP(D62, Internal!$B$35:C$39, 2, FALSE), IF(OR(D62="QA", D62="Revision"), _xlfn.CONCAT("/", H62), "")))</f>
+        <v>T0052/QA/T0035/D</v>
       </c>
       <c r="D62" s="53" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E62" s="53" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F62" s="53" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="G62" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="H62" s="53"/>
-      <c r="I62" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="J62" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="K62" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L62" s="72">
+        <v>77</v>
+      </c>
+      <c r="H62" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="I62" s="108">
+        <v>45772</v>
+      </c>
+      <c r="J62" s="101">
+        <v>45772</v>
+      </c>
+      <c r="K62" s="70" t="str">
+        <f ca="1">IF(OR(I62="",J62=""),"",IF(AND(J62&lt;&gt;"",I62&gt;=NOW()),"Planned",IF(AND(J62&lt;&gt;"",J62&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L62" s="71">
         <v>1</v>
       </c>
-      <c r="M62" s="72"/>
-      <c r="N62" s="71" t="s">
-        <v>282</v>
-      </c>
-      <c r="O62" s="71"/>
+      <c r="M62" s="71"/>
+      <c r="N62" s="70">
+        <f>IF(ISBLANK(L62), "", L62*VLOOKUP($F62,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O62" s="70" t="str">
+        <f>IF(ISBLANK(M62), "", M62*VLOOKUP($F62,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P62" s="53" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="68">
         <v>53</v>
       </c>
-      <c r="C63" s="69" t="s">
-        <v>330</v>
+      <c r="C63" s="69" t="str">
+        <f>IF(ISBLANK(D63), "", _xlfn.CONCAT("T", TEXT(B63, "0000"), "/", VLOOKUP(D63, Internal!$B$35:C$39, 2, FALSE), IF(OR(D63="QA", D63="Revision"), _xlfn.CONCAT("/", H63), "")))</f>
+        <v>T0053/QA/T0036/D</v>
       </c>
       <c r="D63" s="53" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="E63" s="53" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F63" s="53" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G63" s="53" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="H63" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="I63" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="J63" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="K63" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L63" s="72">
-        <v>4</v>
-      </c>
-      <c r="M63" s="72"/>
-      <c r="N63" s="71" t="s">
-        <v>269</v>
-      </c>
-      <c r="O63" s="71"/>
+        <v>215</v>
+      </c>
+      <c r="I63" s="108">
+        <v>45772</v>
+      </c>
+      <c r="J63" s="101">
+        <v>45772</v>
+      </c>
+      <c r="K63" s="70" t="str">
+        <f ca="1">IF(OR(I63="",J63=""),"",IF(AND(J63&lt;&gt;"",I63&gt;=NOW()),"Planned",IF(AND(J63&lt;&gt;"",J63&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L63" s="71">
+        <v>1</v>
+      </c>
+      <c r="M63" s="71"/>
+      <c r="N63" s="70">
+        <f>IF(ISBLANK(L63), "", L63*VLOOKUP($F63,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>25</v>
+      </c>
+      <c r="O63" s="70" t="str">
+        <f>IF(ISBLANK(M63), "", M63*VLOOKUP($F63,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P63" s="53" t="s">
-        <v>288</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="68">
         <v>54</v>
       </c>
-      <c r="C64" s="69" t="s">
-        <v>331</v>
+      <c r="C64" s="69" t="str">
+        <f>IF(ISBLANK(D64), "", _xlfn.CONCAT("T", TEXT(B64, "0000"), "/", VLOOKUP(D64, Internal!$B$35:C$39, 2, FALSE), IF(OR(D64="QA", D64="Revision"), _xlfn.CONCAT("/", H64), "")))</f>
+        <v>T0054/QA/T0064/D</v>
       </c>
       <c r="D64" s="53" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="E64" s="53" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F64" s="53" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G64" s="53" t="s">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="H64" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="I64" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="J64" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="K64" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L64" s="72">
+        <v>101</v>
+      </c>
+      <c r="I64" s="108">
+        <v>45772</v>
+      </c>
+      <c r="J64" s="101">
+        <v>45775</v>
+      </c>
+      <c r="K64" s="70" t="str">
+        <f ca="1">IF(OR(I64="",J64=""),"",IF(AND(J64&lt;&gt;"",I64&gt;=NOW()),"Planned",IF(AND(J64&lt;&gt;"",J64&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L64" s="71">
         <v>4</v>
       </c>
-      <c r="M64" s="72"/>
-      <c r="N64" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="O64" s="71"/>
+      <c r="M64" s="71"/>
+      <c r="N64" s="70">
+        <f>IF(ISBLANK(L64), "", L64*VLOOKUP($F64,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O64" s="70" t="str">
+        <f>IF(ISBLANK(M64), "", M64*VLOOKUP($F64,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P64" s="53" t="s">
-        <v>289</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="68">
         <v>55</v>
       </c>
-      <c r="C65" s="69" t="s">
-        <v>332</v>
+      <c r="C65" s="69" t="str">
+        <f>IF(ISBLANK(D65), "", _xlfn.CONCAT("T", TEXT(B65, "0000"), "/", VLOOKUP(D65, Internal!$B$35:C$39, 2, FALSE), IF(OR(D65="QA", D65="Revision"), _xlfn.CONCAT("/", H65), "")))</f>
+        <v>T0055/QA/T0020/D</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E65" s="53" t="s">
         <v>47</v>
       </c>
       <c r="F65" s="53" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="G65" s="53" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="H65" s="53" t="s">
-        <v>331</v>
-      </c>
-      <c r="I65" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="J65" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="K65" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L65" s="72">
-        <v>1</v>
-      </c>
-      <c r="M65" s="72"/>
-      <c r="N65" s="71" t="s">
-        <v>282</v>
-      </c>
-      <c r="O65" s="71"/>
+        <v>119</v>
+      </c>
+      <c r="I65" s="108">
+        <v>45772</v>
+      </c>
+      <c r="J65" s="101">
+        <v>45775</v>
+      </c>
+      <c r="K65" s="70" t="str">
+        <f ca="1">IF(OR(I65="",J65=""),"",IF(AND(J65&lt;&gt;"",I65&gt;=NOW()),"Planned",IF(AND(J65&lt;&gt;"",J65&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L65" s="71">
+        <v>4</v>
+      </c>
+      <c r="M65" s="71"/>
+      <c r="N65" s="70">
+        <f>IF(ISBLANK(L65), "", L65*VLOOKUP($F65,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O65" s="70" t="str">
+        <f>IF(ISBLANK(M65), "", M65*VLOOKUP($F65,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P65" s="53" t="s">
-        <v>290</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="68">
         <v>56</v>
       </c>
-      <c r="C66" s="69" t="s">
-        <v>333</v>
+      <c r="C66" s="69" t="str">
+        <f>IF(ISBLANK(D66), "", _xlfn.CONCAT("T", TEXT(B66, "0000"), "/", VLOOKUP(D66, Internal!$B$35:C$39, 2, FALSE), IF(OR(D66="QA", D66="Revision"), _xlfn.CONCAT("/", H66), "")))</f>
+        <v>T0056/QA/T0019/D</v>
       </c>
       <c r="D66" s="53" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="E66" s="53" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F66" s="53" t="s">
         <v>60</v>
       </c>
       <c r="G66" s="53" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="H66" s="53" t="s">
-        <v>332</v>
-      </c>
-      <c r="I66" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="J66" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="K66" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L66" s="72">
-        <v>1</v>
-      </c>
-      <c r="M66" s="72"/>
-      <c r="N66" s="71" t="s">
-        <v>282</v>
-      </c>
-      <c r="O66" s="71"/>
+        <v>118</v>
+      </c>
+      <c r="I66" s="108">
+        <v>45772</v>
+      </c>
+      <c r="J66" s="101">
+        <v>45775</v>
+      </c>
+      <c r="K66" s="70" t="str">
+        <f ca="1">IF(OR(I66="",J66=""),"",IF(AND(J66&lt;&gt;"",I66&gt;=NOW()),"Planned",IF(AND(J66&lt;&gt;"",J66&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L66" s="71">
+        <v>4</v>
+      </c>
+      <c r="M66" s="71"/>
+      <c r="N66" s="70">
+        <f>IF(ISBLANK(L66), "", L66*VLOOKUP($F66,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O66" s="70" t="str">
+        <f>IF(ISBLANK(M66), "", M66*VLOOKUP($F66,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P66" s="53" t="s">
-        <v>291</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="68">
         <v>57</v>
       </c>
-      <c r="C67" s="69" t="s">
-        <v>295</v>
+      <c r="C67" s="69" t="str">
+        <f>IF(ISBLANK(D67), "", _xlfn.CONCAT("T", TEXT(B67, "0000"), "/", VLOOKUP(D67, Internal!$B$35:C$39, 2, FALSE), IF(OR(D67="QA", D67="Revision"), _xlfn.CONCAT("/", H67), "")))</f>
+        <v>T0057/QA/T0020/D</v>
       </c>
       <c r="D67" s="53" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E67" s="53" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F67" s="53" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G67" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H67" s="53"/>
-      <c r="I67" s="70" t="s">
-        <v>292</v>
-      </c>
-      <c r="J67" s="70" t="s">
-        <v>293</v>
-      </c>
-      <c r="K67" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L67" s="72">
-        <v>1.8</v>
-      </c>
-      <c r="M67" s="72"/>
-      <c r="N67" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O67" s="71"/>
+        <v>61</v>
+      </c>
+      <c r="H67" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="I67" s="108">
+        <v>45772</v>
+      </c>
+      <c r="J67" s="101">
+        <v>45775</v>
+      </c>
+      <c r="K67" s="70" t="str">
+        <f ca="1">IF(OR(I67="",J67=""),"",IF(AND(J67&lt;&gt;"",I67&gt;=NOW()),"Planned",IF(AND(J67&lt;&gt;"",J67&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L67" s="71">
+        <v>4</v>
+      </c>
+      <c r="M67" s="71"/>
+      <c r="N67" s="70">
+        <f>IF(ISBLANK(L67), "", L67*VLOOKUP($F67,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O67" s="70" t="str">
+        <f>IF(ISBLANK(M67), "", M67*VLOOKUP($F67,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P67" s="53" t="s">
-        <v>46</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="68">
         <v>58</v>
       </c>
-      <c r="C68" s="69" t="s">
-        <v>296</v>
+      <c r="C68" s="69" t="str">
+        <f>IF(ISBLANK(D68), "", _xlfn.CONCAT("T", TEXT(B68, "0000"), "/", VLOOKUP(D68, Internal!$B$35:C$39, 2, FALSE), IF(OR(D68="QA", D68="Revision"), _xlfn.CONCAT("/", H68), "")))</f>
+        <v>T0058/QA/T0023/D</v>
       </c>
       <c r="D68" s="53" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E68" s="53" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F68" s="53" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G68" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H68" s="53"/>
-      <c r="I68" s="70">
-        <v>45720.729166666664</v>
-      </c>
-      <c r="J68" s="70">
-        <v>45720.8125</v>
-      </c>
-      <c r="K68" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L68" s="72">
-        <v>1.8</v>
-      </c>
-      <c r="M68" s="72"/>
-      <c r="N68" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O68" s="71"/>
+        <v>61</v>
+      </c>
+      <c r="H68" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="I68" s="108">
+        <v>45772</v>
+      </c>
+      <c r="J68" s="101">
+        <v>45775</v>
+      </c>
+      <c r="K68" s="70" t="str">
+        <f ca="1">IF(OR(I68="",J68=""),"",IF(AND(J68&lt;&gt;"",I68&gt;=NOW()),"Planned",IF(AND(J68&lt;&gt;"",J68&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L68" s="71">
+        <v>4</v>
+      </c>
+      <c r="M68" s="71"/>
+      <c r="N68" s="70">
+        <f>IF(ISBLANK(L68), "", L68*VLOOKUP($F68,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O68" s="70" t="str">
+        <f>IF(ISBLANK(M68), "", M68*VLOOKUP($F68,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P68" s="53" t="s">
-        <v>46</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B69" s="68">
         <v>59</v>
       </c>
-      <c r="C69" s="69" t="s">
-        <v>299</v>
+      <c r="C69" s="69" t="str">
+        <f>IF(ISBLANK(D69), "", _xlfn.CONCAT("T", TEXT(B69, "0000"), "/", VLOOKUP(D69, Internal!$B$35:C$39, 2, FALSE), IF(OR(D69="QA", D69="Revision"), _xlfn.CONCAT("/", H69), "")))</f>
+        <v>T0059/D</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E69" s="53" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F69" s="53" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="G69" s="53" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="H69" s="53"/>
-      <c r="I69" s="70">
-        <v>45842.645833333336</v>
-      </c>
-      <c r="J69" s="70">
-        <v>45842.729166666664</v>
-      </c>
-      <c r="K69" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L69" s="72">
-        <v>1.8</v>
-      </c>
-      <c r="M69" s="72"/>
-      <c r="N69" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O69" s="71"/>
+      <c r="I69" s="108">
+        <v>45775</v>
+      </c>
+      <c r="J69" s="101">
+        <v>45775</v>
+      </c>
+      <c r="K69" s="70" t="str">
+        <f ca="1">IF(OR(I69="",J69=""),"",IF(AND(J69&lt;&gt;"",I69&gt;=NOW()),"Planned",IF(AND(J69&lt;&gt;"",J69&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L69" s="71">
+        <v>2</v>
+      </c>
+      <c r="M69" s="71"/>
+      <c r="N69" s="70">
+        <f>IF(ISBLANK(L69), "", L69*VLOOKUP($F69,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>60</v>
+      </c>
+      <c r="O69" s="70" t="str">
+        <f>IF(ISBLANK(M69), "", M69*VLOOKUP($F69,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P69" s="53" t="s">
-        <v>46</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="68">
         <v>60</v>
       </c>
-      <c r="C70" s="69" t="s">
-        <v>302</v>
+      <c r="C70" s="69" t="str">
+        <f>IF(ISBLANK(D70), "", _xlfn.CONCAT("T", TEXT(B70, "0000"), "/", VLOOKUP(D70, Internal!$B$35:C$39, 2, FALSE), IF(OR(D70="QA", D70="Revision"), _xlfn.CONCAT("/", H70), "")))</f>
+        <v>T0060/O</v>
       </c>
       <c r="D70" s="53" t="s">
         <v>39</v>
@@ -10207,36 +10340,42 @@
         <v>40</v>
       </c>
       <c r="G70" s="53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H70" s="53"/>
-      <c r="I70" s="70">
-        <v>45934.729166666664</v>
-      </c>
-      <c r="J70" s="70">
-        <v>45934.8125</v>
-      </c>
-      <c r="K70" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L70" s="72">
-        <v>1.8</v>
-      </c>
-      <c r="M70" s="72"/>
-      <c r="N70" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O70" s="71"/>
+      <c r="I70" s="108">
+        <v>45775.625</v>
+      </c>
+      <c r="J70" s="101">
+        <v>45775.645833333299</v>
+      </c>
+      <c r="K70" s="70" t="str">
+        <f ca="1">IF(OR(I70="",J70=""),"",IF(AND(J70&lt;&gt;"",I70&gt;=NOW()),"Planned",IF(AND(J70&lt;&gt;"",J70&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L70" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="M70" s="71"/>
+      <c r="N70" s="70">
+        <f>IF(ISBLANK(L70), "", L70*VLOOKUP($F70,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O70" s="70" t="str">
+        <f>IF(ISBLANK(M70), "", M70*VLOOKUP($F70,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P70" s="53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="68">
         <v>61</v>
       </c>
-      <c r="C71" s="69" t="s">
-        <v>305</v>
+      <c r="C71" s="69" t="str">
+        <f>IF(ISBLANK(D71), "", _xlfn.CONCAT("T", TEXT(B71, "0000"), "/", VLOOKUP(D71, Internal!$B$35:C$39, 2, FALSE), IF(OR(D71="QA", D71="Revision"), _xlfn.CONCAT("/", H71), "")))</f>
+        <v>T0061/O</v>
       </c>
       <c r="D71" s="53" t="s">
         <v>39</v>
@@ -10251,23 +10390,28 @@
         <v>45</v>
       </c>
       <c r="H71" s="53"/>
-      <c r="I71" s="70" t="s">
-        <v>297</v>
-      </c>
-      <c r="J71" s="70" t="s">
-        <v>298</v>
-      </c>
-      <c r="K71" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L71" s="72">
+      <c r="I71" s="108">
+        <v>45775.645833333299</v>
+      </c>
+      <c r="J71" s="101">
+        <v>45775.729166666701</v>
+      </c>
+      <c r="K71" s="70" t="str">
+        <f ca="1">IF(OR(I71="",J71=""),"",IF(AND(J71&lt;&gt;"",I71&gt;=NOW()),"Planned",IF(AND(J71&lt;&gt;"",J71&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L71" s="71">
         <v>1.8</v>
       </c>
-      <c r="M71" s="72"/>
-      <c r="N71" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O71" s="71"/>
+      <c r="M71" s="71"/>
+      <c r="N71" s="70">
+        <f>IF(ISBLANK(L71), "", L71*VLOOKUP($F71,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="O71" s="70" t="str">
+        <f>IF(ISBLANK(M71), "", M71*VLOOKUP($F71,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P71" s="53" t="s">
         <v>46</v>
       </c>
@@ -10276,696 +10420,1206 @@
       <c r="B72" s="68">
         <v>62</v>
       </c>
-      <c r="C72" s="69" t="s">
-        <v>308</v>
+      <c r="C72" s="69" t="str">
+        <f>IF(ISBLANK(D72), "", _xlfn.CONCAT("T", TEXT(B72, "0000"), "/", VLOOKUP(D72, Internal!$B$35:C$39, 2, FALSE), IF(OR(D72="QA", D72="Revision"), _xlfn.CONCAT("/", H72), "")))</f>
+        <v>T0062/D</v>
       </c>
       <c r="D72" s="53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E72" s="53" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F72" s="53" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="G72" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H72" s="53"/>
-      <c r="I72" s="70" t="s">
-        <v>300</v>
-      </c>
-      <c r="J72" s="70" t="s">
-        <v>301</v>
-      </c>
-      <c r="K72" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L72" s="72">
-        <v>1.8</v>
-      </c>
-      <c r="M72" s="72"/>
-      <c r="N72" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O72" s="71"/>
+        <v>125</v>
+      </c>
+      <c r="H72" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="I72" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J72" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K72" s="70" t="str">
+        <f ca="1">IF(OR(I72="",J72=""),"",IF(AND(J72&lt;&gt;"",I72&gt;=NOW()),"Planned",IF(AND(J72&lt;&gt;"",J72&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L72" s="71">
+        <v>1</v>
+      </c>
+      <c r="M72" s="71"/>
+      <c r="N72" s="70">
+        <f>IF(ISBLANK(L72), "", L72*VLOOKUP($F72,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>30</v>
+      </c>
+      <c r="O72" s="70" t="str">
+        <f>IF(ISBLANK(M72), "", M72*VLOOKUP($F72,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P72" s="53" t="s">
-        <v>46</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="68">
         <v>63</v>
       </c>
-      <c r="C73" s="69" t="s">
-        <v>311</v>
+      <c r="C73" s="69" t="str">
+        <f>IF(ISBLANK(D73), "", _xlfn.CONCAT("T", TEXT(B73, "0000"), "/", VLOOKUP(D73, Internal!$B$35:C$39, 2, FALSE), IF(OR(D73="QA", D73="Revision"), _xlfn.CONCAT("/", H73), "")))</f>
+        <v>T0063/M</v>
       </c>
       <c r="D73" s="53" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F73" s="53" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="G73" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H73" s="53"/>
-      <c r="I73" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="J73" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="K73" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L73" s="72">
-        <v>1.8</v>
-      </c>
-      <c r="M73" s="72"/>
-      <c r="N73" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O73" s="71"/>
+        <v>127</v>
+      </c>
+      <c r="H73" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="I73" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J73" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K73" s="70" t="str">
+        <f ca="1">IF(OR(I73="",J73=""),"",IF(AND(J73&lt;&gt;"",I73&gt;=NOW()),"Planned",IF(AND(J73&lt;&gt;"",J73&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L73" s="71">
+        <v>4</v>
+      </c>
+      <c r="M73" s="71"/>
+      <c r="N73" s="70">
+        <f>IF(ISBLANK(L73), "", L73*VLOOKUP($F73,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O73" s="70" t="str">
+        <f>IF(ISBLANK(M73), "", M73*VLOOKUP($F73,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P73" s="53" t="s">
-        <v>46</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="68">
         <v>64</v>
       </c>
-      <c r="C74" s="69" t="s">
-        <v>314</v>
+      <c r="C74" s="69" t="str">
+        <f>IF(ISBLANK(D74), "", _xlfn.CONCAT("T", TEXT(B74, "0000"), "/", VLOOKUP(D74, Internal!$B$35:C$39, 2, FALSE), IF(OR(D74="QA", D74="Revision"), _xlfn.CONCAT("/", H74), "")))</f>
+        <v>T0064/D</v>
       </c>
       <c r="D74" s="53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E74" s="53" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F74" s="53" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="G74" s="53" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="H74" s="53"/>
-      <c r="I74" s="70" t="s">
-        <v>306</v>
-      </c>
-      <c r="J74" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="K74" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L74" s="72">
-        <v>1.8</v>
-      </c>
-      <c r="M74" s="72"/>
-      <c r="N74" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O74" s="71"/>
+      <c r="I74" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J74" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K74" s="70" t="str">
+        <f ca="1">IF(OR(I74="",J74=""),"",IF(AND(J74&lt;&gt;"",I74&gt;=NOW()),"Planned",IF(AND(J74&lt;&gt;"",J74&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L74" s="71">
+        <v>1</v>
+      </c>
+      <c r="M74" s="71"/>
+      <c r="N74" s="70">
+        <f>IF(ISBLANK(L74), "", L74*VLOOKUP($F74,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>30</v>
+      </c>
+      <c r="O74" s="70" t="str">
+        <f>IF(ISBLANK(M74), "", M74*VLOOKUP($F74,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P74" s="53" t="s">
-        <v>46</v>
+        <v>229</v>
       </c>
     </row>
     <row r="75" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B75" s="68">
         <v>65</v>
       </c>
-      <c r="C75" s="69" t="s">
-        <v>316</v>
+      <c r="C75" s="69" t="str">
+        <f>IF(ISBLANK(D75), "", _xlfn.CONCAT("T", TEXT(B75, "0000"), "/", VLOOKUP(D75, Internal!$B$35:C$39, 2, FALSE), IF(OR(D75="QA", D75="Revision"), _xlfn.CONCAT("/", H75), "")))</f>
+        <v>T0065/R/T0064/D</v>
       </c>
       <c r="D75" s="53" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="E75" s="53" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F75" s="53" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G75" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H75" s="53"/>
-      <c r="I75" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="J75" s="70" t="s">
-        <v>310</v>
-      </c>
-      <c r="K75" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L75" s="72">
-        <v>1.8</v>
-      </c>
-      <c r="M75" s="72"/>
-      <c r="N75" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O75" s="71"/>
+        <v>133</v>
+      </c>
+      <c r="H75" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="I75" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J75" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K75" s="70" t="str">
+        <f ca="1">IF(OR(I75="",J75=""),"",IF(AND(J75&lt;&gt;"",I75&gt;=NOW()),"Planned",IF(AND(J75&lt;&gt;"",J75&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L75" s="71">
+        <v>4</v>
+      </c>
+      <c r="M75" s="71"/>
+      <c r="N75" s="70">
+        <f>IF(ISBLANK(L75), "", L75*VLOOKUP($F75,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O75" s="70" t="str">
+        <f>IF(ISBLANK(M75), "", M75*VLOOKUP($F75,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P75" s="53" t="s">
-        <v>46</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="68">
         <v>66</v>
       </c>
-      <c r="C76" s="69" t="s">
-        <v>317</v>
+      <c r="C76" s="69" t="str">
+        <f>IF(ISBLANK(D76), "", _xlfn.CONCAT("T", TEXT(B76, "0000"), "/", VLOOKUP(D76, Internal!$B$35:C$39, 2, FALSE), IF(OR(D76="QA", D76="Revision"), _xlfn.CONCAT("/", H76), "")))</f>
+        <v>T0066/R/T0064/D</v>
       </c>
       <c r="D76" s="53" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="E76" s="53" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F76" s="53" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G76" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="H76" s="53"/>
-      <c r="I76" s="70" t="s">
-        <v>312</v>
-      </c>
-      <c r="J76" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="K76" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L76" s="72">
-        <v>20</v>
-      </c>
-      <c r="M76" s="72"/>
-      <c r="N76" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O76" s="71"/>
+        <v>136</v>
+      </c>
+      <c r="H76" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="I76" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J76" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K76" s="70" t="str">
+        <f ca="1">IF(OR(I76="",J76=""),"",IF(AND(J76&lt;&gt;"",I76&gt;=NOW()),"Planned",IF(AND(J76&lt;&gt;"",J76&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L76" s="71">
+        <v>4</v>
+      </c>
+      <c r="M76" s="71"/>
+      <c r="N76" s="70">
+        <f>IF(ISBLANK(L76), "", L76*VLOOKUP($F76,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>200</v>
+      </c>
+      <c r="O76" s="70" t="str">
+        <f>IF(ISBLANK(M76), "", M76*VLOOKUP($F76,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P76" s="53" t="s">
-        <v>313</v>
+        <v>231</v>
       </c>
     </row>
     <row r="77" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B77" s="68">
         <v>67</v>
       </c>
-      <c r="C77" s="69" t="s">
-        <v>319</v>
+      <c r="C77" s="69" t="str">
+        <f>IF(ISBLANK(D77), "", _xlfn.CONCAT("T", TEXT(B77, "0000"), "/", VLOOKUP(D77, Internal!$B$35:C$39, 2, FALSE), IF(OR(D77="QA", D77="Revision"), _xlfn.CONCAT("/", H77), "")))</f>
+        <v>T0067/M</v>
       </c>
       <c r="D77" s="53" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E77" s="53" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F77" s="53" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="G77" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="H77" s="53"/>
-      <c r="I77" s="70" t="s">
-        <v>315</v>
-      </c>
-      <c r="J77" s="70" t="s">
-        <v>292</v>
-      </c>
-      <c r="K77" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L77" s="72">
-        <v>0.5</v>
-      </c>
-      <c r="M77" s="72"/>
-      <c r="N77" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O77" s="71"/>
+        <v>138</v>
+      </c>
+      <c r="H77" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="I77" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J77" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K77" s="70" t="str">
+        <f ca="1">IF(OR(I77="",J77=""),"",IF(AND(J77&lt;&gt;"",I77&gt;=NOW()),"Planned",IF(AND(J77&lt;&gt;"",J77&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L77" s="71">
+        <v>1</v>
+      </c>
+      <c r="M77" s="71"/>
+      <c r="N77" s="70">
+        <f>IF(ISBLANK(L77), "", L77*VLOOKUP($F77,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>30</v>
+      </c>
+      <c r="O77" s="70" t="str">
+        <f>IF(ISBLANK(M77), "", M77*VLOOKUP($F77,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P77" s="53" t="s">
-        <v>44</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B78" s="68">
         <v>68</v>
       </c>
-      <c r="C78" s="69" t="s">
-        <v>321</v>
+      <c r="C78" s="69" t="str">
+        <f>IF(ISBLANK(D78), "", _xlfn.CONCAT("T", TEXT(B78, "0000"), "/", VLOOKUP(D78, Internal!$B$35:C$39, 2, FALSE), IF(OR(D78="QA", D78="Revision"), _xlfn.CONCAT("/", H78), "")))</f>
+        <v>T0068/R/T0067/M</v>
       </c>
       <c r="D78" s="53" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="E78" s="53" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F78" s="53" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G78" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="H78" s="53"/>
-      <c r="I78" s="70">
-        <v>45842.625</v>
-      </c>
-      <c r="J78" s="70">
-        <v>45842.645833333336</v>
-      </c>
-      <c r="K78" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L78" s="72">
-        <v>0.5</v>
-      </c>
-      <c r="M78" s="72"/>
-      <c r="N78" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O78" s="71"/>
+        <v>140</v>
+      </c>
+      <c r="H78" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="I78" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J78" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K78" s="70" t="str">
+        <f ca="1">IF(OR(I78="",J78=""),"",IF(AND(J78&lt;&gt;"",I78&gt;=NOW()),"Planned",IF(AND(J78&lt;&gt;"",J78&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L78" s="71">
+        <v>1</v>
+      </c>
+      <c r="M78" s="71"/>
+      <c r="N78" s="70">
+        <f>IF(ISBLANK(L78), "", L78*VLOOKUP($F78,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>30</v>
+      </c>
+      <c r="O78" s="70" t="str">
+        <f>IF(ISBLANK(M78), "", M78*VLOOKUP($F78,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P78" s="53" t="s">
-        <v>44</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="68">
         <v>69</v>
       </c>
-      <c r="C79" s="69" t="s">
-        <v>334</v>
+      <c r="C79" s="69" t="str">
+        <f>IF(ISBLANK(D79), "", _xlfn.CONCAT("T", TEXT(B79, "0000"), "/", VLOOKUP(D79, Internal!$B$35:C$39, 2, FALSE), IF(OR(D79="QA", D79="Revision"), _xlfn.CONCAT("/", H79), "")))</f>
+        <v>T0069/M</v>
       </c>
       <c r="D79" s="53" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E79" s="53" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F79" s="53" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G79" s="53" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H79" s="53"/>
-      <c r="I79" s="70" t="s">
-        <v>318</v>
-      </c>
-      <c r="J79" s="70" t="s">
-        <v>297</v>
-      </c>
-      <c r="K79" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L79" s="72">
-        <v>0.5</v>
-      </c>
-      <c r="M79" s="72"/>
-      <c r="N79" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O79" s="71"/>
+      <c r="I79" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J79" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K79" s="70" t="str">
+        <f ca="1">IF(OR(I79="",J79=""),"",IF(AND(J79&lt;&gt;"",I79&gt;=NOW()),"Planned",IF(AND(J79&lt;&gt;"",J79&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L79" s="71">
+        <v>2</v>
+      </c>
+      <c r="M79" s="71"/>
+      <c r="N79" s="70">
+        <f>IF(ISBLANK(L79), "", L79*VLOOKUP($F79,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O79" s="70" t="str">
+        <f>IF(ISBLANK(M79), "", M79*VLOOKUP($F79,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P79" s="53" t="s">
-        <v>44</v>
+        <v>235</v>
       </c>
     </row>
     <row r="80" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="68">
         <v>70</v>
       </c>
-      <c r="C80" s="69" t="s">
-        <v>335</v>
+      <c r="C80" s="69" t="str">
+        <f>IF(ISBLANK(D80), "", _xlfn.CONCAT("T", TEXT(B80, "0000"), "/", VLOOKUP(D80, Internal!$B$35:C$39, 2, FALSE), IF(OR(D80="QA", D80="Revision"), _xlfn.CONCAT("/", H80), "")))</f>
+        <v>T0070/M</v>
       </c>
       <c r="D80" s="53" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E80" s="53" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F80" s="53" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G80" s="53" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H80" s="53"/>
-      <c r="I80" s="70" t="s">
-        <v>320</v>
-      </c>
-      <c r="J80" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="K80" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L80" s="72">
-        <v>0.5</v>
-      </c>
-      <c r="M80" s="72"/>
-      <c r="N80" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O80" s="71"/>
+      <c r="I80" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J80" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K80" s="70" t="str">
+        <f ca="1">IF(OR(I80="",J80=""),"",IF(AND(J80&lt;&gt;"",I80&gt;=NOW()),"Planned",IF(AND(J80&lt;&gt;"",J80&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L80" s="71">
+        <v>2</v>
+      </c>
+      <c r="M80" s="71"/>
+      <c r="N80" s="70">
+        <f>IF(ISBLANK(L80), "", L80*VLOOKUP($F80,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O80" s="70" t="str">
+        <f>IF(ISBLANK(M80), "", M80*VLOOKUP($F80,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P80" s="53" t="s">
-        <v>44</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="68">
         <v>71</v>
       </c>
-      <c r="C81" s="69" t="s">
-        <v>336</v>
+      <c r="C81" s="69" t="str">
+        <f>IF(ISBLANK(D81), "", _xlfn.CONCAT("T", TEXT(B81, "0000"), "/", VLOOKUP(D81, Internal!$B$35:C$39, 2, FALSE), IF(OR(D81="QA", D81="Revision"), _xlfn.CONCAT("/", H81), "")))</f>
+        <v>T0071/M</v>
       </c>
       <c r="D81" s="53" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E81" s="53" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F81" s="53" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G81" s="53" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H81" s="53"/>
-      <c r="I81" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="J81" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="K81" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="L81" s="72">
-        <v>0.5</v>
-      </c>
-      <c r="M81" s="72"/>
-      <c r="N81" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="O81" s="71"/>
+      <c r="I81" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J81" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K81" s="70" t="str">
+        <f ca="1">IF(OR(I81="",J81=""),"",IF(AND(J81&lt;&gt;"",I81&gt;=NOW()),"Planned",IF(AND(J81&lt;&gt;"",J81&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L81" s="71">
+        <v>2</v>
+      </c>
+      <c r="M81" s="71"/>
+      <c r="N81" s="70">
+        <f>IF(ISBLANK(L81), "", L81*VLOOKUP($F81,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O81" s="70" t="str">
+        <f>IF(ISBLANK(M81), "", M81*VLOOKUP($F81,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
       <c r="P81" s="53" t="s">
-        <v>44</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="68">
-        <v>69</v>
-      </c>
-      <c r="C82" s="69"/>
-      <c r="D82" s="53"/>
-      <c r="E82" s="53"/>
-      <c r="F82" s="53"/>
-      <c r="G82" s="53"/>
+        <v>72</v>
+      </c>
+      <c r="C82" s="69" t="str">
+        <f>IF(ISBLANK(D82),"",_xlfn.CONCAT("T",TEXT(B82,"0000"),"/",VLOOKUP(D82,Internal!$B$35:C$39,2,FALSE),IF(OR(D82="QA",D82="Revision"),_xlfn.CONCAT("/",H82),"")))</f>
+        <v>T0072/D</v>
+      </c>
+      <c r="D82" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E82" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G82" s="53" t="s">
+        <v>24</v>
+      </c>
       <c r="H82" s="53"/>
-      <c r="I82" s="70"/>
-      <c r="J82" s="70"/>
-      <c r="K82" s="71"/>
-      <c r="L82" s="72"/>
-      <c r="M82" s="72"/>
-      <c r="N82" s="71"/>
-      <c r="O82" s="71"/>
-      <c r="P82" s="53"/>
+      <c r="I82" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J82" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K82" s="70" t="str">
+        <f ca="1">IF(OR(I82="",J82=""),"",IF(AND(J82&lt;&gt;"",I82&gt;=NOW()),"Planned",IF(AND(J82&lt;&gt;"",J82&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L82" s="71">
+        <v>4</v>
+      </c>
+      <c r="M82" s="71"/>
+      <c r="N82" s="70">
+        <f>IF(ISBLANK(L82),"",L82*VLOOKUP($F82,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O82" s="70" t="str">
+        <f>IF(ISBLANK(M82),"",M82*VLOOKUP($F82,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P82" s="53" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="83" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B83" s="68">
-        <v>70</v>
-      </c>
-      <c r="C83" s="69"/>
-      <c r="D83" s="53"/>
-      <c r="E83" s="53"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53"/>
+        <v>73</v>
+      </c>
+      <c r="C83" s="69" t="str">
+        <f>IF(ISBLANK(D83),"",_xlfn.CONCAT("T",TEXT(B83,"0000"),"/",VLOOKUP(D83,Internal!$B$35:C$39,2,FALSE),IF(OR(D83="QA",D83="Revision"),_xlfn.CONCAT("/",H83),"")))</f>
+        <v>T0073/M</v>
+      </c>
+      <c r="D83" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F83" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G83" s="53" t="s">
+        <v>24</v>
+      </c>
       <c r="H83" s="53"/>
-      <c r="I83" s="70"/>
-      <c r="J83" s="70"/>
-      <c r="K83" s="71"/>
-      <c r="L83" s="72"/>
-      <c r="M83" s="72"/>
-      <c r="N83" s="71"/>
-      <c r="O83" s="71"/>
-      <c r="P83" s="53"/>
+      <c r="I83" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J83" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K83" s="70" t="str">
+        <f ca="1">IF(OR(I83="",J83=""),"",IF(AND(J83&lt;&gt;"",I83&gt;=NOW()),"Planned",IF(AND(J83&lt;&gt;"",J83&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L83" s="71">
+        <v>2</v>
+      </c>
+      <c r="M83" s="71"/>
+      <c r="N83" s="70">
+        <f>IF(ISBLANK(L83),"",L83*VLOOKUP($F83,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O83" s="70" t="str">
+        <f>IF(ISBLANK(M83),"",M83*VLOOKUP($F83,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P83" s="53" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="84" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B84" s="68">
-        <v>71</v>
-      </c>
-      <c r="C84" s="69"/>
-      <c r="D84" s="53"/>
-      <c r="E84" s="53"/>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53"/>
+        <v>74</v>
+      </c>
+      <c r="C84" s="69" t="str">
+        <f>IF(ISBLANK(D84),"",_xlfn.CONCAT("T",TEXT(B84,"0000"),"/",VLOOKUP(D84,Internal!$B$35:C$39,2,FALSE),IF(OR(D84="QA",D84="Revision"),_xlfn.CONCAT("/",H84),"")))</f>
+        <v>T0074/M</v>
+      </c>
+      <c r="D84" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E84" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F84" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="53" t="s">
+        <v>28</v>
+      </c>
       <c r="H84" s="53"/>
-      <c r="I84" s="70"/>
-      <c r="J84" s="70"/>
-      <c r="K84" s="71"/>
-      <c r="L84" s="72"/>
-      <c r="M84" s="72"/>
-      <c r="N84" s="71"/>
-      <c r="O84" s="71"/>
-      <c r="P84" s="53"/>
+      <c r="I84" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J84" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K84" s="70" t="str">
+        <f ca="1">IF(OR(I84="",J84=""),"",IF(AND(J84&lt;&gt;"",I84&gt;=NOW()),"Planned",IF(AND(J84&lt;&gt;"",J84&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L84" s="71">
+        <v>2</v>
+      </c>
+      <c r="M84" s="71"/>
+      <c r="N84" s="70">
+        <f>IF(ISBLANK(L84),"",L84*VLOOKUP($F84,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O84" s="70" t="str">
+        <f>IF(ISBLANK(M84),"",M84*VLOOKUP($F84,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P84" s="53" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="85" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B85" s="68">
-        <v>72</v>
-      </c>
-      <c r="C85" s="69"/>
-      <c r="D85" s="53"/>
-      <c r="E85" s="53"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
-      <c r="H85" s="53"/>
-      <c r="I85" s="70"/>
-      <c r="J85" s="70"/>
-      <c r="K85" s="71"/>
-      <c r="L85" s="72"/>
-      <c r="M85" s="72"/>
-      <c r="N85" s="71"/>
-      <c r="O85" s="71"/>
-      <c r="P85" s="53"/>
+        <v>75</v>
+      </c>
+      <c r="C85" s="69" t="str">
+        <f>IF(ISBLANK(D85),"",_xlfn.CONCAT("T",TEXT(B85,"0000"),"/",VLOOKUP(D85,Internal!$B$35:C$39,2,FALSE),IF(OR(D85="QA",D85="Revision"),_xlfn.CONCAT("/",H85),"")))</f>
+        <v>T0075/QA/T0035/D</v>
+      </c>
+      <c r="D85" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E85" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F85" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G85" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="H85" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="I85" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J85" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K85" s="70" t="str">
+        <f ca="1">IF(OR(I85="",J85=""),"",IF(AND(J85&lt;&gt;"",I85&gt;=NOW()),"Planned",IF(AND(J85&lt;&gt;"",J85&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L85" s="71">
+        <v>4</v>
+      </c>
+      <c r="M85" s="71"/>
+      <c r="N85" s="70">
+        <f>IF(ISBLANK(L85),"",L85*VLOOKUP($F85,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O85" s="70" t="str">
+        <f>IF(ISBLANK(M85),"",M85*VLOOKUP($F85,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P85" s="53" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="86" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B86" s="68">
-        <v>73</v>
-      </c>
-      <c r="C86" s="69"/>
-      <c r="D86" s="53"/>
-      <c r="E86" s="53"/>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53"/>
-      <c r="H86" s="53"/>
-      <c r="I86" s="70"/>
-      <c r="J86" s="70"/>
-      <c r="K86" s="71"/>
-      <c r="L86" s="72"/>
-      <c r="M86" s="72"/>
-      <c r="N86" s="71"/>
-      <c r="O86" s="71"/>
-      <c r="P86" s="53"/>
+        <v>76</v>
+      </c>
+      <c r="C86" s="69" t="str">
+        <f>IF(ISBLANK(D86),"",_xlfn.CONCAT("T",TEXT(B86,"0000"),"/",VLOOKUP(D86,Internal!$B$35:C$39,2,FALSE),IF(OR(D86="QA",D86="Revision"),_xlfn.CONCAT("/",H86),"")))</f>
+        <v>T0076/QA/T0058/QA/T0023/D</v>
+      </c>
+      <c r="D86" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E86" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F86" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G86" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="H86" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="I86" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J86" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K86" s="70" t="str">
+        <f ca="1">IF(OR(I86="",J86=""),"",IF(AND(J86&lt;&gt;"",I86&gt;=NOW()),"Planned",IF(AND(J86&lt;&gt;"",J86&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L86" s="71">
+        <v>4</v>
+      </c>
+      <c r="M86" s="71"/>
+      <c r="N86" s="70">
+        <f>IF(ISBLANK(L86),"",L86*VLOOKUP($F86,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O86" s="70" t="str">
+        <f>IF(ISBLANK(M86),"",M86*VLOOKUP($F86,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P86" s="53" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="87" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="68">
-        <v>74</v>
-      </c>
-      <c r="C87" s="69"/>
-      <c r="D87" s="53"/>
-      <c r="E87" s="53"/>
-      <c r="F87" s="53"/>
-      <c r="G87" s="53"/>
-      <c r="H87" s="53"/>
-      <c r="I87" s="70"/>
-      <c r="J87" s="70"/>
-      <c r="K87" s="71"/>
-      <c r="L87" s="72"/>
-      <c r="M87" s="72"/>
-      <c r="N87" s="71"/>
-      <c r="O87" s="71"/>
-      <c r="P87" s="53"/>
+        <v>77</v>
+      </c>
+      <c r="C87" s="69" t="str">
+        <f>IF(ISBLANK(D87),"",_xlfn.CONCAT("T",TEXT(B87,"0000"),"/",VLOOKUP(D87,Internal!$B$35:C$39,2,FALSE),IF(OR(D87="QA",D87="Revision"),_xlfn.CONCAT("/",H87),"")))</f>
+        <v>T0077/QA/T0076/QA/T0058/QA/T0023/D</v>
+      </c>
+      <c r="D87" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E87" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F87" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G87" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="H87" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="I87" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J87" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K87" s="70" t="str">
+        <f ca="1">IF(OR(I87="",J87=""),"",IF(AND(J87&lt;&gt;"",I87&gt;=NOW()),"Planned",IF(AND(J87&lt;&gt;"",J87&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L87" s="71">
+        <v>4</v>
+      </c>
+      <c r="M87" s="71"/>
+      <c r="N87" s="70">
+        <f>IF(ISBLANK(L87),"",L87*VLOOKUP($F87,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O87" s="70" t="str">
+        <f>IF(ISBLANK(M87),"",M87*VLOOKUP($F87,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P87" s="53" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="88" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B88" s="68">
-        <v>75</v>
-      </c>
-      <c r="C88" s="69"/>
-      <c r="D88" s="53"/>
-      <c r="E88" s="53"/>
-      <c r="F88" s="53"/>
-      <c r="G88" s="53"/>
-      <c r="H88" s="53"/>
-      <c r="I88" s="70"/>
-      <c r="J88" s="70"/>
-      <c r="K88" s="71"/>
-      <c r="L88" s="72"/>
-      <c r="M88" s="72"/>
-      <c r="N88" s="71"/>
-      <c r="O88" s="71"/>
-      <c r="P88" s="53"/>
+        <v>78</v>
+      </c>
+      <c r="C88" s="69" t="str">
+        <f>IF(ISBLANK(D88),"",_xlfn.CONCAT("T",TEXT(B88,"0000"),"/",VLOOKUP(D88,Internal!$B$35:C$39,2,FALSE),IF(OR(D88="QA",D88="Revision"),_xlfn.CONCAT("/",H88),"")))</f>
+        <v>T0078/QA/T0077/QA/T0076/QA/T0058/QA/T0023/D</v>
+      </c>
+      <c r="D88" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E88" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="F88" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G88" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="H88" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="I88" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J88" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K88" s="70" t="str">
+        <f ca="1">IF(OR(I88="",J88=""),"",IF(AND(J88&lt;&gt;"",I88&gt;=NOW()),"Planned",IF(AND(J88&lt;&gt;"",J88&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L88" s="71">
+        <v>3</v>
+      </c>
+      <c r="M88" s="71"/>
+      <c r="N88" s="70">
+        <f>IF(ISBLANK(L88),"",L88*VLOOKUP($F88,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>90</v>
+      </c>
+      <c r="O88" s="70" t="str">
+        <f>IF(ISBLANK(M88),"",M88*VLOOKUP($F88,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P88" s="53" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="89" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B89" s="68">
-        <v>76</v>
-      </c>
-      <c r="C89" s="69"/>
-      <c r="D89" s="53"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
-      <c r="H89" s="53"/>
-      <c r="I89" s="70"/>
-      <c r="J89" s="70"/>
-      <c r="K89" s="71"/>
-      <c r="L89" s="72"/>
-      <c r="M89" s="72"/>
-      <c r="N89" s="71"/>
-      <c r="O89" s="71"/>
-      <c r="P89" s="53"/>
+        <v>79</v>
+      </c>
+      <c r="C89" s="69" t="str">
+        <f>IF(ISBLANK(D89),"",_xlfn.CONCAT("T",TEXT(B89,"0000"),"/",VLOOKUP(D89,Internal!$B$35:C$39,2,FALSE),IF(OR(D89="QA",D89="Revision"),_xlfn.CONCAT("/",H89),"")))</f>
+        <v>T0079/QA/T0077/QA/T0076/QA/T0058/QA/T0023/D</v>
+      </c>
+      <c r="D89" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E89" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="F89" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G89" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="H89" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="I89" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J89" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K89" s="70" t="str">
+        <f ca="1">IF(OR(I89="",J89=""),"",IF(AND(J89&lt;&gt;"",I89&gt;=NOW()),"Planned",IF(AND(J89&lt;&gt;"",J89&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L89" s="71">
+        <v>3</v>
+      </c>
+      <c r="M89" s="71"/>
+      <c r="N89" s="70">
+        <f>IF(ISBLANK(L89),"",L89*VLOOKUP($F89,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>90</v>
+      </c>
+      <c r="O89" s="70" t="str">
+        <f>IF(ISBLANK(M89),"",M89*VLOOKUP($F89,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P89" s="53" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="90" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B90" s="68">
-        <v>77</v>
-      </c>
-      <c r="C90" s="69"/>
-      <c r="D90" s="53"/>
-      <c r="E90" s="53"/>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="53"/>
-      <c r="I90" s="70"/>
-      <c r="J90" s="70"/>
-      <c r="K90" s="71"/>
-      <c r="L90" s="72"/>
-      <c r="M90" s="72"/>
-      <c r="N90" s="71"/>
-      <c r="O90" s="71"/>
-      <c r="P90" s="53"/>
+        <v>80</v>
+      </c>
+      <c r="C90" s="69" t="str">
+        <f>IF(ISBLANK(D90),"",_xlfn.CONCAT("T",TEXT(B90,"0000"),"/",VLOOKUP(D90,Internal!$B$35:C$39,2,FALSE),IF(OR(D90="QA",D90="Revision"),_xlfn.CONCAT("/",H90),"")))</f>
+        <v>T0080/QA/T0077/QA/T0076/QA/T0058/QA/T0023/D</v>
+      </c>
+      <c r="D90" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E90" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F90" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G90" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="H90" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="I90" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J90" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K90" s="70" t="str">
+        <f ca="1">IF(OR(I90="",J90=""),"",IF(AND(J90&lt;&gt;"",I90&gt;=NOW()),"Planned",IF(AND(J90&lt;&gt;"",J90&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L90" s="71">
+        <v>4</v>
+      </c>
+      <c r="M90" s="71"/>
+      <c r="N90" s="70">
+        <f>IF(ISBLANK(L90),"",L90*VLOOKUP($F90,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>120</v>
+      </c>
+      <c r="O90" s="70" t="str">
+        <f>IF(ISBLANK(M90),"",M90*VLOOKUP($F90,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P90" s="53" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="91" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B91" s="68">
-        <v>78</v>
-      </c>
-      <c r="C91" s="69"/>
-      <c r="D91" s="53"/>
-      <c r="E91" s="53"/>
-      <c r="F91" s="53"/>
-      <c r="G91" s="53"/>
-      <c r="H91" s="53"/>
-      <c r="I91" s="70"/>
-      <c r="J91" s="70"/>
-      <c r="K91" s="71"/>
-      <c r="L91" s="72"/>
-      <c r="M91" s="72"/>
-      <c r="N91" s="71"/>
-      <c r="O91" s="71"/>
-      <c r="P91" s="53"/>
+        <v>81</v>
+      </c>
+      <c r="C91" s="69" t="str">
+        <f>IF(ISBLANK(D91),"",_xlfn.CONCAT("T",TEXT(B91,"0000"),"/",VLOOKUP(D91,Internal!$B$35:C$39,2,FALSE),IF(OR(D91="QA",D91="Revision"),_xlfn.CONCAT("/",H91),"")))</f>
+        <v>T0081/QA/T0080/QA/T0077/QA/T0076/QA/T0058/QA/T0023/D</v>
+      </c>
+      <c r="D91" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E91" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F91" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G91" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="H91" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="I91" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J91" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K91" s="70" t="str">
+        <f ca="1">IF(OR(I91="",J91=""),"",IF(AND(J91&lt;&gt;"",I91&gt;=NOW()),"Planned",IF(AND(J91&lt;&gt;"",J91&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L91" s="71">
+        <v>3</v>
+      </c>
+      <c r="M91" s="71"/>
+      <c r="N91" s="70">
+        <f>IF(ISBLANK(L91),"",L91*VLOOKUP($F91,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>90</v>
+      </c>
+      <c r="O91" s="70" t="str">
+        <f>IF(ISBLANK(M91),"",M91*VLOOKUP($F91,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P91" s="53" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="92" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="68">
-        <v>79</v>
-      </c>
-      <c r="C92" s="69"/>
-      <c r="D92" s="53"/>
-      <c r="E92" s="53"/>
-      <c r="F92" s="53"/>
-      <c r="G92" s="53"/>
+        <v>82</v>
+      </c>
+      <c r="C92" s="69" t="str">
+        <f>IF(ISBLANK(D92),"",_xlfn.CONCAT("T",TEXT(B92,"0000"),"/",VLOOKUP(D92,Internal!$B$35:C$39,2,FALSE),IF(OR(D92="QA",D92="Revision"),_xlfn.CONCAT("/",H92),"")))</f>
+        <v>T0082/D</v>
+      </c>
+      <c r="D92" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="F92" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G92" s="53" t="s">
+        <v>50</v>
+      </c>
       <c r="H92" s="53"/>
-      <c r="I92" s="70"/>
-      <c r="J92" s="70"/>
-      <c r="K92" s="71"/>
-      <c r="L92" s="72"/>
-      <c r="M92" s="72"/>
-      <c r="N92" s="71"/>
-      <c r="O92" s="71"/>
-      <c r="P92" s="53"/>
+      <c r="I92" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J92" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K92" s="70" t="str">
+        <f ca="1">IF(OR(I92="",J92=""),"",IF(AND(J92&lt;&gt;"",I92&gt;=NOW()),"Planned",IF(AND(J92&lt;&gt;"",J92&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L92" s="71">
+        <v>4</v>
+      </c>
+      <c r="M92" s="71"/>
+      <c r="N92" s="70">
+        <f>IF(ISBLANK(L92),"",L92*VLOOKUP($F92,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O92" s="70" t="str">
+        <f>IF(ISBLANK(M92),"",M92*VLOOKUP($F92,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P92" s="53" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="93" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B93" s="68">
-        <v>80</v>
-      </c>
-      <c r="C93" s="69"/>
-      <c r="D93" s="53"/>
-      <c r="E93" s="53"/>
-      <c r="F93" s="53"/>
-      <c r="G93" s="53"/>
-      <c r="H93" s="53"/>
-      <c r="I93" s="70"/>
-      <c r="J93" s="70"/>
-      <c r="K93" s="71"/>
-      <c r="L93" s="72"/>
-      <c r="M93" s="72"/>
-      <c r="N93" s="71"/>
-      <c r="O93" s="71"/>
-      <c r="P93" s="53"/>
+        <v>83</v>
+      </c>
+      <c r="C93" s="69" t="str">
+        <f>IF(ISBLANK(D93),"",_xlfn.CONCAT("T",TEXT(B93,"0000"),"/",VLOOKUP(D93,Internal!$B$35:C$39,2,FALSE),IF(OR(D93="QA",D93="Revision"),_xlfn.CONCAT("/",H93),"")))</f>
+        <v>T0083/D</v>
+      </c>
+      <c r="D93" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F93" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G93" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="H93" s="53" t="s">
+        <v>258</v>
+      </c>
+      <c r="I93" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J93" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K93" s="70" t="str">
+        <f ca="1">IF(OR(I93="",J93=""),"",IF(AND(J93&lt;&gt;"",I93&gt;=NOW()),"Planned",IF(AND(J93&lt;&gt;"",J93&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L93" s="71">
+        <v>4</v>
+      </c>
+      <c r="M93" s="71"/>
+      <c r="N93" s="70">
+        <f>IF(ISBLANK(L93),"",L93*VLOOKUP($F93,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O93" s="70" t="str">
+        <f>IF(ISBLANK(M93),"",M93*VLOOKUP($F93,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P93" s="53" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="94" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="68">
-        <v>81</v>
-      </c>
-      <c r="C94" s="69"/>
-      <c r="D94" s="53"/>
-      <c r="E94" s="53"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
-      <c r="H94" s="53"/>
-      <c r="I94" s="70"/>
-      <c r="J94" s="70"/>
-      <c r="K94" s="71"/>
-      <c r="L94" s="72"/>
-      <c r="M94" s="72"/>
-      <c r="N94" s="71"/>
-      <c r="O94" s="71"/>
-      <c r="P94" s="53"/>
+        <v>84</v>
+      </c>
+      <c r="C94" s="69" t="str">
+        <f>IF(ISBLANK(D94),"",_xlfn.CONCAT("T",TEXT(B94,"0000"),"/",VLOOKUP(D94,Internal!$B$35:C$39,2,FALSE),IF(OR(D94="QA",D94="Revision"),_xlfn.CONCAT("/",H94),"")))</f>
+        <v>T0084/QA/T0083/D</v>
+      </c>
+      <c r="D94" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="E94" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G94" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="H94" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="I94" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J94" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K94" s="70" t="str">
+        <f ca="1">IF(OR(I94="",J94=""),"",IF(AND(J94&lt;&gt;"",I94&gt;=NOW()),"Planned",IF(AND(J94&lt;&gt;"",J94&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L94" s="71">
+        <v>3</v>
+      </c>
+      <c r="M94" s="71"/>
+      <c r="N94" s="70">
+        <f>IF(ISBLANK(L94),"",L94*VLOOKUP($F94,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>90</v>
+      </c>
+      <c r="O94" s="70" t="str">
+        <f>IF(ISBLANK(M94),"",M94*VLOOKUP($F94,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P94" s="53" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="95" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B95" s="68">
-        <v>82</v>
-      </c>
-      <c r="C95" s="69"/>
-      <c r="D95" s="53"/>
-      <c r="E95" s="53"/>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53"/>
+        <v>85</v>
+      </c>
+      <c r="C95" s="69" t="str">
+        <f>IF(ISBLANK(D95),"",_xlfn.CONCAT("T",TEXT(B95,"0000"),"/",VLOOKUP(D95,Internal!$B$35:C$39,2,FALSE),IF(OR(D95="QA",D95="Revision"),_xlfn.CONCAT("/",H95),"")))</f>
+        <v>T0085/D</v>
+      </c>
+      <c r="D95" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="F95" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G95" s="53" t="s">
+        <v>24</v>
+      </c>
       <c r="H95" s="53"/>
-      <c r="I95" s="70"/>
-      <c r="J95" s="70"/>
-      <c r="K95" s="71"/>
-      <c r="L95" s="72"/>
-      <c r="M95" s="72"/>
-      <c r="N95" s="71"/>
-      <c r="O95" s="71"/>
-      <c r="P95" s="53"/>
+      <c r="I95" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J95" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K95" s="70" t="str">
+        <f ca="1">IF(OR(I95="",J95=""),"",IF(AND(J95&lt;&gt;"",I95&gt;=NOW()),"Planned",IF(AND(J95&lt;&gt;"",J95&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L95" s="71">
+        <v>2</v>
+      </c>
+      <c r="M95" s="71"/>
+      <c r="N95" s="70">
+        <f>IF(ISBLANK(L95),"",L95*VLOOKUP($F95,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>50</v>
+      </c>
+      <c r="O95" s="70" t="str">
+        <f>IF(ISBLANK(M95),"",M95*VLOOKUP($F95,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P95" s="53" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="96" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B96" s="68">
-        <v>83</v>
-      </c>
-      <c r="C96" s="69"/>
-      <c r="D96" s="53"/>
-      <c r="E96" s="53"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="53"/>
+        <v>86</v>
+      </c>
+      <c r="C96" s="69" t="str">
+        <f>IF(ISBLANK(D96),"",_xlfn.CONCAT("T",TEXT(B96,"0000"),"/",VLOOKUP(D96,Internal!$B$35:C$39,2,FALSE),IF(OR(D96="QA",D96="Revision"),_xlfn.CONCAT("/",H96),"")))</f>
+        <v>T0086/M</v>
+      </c>
+      <c r="D96" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F96" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" s="53" t="s">
+        <v>26</v>
+      </c>
       <c r="H96" s="53"/>
-      <c r="I96" s="70"/>
-      <c r="J96" s="70"/>
-      <c r="K96" s="71"/>
-      <c r="L96" s="72"/>
-      <c r="M96" s="72"/>
-      <c r="N96" s="71"/>
-      <c r="O96" s="71"/>
-      <c r="P96" s="53"/>
+      <c r="I96" s="108">
+        <v>45776</v>
+      </c>
+      <c r="J96" s="101">
+        <v>45776</v>
+      </c>
+      <c r="K96" s="70" t="str">
+        <f ca="1">IF(OR(I96="",J96=""),"",IF(AND(J96&lt;&gt;"",I96&gt;=NOW()),"Planned",IF(AND(J96&lt;&gt;"",J96&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L96" s="71">
+        <v>2</v>
+      </c>
+      <c r="M96" s="71"/>
+      <c r="N96" s="70">
+        <f>IF(ISBLANK(L96),"",L96*VLOOKUP($F96,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v>100</v>
+      </c>
+      <c r="O96" s="70" t="str">
+        <f>IF(ISBLANK(M96),"",M96*VLOOKUP($F96,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P96" s="53" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="97" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B97" s="68">
@@ -10977,13 +11631,13 @@
       <c r="F97" s="53"/>
       <c r="G97" s="53"/>
       <c r="H97" s="53"/>
-      <c r="I97" s="70"/>
-      <c r="J97" s="70"/>
-      <c r="K97" s="71"/>
-      <c r="L97" s="72"/>
-      <c r="M97" s="72"/>
-      <c r="N97" s="71"/>
-      <c r="O97" s="71"/>
+      <c r="I97" s="108"/>
+      <c r="J97" s="101"/>
+      <c r="K97" s="70"/>
+      <c r="L97" s="71"/>
+      <c r="M97" s="71"/>
+      <c r="N97" s="70"/>
+      <c r="O97" s="70"/>
       <c r="P97" s="53"/>
     </row>
     <row r="98" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10996,13 +11650,13 @@
       <c r="F98" s="53"/>
       <c r="G98" s="53"/>
       <c r="H98" s="53"/>
-      <c r="I98" s="70"/>
-      <c r="J98" s="70"/>
-      <c r="K98" s="71"/>
-      <c r="L98" s="72"/>
-      <c r="M98" s="72"/>
-      <c r="N98" s="71"/>
-      <c r="O98" s="71"/>
+      <c r="I98" s="108"/>
+      <c r="J98" s="101"/>
+      <c r="K98" s="70"/>
+      <c r="L98" s="71"/>
+      <c r="M98" s="71"/>
+      <c r="N98" s="70"/>
+      <c r="O98" s="70"/>
       <c r="P98" s="53"/>
     </row>
     <row r="99" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11015,13 +11669,13 @@
       <c r="F99" s="53"/>
       <c r="G99" s="53"/>
       <c r="H99" s="53"/>
-      <c r="I99" s="70"/>
-      <c r="J99" s="70"/>
-      <c r="K99" s="71"/>
-      <c r="L99" s="72"/>
-      <c r="M99" s="72"/>
-      <c r="N99" s="71"/>
-      <c r="O99" s="71"/>
+      <c r="I99" s="108"/>
+      <c r="J99" s="101"/>
+      <c r="K99" s="70"/>
+      <c r="L99" s="71"/>
+      <c r="M99" s="71"/>
+      <c r="N99" s="70"/>
+      <c r="O99" s="70"/>
       <c r="P99" s="53"/>
     </row>
     <row r="100" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11034,13 +11688,13 @@
       <c r="F100" s="53"/>
       <c r="G100" s="53"/>
       <c r="H100" s="53"/>
-      <c r="I100" s="70"/>
-      <c r="J100" s="70"/>
-      <c r="K100" s="71"/>
-      <c r="L100" s="72"/>
-      <c r="M100" s="72"/>
-      <c r="N100" s="71"/>
-      <c r="O100" s="71"/>
+      <c r="I100" s="108"/>
+      <c r="J100" s="101"/>
+      <c r="K100" s="70"/>
+      <c r="L100" s="71"/>
+      <c r="M100" s="71"/>
+      <c r="N100" s="70"/>
+      <c r="O100" s="70"/>
       <c r="P100" s="53"/>
     </row>
     <row r="101" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11053,13 +11707,13 @@
       <c r="F101" s="53"/>
       <c r="G101" s="53"/>
       <c r="H101" s="53"/>
-      <c r="I101" s="70"/>
-      <c r="J101" s="70"/>
-      <c r="K101" s="71"/>
-      <c r="L101" s="72"/>
-      <c r="M101" s="72"/>
-      <c r="N101" s="71"/>
-      <c r="O101" s="71"/>
+      <c r="I101" s="108"/>
+      <c r="J101" s="101"/>
+      <c r="K101" s="70"/>
+      <c r="L101" s="71"/>
+      <c r="M101" s="71"/>
+      <c r="N101" s="70"/>
+      <c r="O101" s="70"/>
       <c r="P101" s="53"/>
     </row>
     <row r="102" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11072,13 +11726,13 @@
       <c r="F102" s="53"/>
       <c r="G102" s="53"/>
       <c r="H102" s="53"/>
-      <c r="I102" s="70"/>
-      <c r="J102" s="70"/>
-      <c r="K102" s="71"/>
-      <c r="L102" s="72"/>
-      <c r="M102" s="72"/>
-      <c r="N102" s="71"/>
-      <c r="O102" s="71"/>
+      <c r="I102" s="108"/>
+      <c r="J102" s="101"/>
+      <c r="K102" s="70"/>
+      <c r="L102" s="71"/>
+      <c r="M102" s="71"/>
+      <c r="N102" s="70"/>
+      <c r="O102" s="70"/>
       <c r="P102" s="53"/>
     </row>
     <row r="103" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11091,13 +11745,13 @@
       <c r="F103" s="53"/>
       <c r="G103" s="53"/>
       <c r="H103" s="53"/>
-      <c r="I103" s="70"/>
-      <c r="J103" s="70"/>
-      <c r="K103" s="71"/>
-      <c r="L103" s="72"/>
-      <c r="M103" s="72"/>
-      <c r="N103" s="71"/>
-      <c r="O103" s="71"/>
+      <c r="I103" s="108"/>
+      <c r="J103" s="101"/>
+      <c r="K103" s="70"/>
+      <c r="L103" s="71"/>
+      <c r="M103" s="71"/>
+      <c r="N103" s="70"/>
+      <c r="O103" s="70"/>
       <c r="P103" s="53"/>
     </row>
     <row r="104" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11110,13 +11764,13 @@
       <c r="F104" s="53"/>
       <c r="G104" s="53"/>
       <c r="H104" s="53"/>
-      <c r="I104" s="70"/>
-      <c r="J104" s="70"/>
-      <c r="K104" s="71"/>
-      <c r="L104" s="72"/>
-      <c r="M104" s="72"/>
-      <c r="N104" s="71"/>
-      <c r="O104" s="71"/>
+      <c r="I104" s="108"/>
+      <c r="J104" s="101"/>
+      <c r="K104" s="70"/>
+      <c r="L104" s="71"/>
+      <c r="M104" s="71"/>
+      <c r="N104" s="70"/>
+      <c r="O104" s="70"/>
       <c r="P104" s="53"/>
     </row>
     <row r="105" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11129,13 +11783,13 @@
       <c r="F105" s="53"/>
       <c r="G105" s="53"/>
       <c r="H105" s="53"/>
-      <c r="I105" s="70"/>
-      <c r="J105" s="70"/>
-      <c r="K105" s="71"/>
-      <c r="L105" s="72"/>
-      <c r="M105" s="72"/>
-      <c r="N105" s="71"/>
-      <c r="O105" s="71"/>
+      <c r="I105" s="108"/>
+      <c r="J105" s="101"/>
+      <c r="K105" s="70"/>
+      <c r="L105" s="71"/>
+      <c r="M105" s="71"/>
+      <c r="N105" s="70"/>
+      <c r="O105" s="70"/>
       <c r="P105" s="53"/>
     </row>
     <row r="106" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11148,13 +11802,13 @@
       <c r="F106" s="53"/>
       <c r="G106" s="53"/>
       <c r="H106" s="53"/>
-      <c r="I106" s="70"/>
-      <c r="J106" s="70"/>
-      <c r="K106" s="71"/>
-      <c r="L106" s="72"/>
-      <c r="M106" s="72"/>
-      <c r="N106" s="71"/>
-      <c r="O106" s="71"/>
+      <c r="I106" s="108"/>
+      <c r="J106" s="101"/>
+      <c r="K106" s="70"/>
+      <c r="L106" s="71"/>
+      <c r="M106" s="71"/>
+      <c r="N106" s="70"/>
+      <c r="O106" s="70"/>
       <c r="P106" s="53"/>
     </row>
     <row r="107" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11167,13 +11821,13 @@
       <c r="F107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
-      <c r="I107" s="70"/>
-      <c r="J107" s="70"/>
-      <c r="K107" s="71"/>
-      <c r="L107" s="72"/>
-      <c r="M107" s="72"/>
-      <c r="N107" s="71"/>
-      <c r="O107" s="71"/>
+      <c r="I107" s="108"/>
+      <c r="J107" s="101"/>
+      <c r="K107" s="70"/>
+      <c r="L107" s="71"/>
+      <c r="M107" s="71"/>
+      <c r="N107" s="70"/>
+      <c r="O107" s="70"/>
       <c r="P107" s="53"/>
     </row>
     <row r="108" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11186,13 +11840,13 @@
       <c r="F108" s="53"/>
       <c r="G108" s="53"/>
       <c r="H108" s="53"/>
-      <c r="I108" s="70"/>
-      <c r="J108" s="70"/>
-      <c r="K108" s="71"/>
-      <c r="L108" s="72"/>
-      <c r="M108" s="72"/>
-      <c r="N108" s="71"/>
-      <c r="O108" s="71"/>
+      <c r="I108" s="108"/>
+      <c r="J108" s="101"/>
+      <c r="K108" s="70"/>
+      <c r="L108" s="71"/>
+      <c r="M108" s="71"/>
+      <c r="N108" s="70"/>
+      <c r="O108" s="70"/>
       <c r="P108" s="53"/>
     </row>
     <row r="109" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11205,13 +11859,13 @@
       <c r="F109" s="53"/>
       <c r="G109" s="53"/>
       <c r="H109" s="53"/>
-      <c r="I109" s="70"/>
-      <c r="J109" s="70"/>
-      <c r="K109" s="71"/>
-      <c r="L109" s="72"/>
-      <c r="M109" s="72"/>
-      <c r="N109" s="71"/>
-      <c r="O109" s="71"/>
+      <c r="I109" s="108"/>
+      <c r="J109" s="101"/>
+      <c r="K109" s="70"/>
+      <c r="L109" s="71"/>
+      <c r="M109" s="71"/>
+      <c r="N109" s="70"/>
+      <c r="O109" s="70"/>
       <c r="P109" s="53"/>
     </row>
     <row r="110" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11224,13 +11878,13 @@
       <c r="F110" s="53"/>
       <c r="G110" s="53"/>
       <c r="H110" s="53"/>
-      <c r="I110" s="70"/>
-      <c r="J110" s="70"/>
-      <c r="K110" s="71"/>
-      <c r="L110" s="72"/>
-      <c r="M110" s="72"/>
-      <c r="N110" s="71"/>
-      <c r="O110" s="71"/>
+      <c r="I110" s="108"/>
+      <c r="J110" s="101"/>
+      <c r="K110" s="70"/>
+      <c r="L110" s="71"/>
+      <c r="M110" s="71"/>
+      <c r="N110" s="70"/>
+      <c r="O110" s="70"/>
       <c r="P110" s="53"/>
     </row>
     <row r="111" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11243,13 +11897,13 @@
       <c r="F111" s="53"/>
       <c r="G111" s="53"/>
       <c r="H111" s="53"/>
-      <c r="I111" s="70"/>
-      <c r="J111" s="70"/>
-      <c r="K111" s="71"/>
-      <c r="L111" s="72"/>
-      <c r="M111" s="72"/>
-      <c r="N111" s="71"/>
-      <c r="O111" s="71"/>
+      <c r="I111" s="108"/>
+      <c r="J111" s="101"/>
+      <c r="K111" s="70"/>
+      <c r="L111" s="71"/>
+      <c r="M111" s="71"/>
+      <c r="N111" s="70"/>
+      <c r="O111" s="70"/>
       <c r="P111" s="53"/>
     </row>
     <row r="112" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11262,13 +11916,13 @@
       <c r="F112" s="53"/>
       <c r="G112" s="53"/>
       <c r="H112" s="53"/>
-      <c r="I112" s="70"/>
-      <c r="J112" s="70"/>
-      <c r="K112" s="71"/>
-      <c r="L112" s="72"/>
-      <c r="M112" s="72"/>
-      <c r="N112" s="71"/>
-      <c r="O112" s="71"/>
+      <c r="I112" s="108"/>
+      <c r="J112" s="101"/>
+      <c r="K112" s="70"/>
+      <c r="L112" s="71"/>
+      <c r="M112" s="71"/>
+      <c r="N112" s="70"/>
+      <c r="O112" s="70"/>
       <c r="P112" s="53"/>
     </row>
     <row r="113" spans="2:16" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11281,13 +11935,13 @@
       <c r="F113" s="53"/>
       <c r="G113" s="53"/>
       <c r="H113" s="53"/>
-      <c r="I113" s="70"/>
-      <c r="J113" s="70"/>
-      <c r="K113" s="71"/>
-      <c r="L113" s="72"/>
-      <c r="M113" s="72"/>
-      <c r="N113" s="71"/>
-      <c r="O113" s="71"/>
+      <c r="I113" s="108"/>
+      <c r="J113" s="101"/>
+      <c r="K113" s="70"/>
+      <c r="L113" s="71"/>
+      <c r="M113" s="71"/>
+      <c r="N113" s="70"/>
+      <c r="O113" s="70"/>
       <c r="P113" s="53"/>
     </row>
   </sheetData>
@@ -11309,7 +11963,7 @@
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Activity" prompt="Select the Activity to perfom.  Use &quot;Other&quot; only in truly exceptional cases." sqref="G11:G113" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>INDIRECT(F11)</formula1>
     </dataValidation>
@@ -11325,6 +11979,15 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Parent" prompt="Select the parent task if necessary.  Usually, only &quot;Quality Assurance&quot; and &quot;Revision&quot; tasks have parents." sqref="H11:H113" xr:uid="{00000000-0002-0000-0300-000008000000}">
       <formula1>$C$11:$C$113</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D110" xr:uid="{F7FB6055-8B8A-493E-8FE5-0EDA0EB87E11}">
+      <formula1>"Management,Development,QA,Revision,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11:E110" xr:uid="{61DBA11D-1E7A-40DB-AB24-CB25485A3EE5}">
+      <formula1>"Student 1,Student 2,Student 3,Student 4,Student 5,ALL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11:F110" xr:uid="{6DF7149E-7A2F-49B0-9FC1-079FDA7729F6}">
+      <formula1>"Student,Manager,Analyst,Developer,Tester,Operator,Other"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11342,40 +12005,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="101" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
+      <c r="C2" s="95" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
+      <c r="P2" s="93"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93"/>
+      <c r="P4" s="93"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -11394,7 +12057,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="102" t="s">
+      <c r="C6" s="96" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -11417,7 +12080,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="99"/>
+      <c r="C7" s="93"/>
       <c r="D7" s="11" t="s">
         <v>4</v>
       </c>
@@ -11435,19 +12098,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="98" t="s">
+      <c r="I9" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="99"/>
+      <c r="J9" s="93"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="98" t="s">
+      <c r="L9" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="99"/>
-      <c r="N9" s="98" t="s">
+      <c r="M9" s="93"/>
+      <c r="N9" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="99"/>
+      <c r="O9" s="93"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -14648,52 +15311,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="101" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
+      <c r="B2" s="95" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="100" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
+      <c r="B4" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
@@ -14708,7 +15371,7 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="25" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -14810,7 +15473,7 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="26" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -14823,7 +15486,7 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -14836,7 +15499,7 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="15" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -14849,7 +15512,7 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="16" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -14873,7 +15536,7 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -14899,7 +15562,7 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="18" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -14923,13 +15586,13 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="27" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E25" s="29"/>
       <c r="F25" s="29"/>
@@ -14972,7 +15635,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>34</v>
@@ -14996,13 +15659,13 @@
         <v>40</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>26</v>
@@ -15021,7 +15684,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>37</v>
@@ -15057,7 +15720,7 @@
         <v>61</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>26</v>
@@ -15126,10 +15789,10 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="33" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
@@ -15144,7 +15807,7 @@
         <v>21</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
@@ -15159,7 +15822,7 @@
         <v>30</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
@@ -15189,7 +15852,7 @@
         <v>132</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
@@ -15204,7 +15867,7 @@
         <v>39</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>

--- a/reports/Group/Project-planing.xlsx
+++ b/reports/Group/Project-planing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxnii\OneDrive\Documentos\DP2\Workspace-26\Projects\Acme-Starters-B\reports\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197D0FBF-C470-425F-8518-8E3B566E135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A1B24C-F651-4606-9446-8AA27DDC2A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,7 +876,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$EUR]\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1177,7 +1177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1404,6 +1404,21 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1428,34 +1443,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1885,118 +1872,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="100" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="99" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="102"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="97"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="97"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="97"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="102"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="97"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="97"/>
-      <c r="I9" s="97"/>
-      <c r="J9" s="97"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="102"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97"/>
-      <c r="H10" s="97"/>
-      <c r="I10" s="97"/>
-      <c r="J10" s="97"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="97"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="97"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="97"/>
-      <c r="I12" s="97"/>
-      <c r="J12" s="97"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2013,17 +2000,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="100" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
@@ -2037,39 +2024,39 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="99" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -2097,29 +2084,29 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
-      <c r="C9" s="98" t="s">
+      <c r="C9" s="103" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="93"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="49"/>
-      <c r="C10" s="98" t="s">
+      <c r="C10" s="103" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="50"/>
@@ -2136,16 +2123,16 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
-      <c r="C12" s="98" t="s">
+      <c r="C12" s="103" t="s">
         <v>151</v>
       </c>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2172,40 +2159,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="104"/>
+      <c r="P4" s="104"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -2224,7 +2211,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="101" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -2247,7 +2234,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="99"/>
+      <c r="C7" s="104"/>
       <c r="D7" s="10" t="s">
         <v>4</v>
       </c>
@@ -2265,19 +2252,19 @@
       <c r="F9" s="57"/>
       <c r="G9" s="57"/>
       <c r="H9" s="57"/>
-      <c r="I9" s="96" t="s">
+      <c r="I9" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="99"/>
+      <c r="J9" s="104"/>
       <c r="K9" s="57"/>
-      <c r="L9" s="96" t="s">
+      <c r="L9" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="99"/>
-      <c r="N9" s="96" t="s">
+      <c r="M9" s="104"/>
+      <c r="N9" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="99"/>
+      <c r="O9" s="104"/>
       <c r="P9" s="57"/>
     </row>
     <row r="10" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7335,47 +7322,45 @@
   <dimension ref="B2:P113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="8" width="18.88671875" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" style="107" customWidth="1"/>
-    <col min="10" max="15" width="18.88671875" customWidth="1"/>
+    <col min="3" max="15" width="18.88671875" customWidth="1"/>
     <col min="16" max="16" width="64.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="100" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="93"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="98"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -7384,7 +7369,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="106"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -7394,7 +7379,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="101" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -7407,7 +7392,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="106"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -7417,7 +7402,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="93"/>
+      <c r="C7" s="98"/>
       <c r="D7" s="11" t="s">
         <v>4</v>
       </c>
@@ -7435,19 +7420,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="92" t="s">
+      <c r="I9" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="93"/>
+      <c r="J9" s="98"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="92" t="s">
+      <c r="L9" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="93"/>
-      <c r="N9" s="92" t="s">
+      <c r="M9" s="98"/>
+      <c r="N9" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="93"/>
+      <c r="O9" s="98"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7518,14 +7503,14 @@
         <v>41</v>
       </c>
       <c r="H11" s="53"/>
-      <c r="I11" s="108">
+      <c r="I11" s="92">
         <v>45741</v>
       </c>
-      <c r="J11" s="101">
+      <c r="J11" s="92">
         <v>45776</v>
       </c>
       <c r="K11" s="70" t="str">
-        <f ca="1">IF(OR(I11="",J11=""),"",IF(AND(J11&lt;&gt;"",I11&gt;=NOW()),"Planned",IF(AND(J11&lt;&gt;"",J11&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ref="K11:K42" ca="1" si="0">IF(OR(I11="",J11=""),"",IF(AND(J11&lt;&gt;"",I11&gt;=NOW()),"Planned",IF(AND(J11&lt;&gt;"",J11&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L11" s="71">
@@ -7565,14 +7550,14 @@
         <v>43</v>
       </c>
       <c r="H12" s="53"/>
-      <c r="I12" s="108">
+      <c r="I12" s="92">
         <v>45747.625</v>
       </c>
-      <c r="J12" s="101">
+      <c r="J12" s="92">
         <v>45747.645833333299</v>
       </c>
       <c r="K12" s="70" t="str">
-        <f ca="1">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L12" s="71">
@@ -7612,14 +7597,14 @@
         <v>45</v>
       </c>
       <c r="H13" s="53"/>
-      <c r="I13" s="108">
+      <c r="I13" s="92">
         <v>45747.645833333299</v>
       </c>
-      <c r="J13" s="101">
+      <c r="J13" s="92">
         <v>45747.729166666701</v>
       </c>
       <c r="K13" s="70" t="str">
-        <f ca="1">IF(OR(I13="",J13=""),"",IF(AND(J13&lt;&gt;"",I13&gt;=NOW()),"Planned",IF(AND(J13&lt;&gt;"",J13&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L13" s="71">
@@ -7659,14 +7644,14 @@
         <v>28</v>
       </c>
       <c r="H14" s="53"/>
-      <c r="I14" s="108">
+      <c r="I14" s="92">
         <v>45748</v>
       </c>
-      <c r="J14" s="101">
+      <c r="J14" s="92">
         <v>45751</v>
       </c>
       <c r="K14" s="70" t="str">
-        <f ca="1">IF(OR(I14="",J14=""),"",IF(AND(J14&lt;&gt;"",I14&gt;=NOW()),"Planned",IF(AND(J14&lt;&gt;"",J14&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L14" s="71">
@@ -7708,14 +7693,14 @@
         <v>24</v>
       </c>
       <c r="H15" s="53"/>
-      <c r="I15" s="108">
+      <c r="I15" s="92">
         <v>45748</v>
       </c>
-      <c r="J15" s="101">
+      <c r="J15" s="92">
         <v>45751</v>
       </c>
       <c r="K15" s="70" t="str">
-        <f ca="1">IF(OR(I15="",J15=""),"",IF(AND(J15&lt;&gt;"",I15&gt;=NOW()),"Planned",IF(AND(J15&lt;&gt;"",J15&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L15" s="71">
@@ -7757,14 +7742,14 @@
         <v>26</v>
       </c>
       <c r="H16" s="53"/>
-      <c r="I16" s="108">
+      <c r="I16" s="92">
         <v>45748</v>
       </c>
-      <c r="J16" s="101">
+      <c r="J16" s="92">
         <v>45751</v>
       </c>
       <c r="K16" s="70" t="str">
-        <f ca="1">IF(OR(I16="",J16=""),"",IF(AND(J16&lt;&gt;"",I16&gt;=NOW()),"Planned",IF(AND(J16&lt;&gt;"",J16&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L16" s="71">
@@ -7806,14 +7791,14 @@
         <v>34</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="108">
+      <c r="I17" s="92">
         <v>45748</v>
       </c>
-      <c r="J17" s="101">
+      <c r="J17" s="92">
         <v>45751</v>
       </c>
       <c r="K17" s="70" t="str">
-        <f ca="1">IF(OR(I17="",J17=""),"",IF(AND(J17&lt;&gt;"",I17&gt;=NOW()),"Planned",IF(AND(J17&lt;&gt;"",J17&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L17" s="71">
@@ -7855,14 +7840,14 @@
         <v>24</v>
       </c>
       <c r="H18" s="53"/>
-      <c r="I18" s="108">
+      <c r="I18" s="92">
         <v>45748</v>
       </c>
-      <c r="J18" s="101">
+      <c r="J18" s="92">
         <v>45751</v>
       </c>
       <c r="K18" s="70" t="str">
-        <f ca="1">IF(OR(I18="",J18=""),"",IF(AND(J18&lt;&gt;"",I18&gt;=NOW()),"Planned",IF(AND(J18&lt;&gt;"",J18&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L18" s="71">
@@ -7904,14 +7889,14 @@
         <v>24</v>
       </c>
       <c r="H19" s="53"/>
-      <c r="I19" s="108">
+      <c r="I19" s="92">
         <v>45748</v>
       </c>
-      <c r="J19" s="101">
+      <c r="J19" s="92">
         <v>45751</v>
       </c>
       <c r="K19" s="70" t="str">
-        <f ca="1">IF(OR(I19="",J19=""),"",IF(AND(J19&lt;&gt;"",I19&gt;=NOW()),"Planned",IF(AND(J19&lt;&gt;"",J19&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L19" s="71">
@@ -7953,14 +7938,14 @@
         <v>37</v>
       </c>
       <c r="H20" s="53"/>
-      <c r="I20" s="108">
+      <c r="I20" s="92">
         <v>45748</v>
       </c>
-      <c r="J20" s="101">
+      <c r="J20" s="92">
         <v>45751</v>
       </c>
       <c r="K20" s="70" t="str">
-        <f ca="1">IF(OR(I20="",J20=""),"",IF(AND(J20&lt;&gt;"",I20&gt;=NOW()),"Planned",IF(AND(J20&lt;&gt;"",J20&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L20" s="71">
@@ -8002,14 +7987,14 @@
         <v>171</v>
       </c>
       <c r="H21" s="53"/>
-      <c r="I21" s="108">
+      <c r="I21" s="92">
         <v>45748</v>
       </c>
-      <c r="J21" s="101">
+      <c r="J21" s="92">
         <v>45751</v>
       </c>
       <c r="K21" s="70" t="str">
-        <f ca="1">IF(OR(I21="",J21=""),"",IF(AND(J21&lt;&gt;"",I21&gt;=NOW()),"Planned",IF(AND(J21&lt;&gt;"",J21&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L21" s="71">
@@ -8051,14 +8036,14 @@
         <v>50</v>
       </c>
       <c r="H22" s="53"/>
-      <c r="I22" s="108">
+      <c r="I22" s="92">
         <v>45748</v>
       </c>
-      <c r="J22" s="101">
+      <c r="J22" s="92">
         <v>45751</v>
       </c>
       <c r="K22" s="70" t="str">
-        <f ca="1">IF(OR(I22="",J22=""),"",IF(AND(J22&lt;&gt;"",I22&gt;=NOW()),"Planned",IF(AND(J22&lt;&gt;"",J22&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L22" s="71">
@@ -8098,14 +8083,14 @@
         <v>45</v>
       </c>
       <c r="H23" s="53"/>
-      <c r="I23" s="108">
+      <c r="I23" s="92">
         <v>45750.729166666701</v>
       </c>
-      <c r="J23" s="101">
+      <c r="J23" s="92">
         <v>45750.8125</v>
       </c>
       <c r="K23" s="70" t="str">
-        <f ca="1">IF(OR(I23="",J23=""),"",IF(AND(J23&lt;&gt;"",I23&gt;=NOW()),"Planned",IF(AND(J23&lt;&gt;"",J23&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L23" s="71">
@@ -8145,14 +8130,14 @@
         <v>50</v>
       </c>
       <c r="H24" s="53"/>
-      <c r="I24" s="108">
+      <c r="I24" s="92">
         <v>45754</v>
       </c>
-      <c r="J24" s="101">
+      <c r="J24" s="92">
         <v>45758</v>
       </c>
       <c r="K24" s="70" t="str">
-        <f ca="1">IF(OR(I24="",J24=""),"",IF(AND(J24&lt;&gt;"",I24&gt;=NOW()),"Planned",IF(AND(J24&lt;&gt;"",J24&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L24" s="71">
@@ -8192,14 +8177,14 @@
         <v>50</v>
       </c>
       <c r="H25" s="53"/>
-      <c r="I25" s="108">
+      <c r="I25" s="92">
         <v>45754</v>
       </c>
-      <c r="J25" s="101">
+      <c r="J25" s="92">
         <v>45758</v>
       </c>
       <c r="K25" s="70" t="str">
-        <f ca="1">IF(OR(I25="",J25=""),"",IF(AND(J25&lt;&gt;"",I25&gt;=NOW()),"Planned",IF(AND(J25&lt;&gt;"",J25&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L25" s="71">
@@ -8239,14 +8224,14 @@
         <v>50</v>
       </c>
       <c r="H26" s="53"/>
-      <c r="I26" s="108">
+      <c r="I26" s="92">
         <v>45754</v>
       </c>
-      <c r="J26" s="101">
+      <c r="J26" s="92">
         <v>45758</v>
       </c>
       <c r="K26" s="70" t="str">
-        <f ca="1">IF(OR(I26="",J26=""),"",IF(AND(J26&lt;&gt;"",I26&gt;=NOW()),"Planned",IF(AND(J26&lt;&gt;"",J26&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L26" s="71">
@@ -8286,14 +8271,14 @@
         <v>50</v>
       </c>
       <c r="H27" s="53"/>
-      <c r="I27" s="108">
+      <c r="I27" s="92">
         <v>45754</v>
       </c>
-      <c r="J27" s="101">
+      <c r="J27" s="92">
         <v>45758</v>
       </c>
       <c r="K27" s="70" t="str">
-        <f ca="1">IF(OR(I27="",J27=""),"",IF(AND(J27&lt;&gt;"",I27&gt;=NOW()),"Planned",IF(AND(J27&lt;&gt;"",J27&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L27" s="71">
@@ -8333,14 +8318,14 @@
         <v>50</v>
       </c>
       <c r="H28" s="53"/>
-      <c r="I28" s="108">
+      <c r="I28" s="92">
         <v>45754</v>
       </c>
-      <c r="J28" s="101">
+      <c r="J28" s="92">
         <v>45758</v>
       </c>
       <c r="K28" s="70" t="str">
-        <f ca="1">IF(OR(I28="",J28=""),"",IF(AND(J28&lt;&gt;"",I28&gt;=NOW()),"Planned",IF(AND(J28&lt;&gt;"",J28&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L28" s="71">
@@ -8380,14 +8365,14 @@
         <v>50</v>
       </c>
       <c r="H29" s="53"/>
-      <c r="I29" s="108">
+      <c r="I29" s="92">
         <v>45754</v>
       </c>
-      <c r="J29" s="101">
+      <c r="J29" s="92">
         <v>45758</v>
       </c>
       <c r="K29" s="70" t="str">
-        <f ca="1">IF(OR(I29="",J29=""),"",IF(AND(J29&lt;&gt;"",I29&gt;=NOW()),"Planned",IF(AND(J29&lt;&gt;"",J29&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L29" s="71">
@@ -8427,14 +8412,14 @@
         <v>50</v>
       </c>
       <c r="H30" s="53"/>
-      <c r="I30" s="108">
+      <c r="I30" s="92">
         <v>45754</v>
       </c>
-      <c r="J30" s="101">
+      <c r="J30" s="92">
         <v>45758</v>
       </c>
       <c r="K30" s="70" t="str">
-        <f ca="1">IF(OR(I30="",J30=""),"",IF(AND(J30&lt;&gt;"",I30&gt;=NOW()),"Planned",IF(AND(J30&lt;&gt;"",J30&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L30" s="71">
@@ -8474,14 +8459,14 @@
         <v>50</v>
       </c>
       <c r="H31" s="53"/>
-      <c r="I31" s="108">
+      <c r="I31" s="92">
         <v>45754</v>
       </c>
-      <c r="J31" s="101">
+      <c r="J31" s="92">
         <v>45758</v>
       </c>
       <c r="K31" s="70" t="str">
-        <f ca="1">IF(OR(I31="",J31=""),"",IF(AND(J31&lt;&gt;"",I31&gt;=NOW()),"Planned",IF(AND(J31&lt;&gt;"",J31&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L31" s="71">
@@ -8521,14 +8506,14 @@
         <v>50</v>
       </c>
       <c r="H32" s="53"/>
-      <c r="I32" s="108">
+      <c r="I32" s="92">
         <v>45754</v>
       </c>
-      <c r="J32" s="101">
+      <c r="J32" s="92">
         <v>45758</v>
       </c>
       <c r="K32" s="70" t="str">
-        <f ca="1">IF(OR(I32="",J32=""),"",IF(AND(J32&lt;&gt;"",I32&gt;=NOW()),"Planned",IF(AND(J32&lt;&gt;"",J32&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L32" s="71">
@@ -8568,14 +8553,14 @@
         <v>50</v>
       </c>
       <c r="H33" s="53"/>
-      <c r="I33" s="108">
+      <c r="I33" s="92">
         <v>45754</v>
       </c>
-      <c r="J33" s="101">
+      <c r="J33" s="92">
         <v>45758</v>
       </c>
       <c r="K33" s="70" t="str">
-        <f ca="1">IF(OR(I33="",J33=""),"",IF(AND(J33&lt;&gt;"",I33&gt;=NOW()),"Planned",IF(AND(J33&lt;&gt;"",J33&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L33" s="71">
@@ -8615,14 +8600,14 @@
         <v>43</v>
       </c>
       <c r="H34" s="53"/>
-      <c r="I34" s="108">
+      <c r="I34" s="92">
         <v>45754.625</v>
       </c>
-      <c r="J34" s="101">
+      <c r="J34" s="92">
         <v>45754.645833333299</v>
       </c>
       <c r="K34" s="70" t="str">
-        <f ca="1">IF(OR(I34="",J34=""),"",IF(AND(J34&lt;&gt;"",I34&gt;=NOW()),"Planned",IF(AND(J34&lt;&gt;"",J34&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L34" s="71">
@@ -8662,14 +8647,14 @@
         <v>45</v>
       </c>
       <c r="H35" s="53"/>
-      <c r="I35" s="108">
+      <c r="I35" s="92">
         <v>45754.645833333299</v>
       </c>
-      <c r="J35" s="101">
+      <c r="J35" s="92">
         <v>45754.729166666701</v>
       </c>
       <c r="K35" s="70" t="str">
-        <f ca="1">IF(OR(I35="",J35=""),"",IF(AND(J35&lt;&gt;"",I35&gt;=NOW()),"Planned",IF(AND(J35&lt;&gt;"",J35&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L35" s="71">
@@ -8709,14 +8694,14 @@
         <v>45</v>
       </c>
       <c r="H36" s="53"/>
-      <c r="I36" s="108">
+      <c r="I36" s="92">
         <v>45757.729166666701</v>
       </c>
-      <c r="J36" s="101">
+      <c r="J36" s="92">
         <v>45757.8125</v>
       </c>
       <c r="K36" s="70" t="str">
-        <f ca="1">IF(OR(I36="",J36=""),"",IF(AND(J36&lt;&gt;"",I36&gt;=NOW()),"Planned",IF(AND(J36&lt;&gt;"",J36&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L36" s="71">
@@ -8758,14 +8743,14 @@
       <c r="H37" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="I37" s="108">
+      <c r="I37" s="92">
         <v>45761</v>
       </c>
-      <c r="J37" s="101">
+      <c r="J37" s="92">
         <v>45762</v>
       </c>
       <c r="K37" s="70" t="str">
-        <f ca="1">IF(OR(I37="",J37=""),"",IF(AND(J37&lt;&gt;"",I37&gt;=NOW()),"Planned",IF(AND(J37&lt;&gt;"",J37&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L37" s="71">
@@ -8807,14 +8792,14 @@
       <c r="H38" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="I38" s="108">
+      <c r="I38" s="92">
         <v>45761</v>
       </c>
-      <c r="J38" s="101">
+      <c r="J38" s="92">
         <v>45762</v>
       </c>
       <c r="K38" s="70" t="str">
-        <f ca="1">IF(OR(I38="",J38=""),"",IF(AND(J38&lt;&gt;"",I38&gt;=NOW()),"Planned",IF(AND(J38&lt;&gt;"",J38&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L38" s="71">
@@ -8856,14 +8841,14 @@
       <c r="H39" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="I39" s="108">
+      <c r="I39" s="92">
         <v>45761</v>
       </c>
-      <c r="J39" s="101">
+      <c r="J39" s="92">
         <v>45762</v>
       </c>
       <c r="K39" s="70" t="str">
-        <f ca="1">IF(OR(I39="",J39=""),"",IF(AND(J39&lt;&gt;"",I39&gt;=NOW()),"Planned",IF(AND(J39&lt;&gt;"",J39&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L39" s="71">
@@ -8905,14 +8890,14 @@
       <c r="H40" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="I40" s="108">
+      <c r="I40" s="92">
         <v>45761</v>
       </c>
-      <c r="J40" s="101">
+      <c r="J40" s="92">
         <v>45762</v>
       </c>
       <c r="K40" s="70" t="str">
-        <f ca="1">IF(OR(I40="",J40=""),"",IF(AND(J40&lt;&gt;"",I40&gt;=NOW()),"Planned",IF(AND(J40&lt;&gt;"",J40&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L40" s="71">
@@ -8954,14 +8939,14 @@
       <c r="H41" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="I41" s="108">
+      <c r="I41" s="92">
         <v>45761</v>
       </c>
-      <c r="J41" s="101">
+      <c r="J41" s="92">
         <v>45762</v>
       </c>
       <c r="K41" s="70" t="str">
-        <f ca="1">IF(OR(I41="",J41=""),"",IF(AND(J41&lt;&gt;"",I41&gt;=NOW()),"Planned",IF(AND(J41&lt;&gt;"",J41&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L41" s="71">
@@ -9001,14 +8986,14 @@
         <v>50</v>
       </c>
       <c r="H42" s="53"/>
-      <c r="I42" s="108">
+      <c r="I42" s="92">
         <v>45761</v>
       </c>
-      <c r="J42" s="101">
+      <c r="J42" s="92">
         <v>45765</v>
       </c>
       <c r="K42" s="70" t="str">
-        <f ca="1">IF(OR(I42="",J42=""),"",IF(AND(J42&lt;&gt;"",I42&gt;=NOW()),"Planned",IF(AND(J42&lt;&gt;"",J42&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L42" s="71">
@@ -9048,14 +9033,14 @@
         <v>50</v>
       </c>
       <c r="H43" s="53"/>
-      <c r="I43" s="108">
+      <c r="I43" s="92">
         <v>45761</v>
       </c>
-      <c r="J43" s="101">
+      <c r="J43" s="92">
         <v>45765</v>
       </c>
       <c r="K43" s="70" t="str">
-        <f ca="1">IF(OR(I43="",J43=""),"",IF(AND(J43&lt;&gt;"",I43&gt;=NOW()),"Planned",IF(AND(J43&lt;&gt;"",J43&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ref="K43:K74" ca="1" si="1">IF(OR(I43="",J43=""),"",IF(AND(J43&lt;&gt;"",I43&gt;=NOW()),"Planned",IF(AND(J43&lt;&gt;"",J43&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L43" s="71">
@@ -9095,14 +9080,14 @@
         <v>50</v>
       </c>
       <c r="H44" s="53"/>
-      <c r="I44" s="108">
+      <c r="I44" s="92">
         <v>45761</v>
       </c>
-      <c r="J44" s="101">
+      <c r="J44" s="92">
         <v>45765</v>
       </c>
       <c r="K44" s="70" t="str">
-        <f ca="1">IF(OR(I44="",J44=""),"",IF(AND(J44&lt;&gt;"",I44&gt;=NOW()),"Planned",IF(AND(J44&lt;&gt;"",J44&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L44" s="71">
@@ -9142,14 +9127,14 @@
         <v>50</v>
       </c>
       <c r="H45" s="53"/>
-      <c r="I45" s="108">
+      <c r="I45" s="92">
         <v>45761</v>
       </c>
-      <c r="J45" s="101">
+      <c r="J45" s="92">
         <v>45765</v>
       </c>
       <c r="K45" s="70" t="str">
-        <f ca="1">IF(OR(I45="",J45=""),"",IF(AND(J45&lt;&gt;"",I45&gt;=NOW()),"Planned",IF(AND(J45&lt;&gt;"",J45&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L45" s="71">
@@ -9189,14 +9174,14 @@
         <v>50</v>
       </c>
       <c r="H46" s="53"/>
-      <c r="I46" s="108">
+      <c r="I46" s="92">
         <v>45761</v>
       </c>
-      <c r="J46" s="101">
+      <c r="J46" s="92">
         <v>45765</v>
       </c>
       <c r="K46" s="70" t="str">
-        <f ca="1">IF(OR(I46="",J46=""),"",IF(AND(J46&lt;&gt;"",I46&gt;=NOW()),"Planned",IF(AND(J46&lt;&gt;"",J46&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L46" s="71">
@@ -9236,14 +9221,14 @@
         <v>43</v>
       </c>
       <c r="H47" s="53"/>
-      <c r="I47" s="108">
+      <c r="I47" s="92">
         <v>45761.625</v>
       </c>
-      <c r="J47" s="101">
+      <c r="J47" s="92">
         <v>45761.645833333299</v>
       </c>
       <c r="K47" s="70" t="str">
-        <f ca="1">IF(OR(I47="",J47=""),"",IF(AND(J47&lt;&gt;"",I47&gt;=NOW()),"Planned",IF(AND(J47&lt;&gt;"",J47&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L47" s="71">
@@ -9283,14 +9268,14 @@
         <v>45</v>
       </c>
       <c r="H48" s="53"/>
-      <c r="I48" s="108">
+      <c r="I48" s="92">
         <v>45761.645833333299</v>
       </c>
-      <c r="J48" s="101">
+      <c r="J48" s="92">
         <v>45761.729166666701</v>
       </c>
       <c r="K48" s="70" t="str">
-        <f ca="1">IF(OR(I48="",J48=""),"",IF(AND(J48&lt;&gt;"",I48&gt;=NOW()),"Planned",IF(AND(J48&lt;&gt;"",J48&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L48" s="71">
@@ -9330,14 +9315,14 @@
         <v>45</v>
       </c>
       <c r="H49" s="53"/>
-      <c r="I49" s="108">
+      <c r="I49" s="92">
         <v>45764.729166666701</v>
       </c>
-      <c r="J49" s="101">
+      <c r="J49" s="92">
         <v>45764.8125</v>
       </c>
       <c r="K49" s="70" t="str">
-        <f ca="1">IF(OR(I49="",J49=""),"",IF(AND(J49&lt;&gt;"",I49&gt;=NOW()),"Planned",IF(AND(J49&lt;&gt;"",J49&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L49" s="71">
@@ -9379,14 +9364,14 @@
       <c r="H50" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="I50" s="108">
+      <c r="I50" s="92">
         <v>45768</v>
       </c>
-      <c r="J50" s="101">
+      <c r="J50" s="92">
         <v>45769</v>
       </c>
       <c r="K50" s="70" t="str">
-        <f ca="1">IF(OR(I50="",J50=""),"",IF(AND(J50&lt;&gt;"",I50&gt;=NOW()),"Planned",IF(AND(J50&lt;&gt;"",J50&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L50" s="71">
@@ -9428,14 +9413,14 @@
       <c r="H51" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="I51" s="108">
+      <c r="I51" s="92">
         <v>45768</v>
       </c>
-      <c r="J51" s="101">
+      <c r="J51" s="92">
         <v>45769</v>
       </c>
       <c r="K51" s="70" t="str">
-        <f ca="1">IF(OR(I51="",J51=""),"",IF(AND(J51&lt;&gt;"",I51&gt;=NOW()),"Planned",IF(AND(J51&lt;&gt;"",J51&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L51" s="71">
@@ -9477,14 +9462,14 @@
       <c r="H52" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="I52" s="108">
+      <c r="I52" s="92">
         <v>45768</v>
       </c>
-      <c r="J52" s="101">
+      <c r="J52" s="92">
         <v>45769</v>
       </c>
       <c r="K52" s="70" t="str">
-        <f ca="1">IF(OR(I52="",J52=""),"",IF(AND(J52&lt;&gt;"",I52&gt;=NOW()),"Planned",IF(AND(J52&lt;&gt;"",J52&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L52" s="71">
@@ -9526,14 +9511,14 @@
       <c r="H53" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="I53" s="108">
+      <c r="I53" s="92">
         <v>45768</v>
       </c>
-      <c r="J53" s="101">
+      <c r="J53" s="92">
         <v>45769</v>
       </c>
       <c r="K53" s="70" t="str">
-        <f ca="1">IF(OR(I53="",J53=""),"",IF(AND(J53&lt;&gt;"",I53&gt;=NOW()),"Planned",IF(AND(J53&lt;&gt;"",J53&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L53" s="71">
@@ -9575,14 +9560,14 @@
       <c r="H54" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="I54" s="108">
+      <c r="I54" s="92">
         <v>45768</v>
       </c>
-      <c r="J54" s="101">
+      <c r="J54" s="92">
         <v>45769</v>
       </c>
       <c r="K54" s="70" t="str">
-        <f ca="1">IF(OR(I54="",J54=""),"",IF(AND(J54&lt;&gt;"",I54&gt;=NOW()),"Planned",IF(AND(J54&lt;&gt;"",J54&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L54" s="71">
@@ -9622,14 +9607,14 @@
         <v>43</v>
       </c>
       <c r="H55" s="74"/>
-      <c r="I55" s="109">
+      <c r="I55" s="93">
         <v>45768.625</v>
       </c>
-      <c r="J55" s="102">
+      <c r="J55" s="93">
         <v>45768.645833333299</v>
       </c>
       <c r="K55" s="75" t="str">
-        <f ca="1">IF(OR(I55="",J55=""),"",IF(AND(J55&lt;&gt;"",I55&gt;=NOW()),"Planned",IF(AND(J55&lt;&gt;"",J55&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L55" s="76">
@@ -9669,14 +9654,14 @@
         <v>45</v>
       </c>
       <c r="H56" s="84"/>
-      <c r="I56" s="103">
+      <c r="I56" s="94">
         <v>45768.645833333299</v>
       </c>
-      <c r="J56" s="103">
+      <c r="J56" s="94">
         <v>45768.729166666701</v>
       </c>
       <c r="K56" s="85" t="str">
-        <f ca="1">IF(OR(I56="",J56=""),"",IF(AND(J56&lt;&gt;"",I56&gt;=NOW()),"Planned",IF(AND(J56&lt;&gt;"",J56&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L56" s="86">
@@ -9716,14 +9701,14 @@
         <v>50</v>
       </c>
       <c r="H57" s="84"/>
-      <c r="I57" s="103">
+      <c r="I57" s="94">
         <v>45769</v>
       </c>
-      <c r="J57" s="103">
+      <c r="J57" s="94">
         <v>45771</v>
       </c>
       <c r="K57" s="85" t="str">
-        <f ca="1">IF(OR(I57="",J57=""),"",IF(AND(J57&lt;&gt;"",I57&gt;=NOW()),"Planned",IF(AND(J57&lt;&gt;"",J57&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L57" s="86">
@@ -9763,14 +9748,14 @@
         <v>50</v>
       </c>
       <c r="H58" s="79"/>
-      <c r="I58" s="104">
+      <c r="I58" s="95">
         <v>45769</v>
       </c>
-      <c r="J58" s="104">
+      <c r="J58" s="95">
         <v>45771</v>
       </c>
       <c r="K58" s="80" t="str">
-        <f ca="1">IF(OR(I58="",J58=""),"",IF(AND(J58&lt;&gt;"",I58&gt;=NOW()),"Planned",IF(AND(J58&lt;&gt;"",J58&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L58" s="81">
@@ -9810,14 +9795,14 @@
         <v>50</v>
       </c>
       <c r="H59" s="89"/>
-      <c r="I59" s="110">
+      <c r="I59" s="96">
         <v>45769</v>
       </c>
-      <c r="J59" s="105">
+      <c r="J59" s="96">
         <v>45771</v>
       </c>
       <c r="K59" s="90" t="str">
-        <f ca="1">IF(OR(I59="",J59=""),"",IF(AND(J59&lt;&gt;"",I59&gt;=NOW()),"Planned",IF(AND(J59&lt;&gt;"",J59&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L59" s="91">
@@ -9857,14 +9842,14 @@
         <v>45</v>
       </c>
       <c r="H60" s="53"/>
-      <c r="I60" s="108">
+      <c r="I60" s="92">
         <v>45771.729166666701</v>
       </c>
-      <c r="J60" s="101">
+      <c r="J60" s="92">
         <v>45771.8125</v>
       </c>
       <c r="K60" s="70" t="str">
-        <f ca="1">IF(OR(I60="",J60=""),"",IF(AND(J60&lt;&gt;"",I60&gt;=NOW()),"Planned",IF(AND(J60&lt;&gt;"",J60&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L60" s="71">
@@ -9906,14 +9891,14 @@
       <c r="H61" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="I61" s="108">
+      <c r="I61" s="92">
         <v>45772</v>
       </c>
-      <c r="J61" s="101">
+      <c r="J61" s="92">
         <v>45772</v>
       </c>
       <c r="K61" s="70" t="str">
-        <f ca="1">IF(OR(I61="",J61=""),"",IF(AND(J61&lt;&gt;"",I61&gt;=NOW()),"Planned",IF(AND(J61&lt;&gt;"",J61&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L61" s="71">
@@ -9955,14 +9940,14 @@
       <c r="H62" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="I62" s="108">
+      <c r="I62" s="92">
         <v>45772</v>
       </c>
-      <c r="J62" s="101">
+      <c r="J62" s="92">
         <v>45772</v>
       </c>
       <c r="K62" s="70" t="str">
-        <f ca="1">IF(OR(I62="",J62=""),"",IF(AND(J62&lt;&gt;"",I62&gt;=NOW()),"Planned",IF(AND(J62&lt;&gt;"",J62&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L62" s="71">
@@ -10004,14 +9989,14 @@
       <c r="H63" s="53" t="s">
         <v>215</v>
       </c>
-      <c r="I63" s="108">
+      <c r="I63" s="92">
         <v>45772</v>
       </c>
-      <c r="J63" s="101">
+      <c r="J63" s="92">
         <v>45772</v>
       </c>
       <c r="K63" s="70" t="str">
-        <f ca="1">IF(OR(I63="",J63=""),"",IF(AND(J63&lt;&gt;"",I63&gt;=NOW()),"Planned",IF(AND(J63&lt;&gt;"",J63&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L63" s="71">
@@ -10053,14 +10038,14 @@
       <c r="H64" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="I64" s="108">
+      <c r="I64" s="92">
         <v>45772</v>
       </c>
-      <c r="J64" s="101">
+      <c r="J64" s="92">
         <v>45775</v>
       </c>
       <c r="K64" s="70" t="str">
-        <f ca="1">IF(OR(I64="",J64=""),"",IF(AND(J64&lt;&gt;"",I64&gt;=NOW()),"Planned",IF(AND(J64&lt;&gt;"",J64&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L64" s="71">
@@ -10102,14 +10087,14 @@
       <c r="H65" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="I65" s="108">
+      <c r="I65" s="92">
         <v>45772</v>
       </c>
-      <c r="J65" s="101">
+      <c r="J65" s="92">
         <v>45775</v>
       </c>
       <c r="K65" s="70" t="str">
-        <f ca="1">IF(OR(I65="",J65=""),"",IF(AND(J65&lt;&gt;"",I65&gt;=NOW()),"Planned",IF(AND(J65&lt;&gt;"",J65&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L65" s="71">
@@ -10151,14 +10136,14 @@
       <c r="H66" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="I66" s="108">
+      <c r="I66" s="92">
         <v>45772</v>
       </c>
-      <c r="J66" s="101">
+      <c r="J66" s="92">
         <v>45775</v>
       </c>
       <c r="K66" s="70" t="str">
-        <f ca="1">IF(OR(I66="",J66=""),"",IF(AND(J66&lt;&gt;"",I66&gt;=NOW()),"Planned",IF(AND(J66&lt;&gt;"",J66&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L66" s="71">
@@ -10200,14 +10185,14 @@
       <c r="H67" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="I67" s="108">
+      <c r="I67" s="92">
         <v>45772</v>
       </c>
-      <c r="J67" s="101">
+      <c r="J67" s="92">
         <v>45775</v>
       </c>
       <c r="K67" s="70" t="str">
-        <f ca="1">IF(OR(I67="",J67=""),"",IF(AND(J67&lt;&gt;"",I67&gt;=NOW()),"Planned",IF(AND(J67&lt;&gt;"",J67&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L67" s="71">
@@ -10249,14 +10234,14 @@
       <c r="H68" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="I68" s="108">
+      <c r="I68" s="92">
         <v>45772</v>
       </c>
-      <c r="J68" s="101">
+      <c r="J68" s="92">
         <v>45775</v>
       </c>
       <c r="K68" s="70" t="str">
-        <f ca="1">IF(OR(I68="",J68=""),"",IF(AND(J68&lt;&gt;"",I68&gt;=NOW()),"Planned",IF(AND(J68&lt;&gt;"",J68&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L68" s="71">
@@ -10296,14 +10281,14 @@
         <v>123</v>
       </c>
       <c r="H69" s="53"/>
-      <c r="I69" s="108">
+      <c r="I69" s="92">
         <v>45775</v>
       </c>
-      <c r="J69" s="101">
+      <c r="J69" s="92">
         <v>45775</v>
       </c>
       <c r="K69" s="70" t="str">
-        <f ca="1">IF(OR(I69="",J69=""),"",IF(AND(J69&lt;&gt;"",I69&gt;=NOW()),"Planned",IF(AND(J69&lt;&gt;"",J69&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L69" s="71">
@@ -10343,14 +10328,14 @@
         <v>43</v>
       </c>
       <c r="H70" s="53"/>
-      <c r="I70" s="108">
+      <c r="I70" s="92">
         <v>45775.625</v>
       </c>
-      <c r="J70" s="101">
+      <c r="J70" s="92">
         <v>45775.645833333299</v>
       </c>
       <c r="K70" s="70" t="str">
-        <f ca="1">IF(OR(I70="",J70=""),"",IF(AND(J70&lt;&gt;"",I70&gt;=NOW()),"Planned",IF(AND(J70&lt;&gt;"",J70&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L70" s="71">
@@ -10390,14 +10375,14 @@
         <v>45</v>
       </c>
       <c r="H71" s="53"/>
-      <c r="I71" s="108">
+      <c r="I71" s="92">
         <v>45775.645833333299</v>
       </c>
-      <c r="J71" s="101">
+      <c r="J71" s="92">
         <v>45775.729166666701</v>
       </c>
       <c r="K71" s="70" t="str">
-        <f ca="1">IF(OR(I71="",J71=""),"",IF(AND(J71&lt;&gt;"",I71&gt;=NOW()),"Planned",IF(AND(J71&lt;&gt;"",J71&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L71" s="71">
@@ -10439,14 +10424,14 @@
       <c r="H72" s="53" t="s">
         <v>240</v>
       </c>
-      <c r="I72" s="108">
+      <c r="I72" s="92">
         <v>45776</v>
       </c>
-      <c r="J72" s="101">
+      <c r="J72" s="92">
         <v>45776</v>
       </c>
       <c r="K72" s="70" t="str">
-        <f ca="1">IF(OR(I72="",J72=""),"",IF(AND(J72&lt;&gt;"",I72&gt;=NOW()),"Planned",IF(AND(J72&lt;&gt;"",J72&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L72" s="71">
@@ -10488,14 +10473,14 @@
       <c r="H73" s="53" t="s">
         <v>240</v>
       </c>
-      <c r="I73" s="108">
+      <c r="I73" s="92">
         <v>45776</v>
       </c>
-      <c r="J73" s="101">
+      <c r="J73" s="92">
         <v>45776</v>
       </c>
       <c r="K73" s="70" t="str">
-        <f ca="1">IF(OR(I73="",J73=""),"",IF(AND(J73&lt;&gt;"",I73&gt;=NOW()),"Planned",IF(AND(J73&lt;&gt;"",J73&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L73" s="71">
@@ -10535,14 +10520,14 @@
         <v>130</v>
       </c>
       <c r="H74" s="53"/>
-      <c r="I74" s="108">
+      <c r="I74" s="92">
         <v>45776</v>
       </c>
-      <c r="J74" s="101">
+      <c r="J74" s="92">
         <v>45776</v>
       </c>
       <c r="K74" s="70" t="str">
-        <f ca="1">IF(OR(I74="",J74=""),"",IF(AND(J74&lt;&gt;"",I74&gt;=NOW()),"Planned",IF(AND(J74&lt;&gt;"",J74&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
       <c r="L74" s="71">
@@ -10584,14 +10569,14 @@
       <c r="H75" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="I75" s="108">
+      <c r="I75" s="92">
         <v>45776</v>
       </c>
-      <c r="J75" s="101">
+      <c r="J75" s="92">
         <v>45776</v>
       </c>
       <c r="K75" s="70" t="str">
-        <f ca="1">IF(OR(I75="",J75=""),"",IF(AND(J75&lt;&gt;"",I75&gt;=NOW()),"Planned",IF(AND(J75&lt;&gt;"",J75&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ref="K75:K96" ca="1" si="2">IF(OR(I75="",J75=""),"",IF(AND(J75&lt;&gt;"",I75&gt;=NOW()),"Planned",IF(AND(J75&lt;&gt;"",J75&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L75" s="71">
@@ -10633,14 +10618,14 @@
       <c r="H76" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="I76" s="108">
+      <c r="I76" s="92">
         <v>45776</v>
       </c>
-      <c r="J76" s="101">
+      <c r="J76" s="92">
         <v>45776</v>
       </c>
       <c r="K76" s="70" t="str">
-        <f ca="1">IF(OR(I76="",J76=""),"",IF(AND(J76&lt;&gt;"",I76&gt;=NOW()),"Planned",IF(AND(J76&lt;&gt;"",J76&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L76" s="71">
@@ -10682,14 +10667,14 @@
       <c r="H77" s="53" t="s">
         <v>241</v>
       </c>
-      <c r="I77" s="108">
+      <c r="I77" s="92">
         <v>45776</v>
       </c>
-      <c r="J77" s="101">
+      <c r="J77" s="92">
         <v>45776</v>
       </c>
       <c r="K77" s="70" t="str">
-        <f ca="1">IF(OR(I77="",J77=""),"",IF(AND(J77&lt;&gt;"",I77&gt;=NOW()),"Planned",IF(AND(J77&lt;&gt;"",J77&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L77" s="71">
@@ -10731,14 +10716,14 @@
       <c r="H78" s="53" t="s">
         <v>242</v>
       </c>
-      <c r="I78" s="108">
+      <c r="I78" s="92">
         <v>45776</v>
       </c>
-      <c r="J78" s="101">
+      <c r="J78" s="92">
         <v>45776</v>
       </c>
       <c r="K78" s="70" t="str">
-        <f ca="1">IF(OR(I78="",J78=""),"",IF(AND(J78&lt;&gt;"",I78&gt;=NOW()),"Planned",IF(AND(J78&lt;&gt;"",J78&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L78" s="71">
@@ -10778,14 +10763,14 @@
         <v>26</v>
       </c>
       <c r="H79" s="53"/>
-      <c r="I79" s="108">
+      <c r="I79" s="92">
         <v>45776</v>
       </c>
-      <c r="J79" s="101">
+      <c r="J79" s="92">
         <v>45776</v>
       </c>
       <c r="K79" s="70" t="str">
-        <f ca="1">IF(OR(I79="",J79=""),"",IF(AND(J79&lt;&gt;"",I79&gt;=NOW()),"Planned",IF(AND(J79&lt;&gt;"",J79&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L79" s="71">
@@ -10825,14 +10810,14 @@
         <v>26</v>
       </c>
       <c r="H80" s="53"/>
-      <c r="I80" s="108">
+      <c r="I80" s="92">
         <v>45776</v>
       </c>
-      <c r="J80" s="101">
+      <c r="J80" s="92">
         <v>45776</v>
       </c>
       <c r="K80" s="70" t="str">
-        <f ca="1">IF(OR(I80="",J80=""),"",IF(AND(J80&lt;&gt;"",I80&gt;=NOW()),"Planned",IF(AND(J80&lt;&gt;"",J80&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L80" s="71">
@@ -10872,14 +10857,14 @@
         <v>26</v>
       </c>
       <c r="H81" s="53"/>
-      <c r="I81" s="108">
+      <c r="I81" s="92">
         <v>45776</v>
       </c>
-      <c r="J81" s="101">
+      <c r="J81" s="92">
         <v>45776</v>
       </c>
       <c r="K81" s="70" t="str">
-        <f ca="1">IF(OR(I81="",J81=""),"",IF(AND(J81&lt;&gt;"",I81&gt;=NOW()),"Planned",IF(AND(J81&lt;&gt;"",J81&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L81" s="71">
@@ -10919,14 +10904,14 @@
         <v>24</v>
       </c>
       <c r="H82" s="53"/>
-      <c r="I82" s="108">
+      <c r="I82" s="92">
         <v>45776</v>
       </c>
-      <c r="J82" s="101">
+      <c r="J82" s="92">
         <v>45776</v>
       </c>
       <c r="K82" s="70" t="str">
-        <f ca="1">IF(OR(I82="",J82=""),"",IF(AND(J82&lt;&gt;"",I82&gt;=NOW()),"Planned",IF(AND(J82&lt;&gt;"",J82&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L82" s="71">
@@ -10966,14 +10951,14 @@
         <v>24</v>
       </c>
       <c r="H83" s="53"/>
-      <c r="I83" s="108">
+      <c r="I83" s="92">
         <v>45776</v>
       </c>
-      <c r="J83" s="101">
+      <c r="J83" s="92">
         <v>45776</v>
       </c>
       <c r="K83" s="70" t="str">
-        <f ca="1">IF(OR(I83="",J83=""),"",IF(AND(J83&lt;&gt;"",I83&gt;=NOW()),"Planned",IF(AND(J83&lt;&gt;"",J83&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L83" s="71">
@@ -11013,14 +10998,14 @@
         <v>28</v>
       </c>
       <c r="H84" s="53"/>
-      <c r="I84" s="108">
+      <c r="I84" s="92">
         <v>45776</v>
       </c>
-      <c r="J84" s="101">
+      <c r="J84" s="92">
         <v>45776</v>
       </c>
       <c r="K84" s="70" t="str">
-        <f ca="1">IF(OR(I84="",J84=""),"",IF(AND(J84&lt;&gt;"",I84&gt;=NOW()),"Planned",IF(AND(J84&lt;&gt;"",J84&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L84" s="71">
@@ -11062,14 +11047,14 @@
       <c r="H85" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="I85" s="108">
+      <c r="I85" s="92">
         <v>45776</v>
       </c>
-      <c r="J85" s="101">
+      <c r="J85" s="92">
         <v>45776</v>
       </c>
       <c r="K85" s="70" t="str">
-        <f ca="1">IF(OR(I85="",J85=""),"",IF(AND(J85&lt;&gt;"",I85&gt;=NOW()),"Planned",IF(AND(J85&lt;&gt;"",J85&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L85" s="71">
@@ -11111,14 +11096,14 @@
       <c r="H86" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="I86" s="108">
+      <c r="I86" s="92">
         <v>45776</v>
       </c>
-      <c r="J86" s="101">
+      <c r="J86" s="92">
         <v>45776</v>
       </c>
       <c r="K86" s="70" t="str">
-        <f ca="1">IF(OR(I86="",J86=""),"",IF(AND(J86&lt;&gt;"",I86&gt;=NOW()),"Planned",IF(AND(J86&lt;&gt;"",J86&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L86" s="71">
@@ -11160,14 +11145,14 @@
       <c r="H87" s="53" t="s">
         <v>249</v>
       </c>
-      <c r="I87" s="108">
+      <c r="I87" s="92">
         <v>45776</v>
       </c>
-      <c r="J87" s="101">
+      <c r="J87" s="92">
         <v>45776</v>
       </c>
       <c r="K87" s="70" t="str">
-        <f ca="1">IF(OR(I87="",J87=""),"",IF(AND(J87&lt;&gt;"",I87&gt;=NOW()),"Planned",IF(AND(J87&lt;&gt;"",J87&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L87" s="71">
@@ -11209,14 +11194,14 @@
       <c r="H88" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="I88" s="108">
+      <c r="I88" s="92">
         <v>45776</v>
       </c>
-      <c r="J88" s="101">
+      <c r="J88" s="92">
         <v>45776</v>
       </c>
       <c r="K88" s="70" t="str">
-        <f ca="1">IF(OR(I88="",J88=""),"",IF(AND(J88&lt;&gt;"",I88&gt;=NOW()),"Planned",IF(AND(J88&lt;&gt;"",J88&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L88" s="71">
@@ -11258,14 +11243,14 @@
       <c r="H89" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="I89" s="108">
+      <c r="I89" s="92">
         <v>45776</v>
       </c>
-      <c r="J89" s="101">
+      <c r="J89" s="92">
         <v>45776</v>
       </c>
       <c r="K89" s="70" t="str">
-        <f ca="1">IF(OR(I89="",J89=""),"",IF(AND(J89&lt;&gt;"",I89&gt;=NOW()),"Planned",IF(AND(J89&lt;&gt;"",J89&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L89" s="71">
@@ -11307,14 +11292,14 @@
       <c r="H90" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="I90" s="108">
+      <c r="I90" s="92">
         <v>45776</v>
       </c>
-      <c r="J90" s="101">
+      <c r="J90" s="92">
         <v>45776</v>
       </c>
       <c r="K90" s="70" t="str">
-        <f ca="1">IF(OR(I90="",J90=""),"",IF(AND(J90&lt;&gt;"",I90&gt;=NOW()),"Planned",IF(AND(J90&lt;&gt;"",J90&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L90" s="71">
@@ -11356,14 +11341,14 @@
       <c r="H91" s="53" t="s">
         <v>255</v>
       </c>
-      <c r="I91" s="108">
+      <c r="I91" s="92">
         <v>45776</v>
       </c>
-      <c r="J91" s="101">
+      <c r="J91" s="92">
         <v>45776</v>
       </c>
       <c r="K91" s="70" t="str">
-        <f ca="1">IF(OR(I91="",J91=""),"",IF(AND(J91&lt;&gt;"",I91&gt;=NOW()),"Planned",IF(AND(J91&lt;&gt;"",J91&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L91" s="71">
@@ -11403,14 +11388,14 @@
         <v>50</v>
       </c>
       <c r="H92" s="53"/>
-      <c r="I92" s="108">
+      <c r="I92" s="92">
         <v>45776</v>
       </c>
-      <c r="J92" s="101">
+      <c r="J92" s="92">
         <v>45776</v>
       </c>
       <c r="K92" s="70" t="str">
-        <f ca="1">IF(OR(I92="",J92=""),"",IF(AND(J92&lt;&gt;"",I92&gt;=NOW()),"Planned",IF(AND(J92&lt;&gt;"",J92&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L92" s="71">
@@ -11452,14 +11437,14 @@
       <c r="H93" s="53" t="s">
         <v>258</v>
       </c>
-      <c r="I93" s="108">
+      <c r="I93" s="92">
         <v>45776</v>
       </c>
-      <c r="J93" s="101">
+      <c r="J93" s="92">
         <v>45776</v>
       </c>
       <c r="K93" s="70" t="str">
-        <f ca="1">IF(OR(I93="",J93=""),"",IF(AND(J93&lt;&gt;"",I93&gt;=NOW()),"Planned",IF(AND(J93&lt;&gt;"",J93&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L93" s="71">
@@ -11501,14 +11486,14 @@
       <c r="H94" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="I94" s="108">
+      <c r="I94" s="92">
         <v>45776</v>
       </c>
-      <c r="J94" s="101">
+      <c r="J94" s="92">
         <v>45776</v>
       </c>
       <c r="K94" s="70" t="str">
-        <f ca="1">IF(OR(I94="",J94=""),"",IF(AND(J94&lt;&gt;"",I94&gt;=NOW()),"Planned",IF(AND(J94&lt;&gt;"",J94&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L94" s="71">
@@ -11548,14 +11533,14 @@
         <v>24</v>
       </c>
       <c r="H95" s="53"/>
-      <c r="I95" s="108">
+      <c r="I95" s="92">
         <v>45776</v>
       </c>
-      <c r="J95" s="101">
+      <c r="J95" s="92">
         <v>45776</v>
       </c>
       <c r="K95" s="70" t="str">
-        <f ca="1">IF(OR(I95="",J95=""),"",IF(AND(J95&lt;&gt;"",I95&gt;=NOW()),"Planned",IF(AND(J95&lt;&gt;"",J95&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L95" s="71">
@@ -11595,14 +11580,14 @@
         <v>26</v>
       </c>
       <c r="H96" s="53"/>
-      <c r="I96" s="108">
+      <c r="I96" s="92">
         <v>45776</v>
       </c>
-      <c r="J96" s="101">
+      <c r="J96" s="92">
         <v>45776</v>
       </c>
       <c r="K96" s="70" t="str">
-        <f ca="1">IF(OR(I96="",J96=""),"",IF(AND(J96&lt;&gt;"",I96&gt;=NOW()),"Planned",IF(AND(J96&lt;&gt;"",J96&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="2"/>
         <v>Completed</v>
       </c>
       <c r="L96" s="71">
@@ -11631,8 +11616,8 @@
       <c r="F97" s="53"/>
       <c r="G97" s="53"/>
       <c r="H97" s="53"/>
-      <c r="I97" s="108"/>
-      <c r="J97" s="101"/>
+      <c r="I97" s="92"/>
+      <c r="J97" s="92"/>
       <c r="K97" s="70"/>
       <c r="L97" s="71"/>
       <c r="M97" s="71"/>
@@ -11650,8 +11635,8 @@
       <c r="F98" s="53"/>
       <c r="G98" s="53"/>
       <c r="H98" s="53"/>
-      <c r="I98" s="108"/>
-      <c r="J98" s="101"/>
+      <c r="I98" s="92"/>
+      <c r="J98" s="92"/>
       <c r="K98" s="70"/>
       <c r="L98" s="71"/>
       <c r="M98" s="71"/>
@@ -11669,8 +11654,8 @@
       <c r="F99" s="53"/>
       <c r="G99" s="53"/>
       <c r="H99" s="53"/>
-      <c r="I99" s="108"/>
-      <c r="J99" s="101"/>
+      <c r="I99" s="92"/>
+      <c r="J99" s="92"/>
       <c r="K99" s="70"/>
       <c r="L99" s="71"/>
       <c r="M99" s="71"/>
@@ -11688,8 +11673,8 @@
       <c r="F100" s="53"/>
       <c r="G100" s="53"/>
       <c r="H100" s="53"/>
-      <c r="I100" s="108"/>
-      <c r="J100" s="101"/>
+      <c r="I100" s="92"/>
+      <c r="J100" s="92"/>
       <c r="K100" s="70"/>
       <c r="L100" s="71"/>
       <c r="M100" s="71"/>
@@ -11707,8 +11692,8 @@
       <c r="F101" s="53"/>
       <c r="G101" s="53"/>
       <c r="H101" s="53"/>
-      <c r="I101" s="108"/>
-      <c r="J101" s="101"/>
+      <c r="I101" s="92"/>
+      <c r="J101" s="92"/>
       <c r="K101" s="70"/>
       <c r="L101" s="71"/>
       <c r="M101" s="71"/>
@@ -11726,8 +11711,8 @@
       <c r="F102" s="53"/>
       <c r="G102" s="53"/>
       <c r="H102" s="53"/>
-      <c r="I102" s="108"/>
-      <c r="J102" s="101"/>
+      <c r="I102" s="92"/>
+      <c r="J102" s="92"/>
       <c r="K102" s="70"/>
       <c r="L102" s="71"/>
       <c r="M102" s="71"/>
@@ -11745,8 +11730,8 @@
       <c r="F103" s="53"/>
       <c r="G103" s="53"/>
       <c r="H103" s="53"/>
-      <c r="I103" s="108"/>
-      <c r="J103" s="101"/>
+      <c r="I103" s="92"/>
+      <c r="J103" s="92"/>
       <c r="K103" s="70"/>
       <c r="L103" s="71"/>
       <c r="M103" s="71"/>
@@ -11764,8 +11749,8 @@
       <c r="F104" s="53"/>
       <c r="G104" s="53"/>
       <c r="H104" s="53"/>
-      <c r="I104" s="108"/>
-      <c r="J104" s="101"/>
+      <c r="I104" s="92"/>
+      <c r="J104" s="92"/>
       <c r="K104" s="70"/>
       <c r="L104" s="71"/>
       <c r="M104" s="71"/>
@@ -11783,8 +11768,8 @@
       <c r="F105" s="53"/>
       <c r="G105" s="53"/>
       <c r="H105" s="53"/>
-      <c r="I105" s="108"/>
-      <c r="J105" s="101"/>
+      <c r="I105" s="92"/>
+      <c r="J105" s="92"/>
       <c r="K105" s="70"/>
       <c r="L105" s="71"/>
       <c r="M105" s="71"/>
@@ -11802,8 +11787,8 @@
       <c r="F106" s="53"/>
       <c r="G106" s="53"/>
       <c r="H106" s="53"/>
-      <c r="I106" s="108"/>
-      <c r="J106" s="101"/>
+      <c r="I106" s="92"/>
+      <c r="J106" s="92"/>
       <c r="K106" s="70"/>
       <c r="L106" s="71"/>
       <c r="M106" s="71"/>
@@ -11821,8 +11806,8 @@
       <c r="F107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
-      <c r="I107" s="108"/>
-      <c r="J107" s="101"/>
+      <c r="I107" s="92"/>
+      <c r="J107" s="92"/>
       <c r="K107" s="70"/>
       <c r="L107" s="71"/>
       <c r="M107" s="71"/>
@@ -11840,8 +11825,8 @@
       <c r="F108" s="53"/>
       <c r="G108" s="53"/>
       <c r="H108" s="53"/>
-      <c r="I108" s="108"/>
-      <c r="J108" s="101"/>
+      <c r="I108" s="92"/>
+      <c r="J108" s="92"/>
       <c r="K108" s="70"/>
       <c r="L108" s="71"/>
       <c r="M108" s="71"/>
@@ -11859,8 +11844,8 @@
       <c r="F109" s="53"/>
       <c r="G109" s="53"/>
       <c r="H109" s="53"/>
-      <c r="I109" s="108"/>
-      <c r="J109" s="101"/>
+      <c r="I109" s="92"/>
+      <c r="J109" s="92"/>
       <c r="K109" s="70"/>
       <c r="L109" s="71"/>
       <c r="M109" s="71"/>
@@ -11878,8 +11863,8 @@
       <c r="F110" s="53"/>
       <c r="G110" s="53"/>
       <c r="H110" s="53"/>
-      <c r="I110" s="108"/>
-      <c r="J110" s="101"/>
+      <c r="I110" s="92"/>
+      <c r="J110" s="92"/>
       <c r="K110" s="70"/>
       <c r="L110" s="71"/>
       <c r="M110" s="71"/>
@@ -11897,8 +11882,8 @@
       <c r="F111" s="53"/>
       <c r="G111" s="53"/>
       <c r="H111" s="53"/>
-      <c r="I111" s="108"/>
-      <c r="J111" s="101"/>
+      <c r="I111" s="92"/>
+      <c r="J111" s="92"/>
       <c r="K111" s="70"/>
       <c r="L111" s="71"/>
       <c r="M111" s="71"/>
@@ -11916,8 +11901,8 @@
       <c r="F112" s="53"/>
       <c r="G112" s="53"/>
       <c r="H112" s="53"/>
-      <c r="I112" s="108"/>
-      <c r="J112" s="101"/>
+      <c r="I112" s="92"/>
+      <c r="J112" s="92"/>
       <c r="K112" s="70"/>
       <c r="L112" s="71"/>
       <c r="M112" s="71"/>
@@ -11935,8 +11920,8 @@
       <c r="F113" s="53"/>
       <c r="G113" s="53"/>
       <c r="H113" s="53"/>
-      <c r="I113" s="108"/>
-      <c r="J113" s="101"/>
+      <c r="I113" s="92"/>
+      <c r="J113" s="92"/>
       <c r="K113" s="70"/>
       <c r="L113" s="71"/>
       <c r="M113" s="71"/>
@@ -12005,40 +11990,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="100" t="s">
         <v>154</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="93"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="98"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -12057,7 +12042,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="101" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -12080,7 +12065,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="93"/>
+      <c r="C7" s="98"/>
       <c r="D7" s="11" t="s">
         <v>4</v>
       </c>
@@ -12098,19 +12083,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="92" t="s">
+      <c r="I9" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="93"/>
+      <c r="J9" s="98"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="92" t="s">
+      <c r="L9" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="93"/>
-      <c r="N9" s="92" t="s">
+      <c r="M9" s="98"/>
+      <c r="N9" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="93"/>
+      <c r="O9" s="98"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -15311,52 +15296,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="100" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="99" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
